--- a/해양시설신고/output/261012_입법영향분석_해양시설신고_법령개정_필요사항.xlsx
+++ b/해양시설신고/output/261012_입법영향분석_해양시설신고_법령개정_필요사항.xlsx
@@ -458,7 +458,7 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
-    <col width="190" customWidth="1" min="7" max="7"/>
+    <col width="250" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,9 +523,9 @@
           <t>「해양환경관리법」 제2조제17호(해양시설 정의: 해양수산부령 위임)
 법 제33조제1항(신고 의무)
 법 제132조제2항제2호(신고 미이행 과태료)
-시행규칙 제17조제1항(별표 1 인용)
-시행규칙 별표 1 해양시설의 범위 — 제1호 가목·라목, 제2호 (2013.3.24. 개정본 기준, 현행본 원문 미대조)
-별표 1 제1호 라목이 재위임한 해양수산부 고시(제정 여부 미확인)
+시행규칙 제3조(법 제2조제17호의 시설 = 별표 1)
+시행규칙 별표 1 해양시설의 범위(제3조 관련, 개정 2020.12.4.) 제1호 가목·다목·라목, 제2호 가목·나목·라목
+별표 1 제1호 라목이 재위임한 해양수산부 고시(국가법령정보센터 행정규칙 DB에서 확인되지 않음)
 시행령 별표 19(과태료 부과기준)</t>
         </is>
       </c>
@@ -537,15 +537,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 항만 포함)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제17조제1항이 별표 1을 인용한다. 별표 1(2013.3.24. 개정본 기준)은 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 시설)에서 가목 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 라목(시멘트·석탄·사료·곡물 등 하역시설) '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 선박 건조·수리·해체시설 등을, 제2호(해양레저·관광·주거·해수이용 시설)에서 연면적 100㎡ 이상 해상관광·주거·음식점 시설(「선박안전법」상 선박 제외), 관경 600㎜ 이상 취수·배수시설(배관 포함), 유어장, 가두리낚시터 등을 열거한다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다. 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 별표 1의 '계류시설(돌핀)', '하역설비', '저장시설' 등은 「항만법」(항만시설), 「항만운송사업법」(항만하역 시설), 「위험물안전관리법」 등 다른 법령의 시설 분류와 연계 없이 일반 용어로만 기재되어 있어, 같은 물적 시설이 신고 대상인지 담당자마다 판단이 갈린다(인터뷰이: "이 법에서만 이런 용어를 쓰는 것 같아서"). ② 제1호 라목은 대상 특정을 해양수산부 고시에 재위임하는데, 해당 고시의 제정 여부가 확인되지 않는다. 고시가 없으면 별표 문언만으로는 "고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐"는 범위 문제가 생긴다(위임사항 미이행 가능성). ③ 별표의 열거 항목은 "해양레저·관광 시설"에 대해서는 제외 규정(선박안전법상 선박 제외)을 두면서 제1호 시설에는 다른 법령과의 중복 처리 기준이 없어 "다른 법령과 중복이 되어도 되는 건지" 불명확하다. ④ 신고 대상 여부가 과태료 부과의 구성요건이므로 대상 범위의 불명확은 곧 제재 요건의 불명확이다.
-[논거] 법 제2조제17호가 대상 시설의 특정을 부령에 포괄 위임하고 별표 1이 다시 고시에 재위임하는 구조에서, 최종 단계(고시)가 비어 있거나 문언이 열려 있으면 신고 의무(법 제33조제1항)와 과태료(법 제132조)의 적용 범위가 법령 문언으로 확정되지 않는다. 의무 부과·제재의 구성요건은 수범자가 예측할 수 있을 정도로 명확해야 한다는 명확성 원칙과 위임입법의 한계(위임받은 사항을 하위법령이 정하지 않은 상태) 문제이며, 담당자 해석이나 질의회신으로 보충할 사항이 아니라 별표·고시 문언 자체의 정비 사항이다. 인터뷰이가 유사 시설에 대해 담당자별 판단이 달라질 수 있다고 인정한 점("조금 있다고 볼 수 있습니다")은 평등 원칙 차원의 문제이기도 하다.
-[개정 방향] ① (부령) 별표 1 각 항목에 근거 법령상 시설 분류를 인용하도록 문언을 고친다. 예: 계류시설은 「항만법」상 항만시설 중 계류시설의 세부 종류로, 하역시설은 「항만운송사업법」상 항만하역 시설로 특정하고, 그 밖의 시설은 '○○법 제○조에 따른 ○○시설' 형식으로 쓴다. ② (부령·고시) 제1호 라목의 '해양수산부장관이 정하여 고시하는' 부분은 고시를 제정하거나, 고시 없이 별표에 직접 열거하는 방식으로 재위임을 해소한다. ③ (부령) 다른 법령에 따라 안전관리·신고 대상이 되는 시설과의 관계(중복 적용 여부, 제외 사유)를 별표 비고에 명시한다. ④ (법률, 선택) 법 제2조제17호의 포괄 위임을 완화하여 시설 유형(기름·유해액체물질의 저장·이송·계류, 취수·배수, 해양레저·관광 등)을 법률에 예시로 열거하고 세부를 부령에 위임한다. 최소 정비안은 ①~③(부령·고시)만으로 가능하다. 연번 2(부산청)와 연계.
-[유의] 별표 1 현행본 전문과 고시 존재 여부를 원문으로 확인해야 하며, 확인 결과에 따라 ②의 서술이 달라질 수 있다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 인터뷰이는 돌핀·하역설비의 정의 연계를 희망하면서도 "그정도까지 복잡한 것은 아니"라고 하여 입법사실의 규모는 크지 않다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="409" customHeight="1">
+          <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 규정에 따른 항만을 포함한다)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제3조가 이를 별표 1의 시설로 정한다. 별표 1(개정 2020.12.4.)은 ① 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 목적 시설)에 가목 기름·유해액체물질 저장시설 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 나목 법 제38조의 오염물질저장시설, 다목 선박 건조·수리·해체시설 '저장시설, 상가시설 및 수리시설(이동식 시설은 제외)', 라목 시멘트·석탄·사료·곡물·고철·광석·목재·토사의 하역시설 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 마목 폐기물해양배출업자의 폐기물저장시설을, ② 제2호(해양레저·관광·주거·해수이용 등 목적 시설)에 가목 연면적 100㎡ 이상 해상관광·주거·음식점 시설(범위: 해역 안 시설, 해역과 육지 사이 연속 시설은 취수·배수 시설(배관 포함)), 나목 관경 600㎜ 이상 취수·배수시설, 다목 유어장, 라목 '그 밖의 시설'의 범위로 '해상송전철탑, 해저광케이블, 해상부유구조물'을, ③ 제3호에 종합해양과학기지를 열거한다. 라목의 계류시설·하역설비를 정하는 해양수산부 고시는 2026.10.12. 국가법령정보센터 행정규칙 DB 검색('해양시설'(고시), '하역설비', '계류시설')에서 확인되지 않았다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 별표 1의 '계류시설(돌핀)', '하역설비', '저장시설', '상가시설' 등은 「항만법」(항만시설), 「항만운송사업법」(항만하역), 「위험물안전관리법」 등 다른 법령의 시설 분류와 연계 없이 일반 용어로만 기재되어 있어, 같은 물적 시설이 신고 대상인지 담당자마다 판단이 갈린다(인터뷰이: "이 법에서만 이런 용어를 쓰는 것 같아서"). ② 제1호 라목은 대상 특정을 해양수산부 고시에 재위임하는데 해당 고시가 확인되지 않는다. 고시가 없으면 별표 문언만으로는 "고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐"는 범위 문제가 생긴다(위임사항 미이행). ③ 별표는 제2호 가목에 대해서만 해역·육지 연속 시설의 신고 범위 기준(취수·배수 시설)을 두고, 제2호 라목 '그 밖의 시설'은 '해상송전철탑, 해저광케이블, 해상부유구조물'의 닫힌 열거여서 육상 철탑 사이를 해상으로 지나는 송전선로처럼 해역과 육지에 걸친 시설의 어느 부분이 신고 대상인지 판단 기준이 없다. ④ 제2호 가목은 「선박안전법」상 선박을 제외하는 등 제외 규정을 두면서 제1호 시설에는 다른 법령에 따른 안전관리 대상과의 중복 처리 기준이 없어 "다른 법령과 중복이 되어도 되는 건지" 불명확하다. ⑤ 신고 대상 여부가 과태료 부과의 구성요건이므로 대상 범위의 불명확은 곧 제재 요건의 불명확이다.
+[논거] 법 제2조제17호가 대상 시설의 특정을 부령에 포괄 위임하고 별표 1이 다시 고시에 재위임하는 구조에서, 최종 단계(고시)가 비어 있거나 문언이 열려 있으면 신고 의무(법 제33조제1항)와 과태료(법 제132조제2항제2호, 「질서위반행위규제법」 제6조의 법정주의)의 적용 범위가 법령 문언으로 확정되지 않는다. 의무 부과·제재의 구성요건은 수범자가 예측할 수 있을 정도로 명확해야 한다는 명확성 원칙과 위임입법의 한계(위임받은 사항을 하위법령이 정하지 않은 상태) 문제이며, 담당자 해석이나 질의회신으로 보충할 사항이 아니라 별표·고시 문언 자체의 정비 사항이다. 인터뷰이가 유사 시설에 대해 담당자별 판단이 달라질 수 있다고 인정한 점("조금 있다고 볼 수 있습니다")은 평등 원칙 차원의 문제이기도 하다.
+[개정 방향] ① (부령) 별표 1 각 항목에 근거 법령상 시설 분류를 인용하도록 문언을 고친다. 예: 계류시설은 「항만법」상 항만시설 중 계류시설의 세부 종류로, 하역시설은 「항만운송사업법」상 항만하역 시설로 특정하고, 그 밖의 시설은 '○○법 제○조에 따른 ○○시설' 형식으로 쓴다. ② (부령·고시) 제1호 라목의 '해양수산부장관이 정하여 고시하는' 부분은 고시를 제정하거나, 고시 없이 별표에 직접 열거하는 방식으로 재위임을 해소한다. ③ (부령) 제2호 가목에만 있는 해역·육지 연속 시설의 범위 기준을 별표 비고로 옮겨 제1호·제2호 전체에 적용되는 공통 기준(예: 해역 안에 설치된 부분과 그에 연속한 배관·선로)으로 두고, 다른 법령에 따른 안전관리 대상 시설과의 관계(중복 적용 여부, 제외 사유)를 비고에 명시한다. ④ (법률, 선택) 법 제2조제17호의 포괄 위임을 완화하여 시설 유형(기름·유해액체물질의 저장·이송·계류, 취수·배수, 해양레저·관광 등)을 법률에 예시로 열거하고 세부를 부령에 위임한다. 최소 정비안은 ①~③(부령·고시)만으로 가능하다. 연번 2(부산청)와 연계.
+[유의] 별표 1 현행본(개정 2020.12.4.)은 원문으로 확인했고, 2013.3.24. 개정본과 비교해 제1호 마목의 인용 법령명만 바뀌었을 뿐 '해상송전철탑' 등은 2013년부터 열거되어 있었다. 고시는 국가법령정보센터 행정규칙 DB에 등재되지 않은 것일 수 있으므로 해양수산부(해양보전과)에 제정 여부를 확인해야 한다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 인터뷰이는 돌핀·하역설비의 정의 연계를 희망하면서도 "그정도까지 복잡한 것은 아니"라고 하여 입법사실의 규모는 크지 않다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="397.5" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -570,9 +570,9 @@
           <t>「해양환경관리법」 제2조제17호(해양시설 정의: 해양수산부령 위임)
 법 제33조제1항(신고 의무)
 법 제132조제2항제2호(신고 미이행 과태료)
-시행규칙 제17조제1항(별표 1 인용)
-시행규칙 별표 1 해양시설의 범위 — 제1호 가목·라목, 제2호 (2013.3.24. 개정본 기준, 현행본 원문 미대조)
-별표 1 제1호 라목이 재위임한 해양수산부 고시(제정 여부 미확인)
+시행규칙 제3조(법 제2조제17호의 시설 = 별표 1)
+시행규칙 별표 1 해양시설의 범위(제3조 관련, 개정 2020.12.4.) 제1호 가목·다목·라목, 제2호 가목·나목·라목
+별표 1 제1호 라목이 재위임한 해양수산부 고시(국가법령정보센터 행정규칙 DB에서 확인되지 않음)
 시행령 별표 19(과태료 부과기준)</t>
         </is>
       </c>
@@ -584,11 +584,11 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 항만 포함)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제17조제1항이 별표 1을 인용한다. 별표 1(2013.3.24. 개정본 기준)은 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 시설)에서 가목 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 라목(시멘트·석탄·사료·곡물 등 하역시설) '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 선박 건조·수리·해체시설 등을, 제2호(해양레저·관광·주거·해수이용 시설)에서 연면적 100㎡ 이상 해상관광·주거·음식점 시설(「선박안전법」상 선박 제외), 관경 600㎜ 이상 취수·배수시설(배관 포함), 유어장, 가두리낚시터 등을 열거한다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다. 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 별표 1의 '계류시설(돌핀)', '하역설비', '저장시설' 등은 「항만법」(항만시설), 「항만운송사업법」(항만하역 시설), 「위험물안전관리법」 등 다른 법령의 시설 분류와 연계 없이 일반 용어로만 기재되어 있어, 같은 물적 시설이 신고 대상인지 담당자마다 판단이 갈린다(인터뷰이: "이 법에서만 이런 용어를 쓰는 것 같아서"). ② 제1호 라목은 대상 특정을 해양수산부 고시에 재위임하는데, 해당 고시의 제정 여부가 확인되지 않는다. 고시가 없으면 별표 문언만으로는 "고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐"는 범위 문제가 생긴다(위임사항 미이행 가능성). ③ 별표의 열거 항목은 "해양레저·관광 시설"에 대해서는 제외 규정(선박안전법상 선박 제외)을 두면서 제1호 시설에는 다른 법령과의 중복 처리 기준이 없어 "다른 법령과 중복이 되어도 되는 건지" 불명확하다. ④ 신고 대상 여부가 과태료 부과의 구성요건이므로 대상 범위의 불명확은 곧 제재 요건의 불명확이다.
-[논거] 법 제2조제17호가 대상 시설의 특정을 부령에 포괄 위임하고 별표 1이 다시 고시에 재위임하는 구조에서, 최종 단계(고시)가 비어 있거나 문언이 열려 있으면 신고 의무(법 제33조제1항)와 과태료(법 제132조)의 적용 범위가 법령 문언으로 확정되지 않는다. 의무 부과·제재의 구성요건은 수범자가 예측할 수 있을 정도로 명확해야 한다는 명확성 원칙과 위임입법의 한계(위임받은 사항을 하위법령이 정하지 않은 상태) 문제이며, 담당자 해석이나 질의회신으로 보충할 사항이 아니라 별표·고시 문언 자체의 정비 사항이다. 인터뷰이가 유사 시설에 대해 담당자별 판단이 달라질 수 있다고 인정한 점("조금 있다고 볼 수 있습니다")은 평등 원칙 차원의 문제이기도 하다.
-[개정 방향] ① (부령) 별표 1 각 항목에 근거 법령상 시설 분류를 인용하도록 문언을 고친다. 예: 계류시설은 「항만법」상 항만시설 중 계류시설의 세부 종류로, 하역시설은 「항만운송사업법」상 항만하역 시설로 특정하고, 그 밖의 시설은 '○○법 제○조에 따른 ○○시설' 형식으로 쓴다. ② (부령·고시) 제1호 라목의 '해양수산부장관이 정하여 고시하는' 부분은 고시를 제정하거나, 고시 없이 별표에 직접 열거하는 방식으로 재위임을 해소한다. ③ (부령) 다른 법령에 따라 안전관리·신고 대상이 되는 시설과의 관계(중복 적용 여부, 제외 사유)를 별표 비고에 명시한다. ④ (법률, 선택) 법 제2조제17호의 포괄 위임을 완화하여 시설 유형(기름·유해액체물질의 저장·이송·계류, 취수·배수, 해양레저·관광 등)을 법률에 예시로 열거하고 세부를 부령에 위임한다. 최소 정비안은 ①~③(부령·고시)만으로 가능하다. 연번 1(군산청)과 연계. 특히 해역과 육지에 걸쳐 연속 설치되는 시설(송전선로·철탑, 배관)은 별표 비고에 '해역 안에 설치된 부분' 등 신고 대상 구간의 기준을 두는 것이 부산청 사례에 직접 대응한다.
-[유의] 별표 1 현행본 전문과 고시 존재 여부를 원문으로 확인해야 하며, 확인 결과에 따라 ②의 서술이 달라질 수 있다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 한전 송전철탑 사례는 인터뷰이가 다른 지방청의 처리 결과를 전해 들은 것이므로 교차 확인이 필요하다. 인터뷰이는 '등' 같은 예시 표현을 희망했으나, 예시 규정은 대상 확대로 읽힐 수 있어 근거 법령 인용 방식이 더 안전하다. [교차확인] 연번 1(군산청 인터뷰)과 동일 쟁점.</t>
+          <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 규정에 따른 항만을 포함한다)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제3조가 이를 별표 1의 시설로 정한다. 별표 1(개정 2020.12.4.)은 ① 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 목적 시설)에 가목 기름·유해액체물질 저장시설 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 나목 법 제38조의 오염물질저장시설, 다목 선박 건조·수리·해체시설 '저장시설, 상가시설 및 수리시설(이동식 시설은 제외)', 라목 시멘트·석탄·사료·곡물·고철·광석·목재·토사의 하역시설 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 마목 폐기물해양배출업자의 폐기물저장시설을, ② 제2호(해양레저·관광·주거·해수이용 등 목적 시설)에 가목 연면적 100㎡ 이상 해상관광·주거·음식점 시설(범위: 해역 안 시설, 해역과 육지 사이 연속 시설은 취수·배수 시설(배관 포함)), 나목 관경 600㎜ 이상 취수·배수시설, 다목 유어장, 라목 '그 밖의 시설'의 범위로 '해상송전철탑, 해저광케이블, 해상부유구조물'을, ③ 제3호에 종합해양과학기지를 열거한다. 라목의 계류시설·하역설비를 정하는 해양수산부 고시는 2026.10.12. 국가법령정보센터 행정규칙 DB 검색('해양시설'(고시), '하역설비', '계류시설')에서 확인되지 않았다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 별표 1의 '계류시설(돌핀)', '하역설비', '저장시설', '상가시설' 등은 「항만법」(항만시설), 「항만운송사업법」(항만하역), 「위험물안전관리법」 등 다른 법령의 시설 분류와 연계 없이 일반 용어로만 기재되어 있어, 같은 물적 시설이 신고 대상인지 담당자마다 판단이 갈린다(인터뷰이: "이 법에서만 이런 용어를 쓰는 것 같아서"). ② 제1호 라목은 대상 특정을 해양수산부 고시에 재위임하는데 해당 고시가 확인되지 않는다. 고시가 없으면 별표 문언만으로는 "고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐"는 범위 문제가 생긴다(위임사항 미이행). ③ 별표는 제2호 가목에 대해서만 해역·육지 연속 시설의 신고 범위 기준(취수·배수 시설)을 두고, 제2호 라목 '그 밖의 시설'은 '해상송전철탑, 해저광케이블, 해상부유구조물'의 닫힌 열거여서 육상 철탑 사이를 해상으로 지나는 송전선로처럼 해역과 육지에 걸친 시설의 어느 부분이 신고 대상인지 판단 기준이 없다. ④ 제2호 가목은 「선박안전법」상 선박을 제외하는 등 제외 규정을 두면서 제1호 시설에는 다른 법령에 따른 안전관리 대상과의 중복 처리 기준이 없어 "다른 법령과 중복이 되어도 되는 건지" 불명확하다. ⑤ 신고 대상 여부가 과태료 부과의 구성요건이므로 대상 범위의 불명확은 곧 제재 요건의 불명확이다.
+[논거] 법 제2조제17호가 대상 시설의 특정을 부령에 포괄 위임하고 별표 1이 다시 고시에 재위임하는 구조에서, 최종 단계(고시)가 비어 있거나 문언이 열려 있으면 신고 의무(법 제33조제1항)와 과태료(법 제132조제2항제2호, 「질서위반행위규제법」 제6조의 법정주의)의 적용 범위가 법령 문언으로 확정되지 않는다. 의무 부과·제재의 구성요건은 수범자가 예측할 수 있을 정도로 명확해야 한다는 명확성 원칙과 위임입법의 한계(위임받은 사항을 하위법령이 정하지 않은 상태) 문제이며, 담당자 해석이나 질의회신으로 보충할 사항이 아니라 별표·고시 문언 자체의 정비 사항이다. 인터뷰이가 유사 시설에 대해 담당자별 판단이 달라질 수 있다고 인정한 점("조금 있다고 볼 수 있습니다")은 평등 원칙 차원의 문제이기도 하다.
+[개정 방향] ① (부령) 별표 1 각 항목에 근거 법령상 시설 분류를 인용하도록 문언을 고친다. 예: 계류시설은 「항만법」상 항만시설 중 계류시설의 세부 종류로, 하역시설은 「항만운송사업법」상 항만하역 시설로 특정하고, 그 밖의 시설은 '○○법 제○조에 따른 ○○시설' 형식으로 쓴다. ② (부령·고시) 제1호 라목의 '해양수산부장관이 정하여 고시하는' 부분은 고시를 제정하거나, 고시 없이 별표에 직접 열거하는 방식으로 재위임을 해소한다. ③ (부령) 제2호 가목에만 있는 해역·육지 연속 시설의 범위 기준을 별표 비고로 옮겨 제1호·제2호 전체에 적용되는 공통 기준(예: 해역 안에 설치된 부분과 그에 연속한 배관·선로)으로 두고, 다른 법령에 따른 안전관리 대상 시설과의 관계(중복 적용 여부, 제외 사유)를 비고에 명시한다. ④ (법률, 선택) 법 제2조제17호의 포괄 위임을 완화하여 시설 유형(기름·유해액체물질의 저장·이송·계류, 취수·배수, 해양레저·관광 등)을 법률에 예시로 열거하고 세부를 부령에 위임한다. 최소 정비안은 ①~③(부령·고시)만으로 가능하다. 연번 1(군산청)과 연계. 부산청의 한전 사례는 별표 1 제2호 라목이 '해상송전철탑'만 열거하고 육상 철탑 사이의 해상 선로 구간을 어떻게 볼지 기준이 없는 데서 생긴 것이므로 ③의 공통 범위 기준이 직접 대응한다.
+[유의] 별표 1 현행본(개정 2020.12.4.)은 원문으로 확인했고, 2013.3.24. 개정본과 비교해 제1호 마목의 인용 법령명만 바뀌었을 뿐 '해상송전철탑' 등은 2013년부터 열거되어 있었다. 고시는 국가법령정보센터 행정규칙 DB에 등재되지 않은 것일 수 있으므로 해양수산부(해양보전과)에 제정 여부를 확인해야 한다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 한전 송전철탑 사례는 인터뷰이가 다른 지방청의 처리 결과를 전해 들은 것이므로 교차 확인이 필요하다. 인터뷰이는 '등' 같은 예시 표현을 희망했으나 예시 규정은 대상 확대로 읽힐 수 있어 근거 법령 인용과 범위 기준 명시가 더 안전하다. [교차확인] 연번 1(군산청 인터뷰)과 동일 쟁점.</t>
         </is>
       </c>
     </row>
@@ -614,13 +614,14 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>「해양환경관리법」 제33조제1항·제2항(원문 미대조)
-시행규칙 제17조제1항·제2항·제5항(원문 미대조)
-시행규칙 별지 제12호서식(처리기간 최초 7일·변경 5일 기재, 원문 미대조)
-시행령 권한 위임 조문(구판 제94조제4항: 신고·변경신고의 '접수' 위임, 현행 조문 번호 미확인)
+          <t>「해양환경관리법」 제33조제1항·제2항
+법 제38조제3항(오염물질저장시설 신고의 수리 여부 통지, 2023.10.24. 신설 — 비교 조문)
+시행령 제94조제4항제2호·제2호의3, 제6항제2호(권한 위임)
+시행규칙 제17조제1항·제2항·제4항·제5항
+시행규칙 별지 제12호서식(처리기간 최초 7일·변경 5일, 처리절차)·별지 제14호서식(신고증명서)
 「행정기본법」 제34조
-「행정절차법」 제40조
-「민원 처리에 관한 법률」 제19조, 같은 법 시행령 제24조·제25조</t>
+「행정절차법」 제40조제2항~제4항
+「민원 처리에 관한 법률」 제19조·제22조제1항, 같은 법 시행령 제24조·제25조</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,11 +632,11 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 그 시설을 임대하는 경우에는 시설임차인)는 해양수산부장관에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(변경신고 후단은 2017.3.21. 개정으로 도입, 법률 번호는 2차 자료 간 상충). 제2항: 신고내용·변경신고 대상·신고 절차 등은 해양수산부령으로 정함. 현행 법률 판본: 2차 자료에 법률 제21065호(2025.10.1. 시행, 타법개정), 2026.1.2. 시행 판본, 법률 제21416호(2026.2.27. 일부개정)가 함께 검색되어 최신 공포번호·시행일은 원문으로 확정 필요. 수리 여부, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 법률에서 확인되지 않음. 시행규칙 제17조(해양시설의 신고 등): 제1항 소유자는 별지 제12호서식 신고서(전자문서 포함)에 설치명세서, 도면·위치도(2만5천분의 1 지형도), 해양오염방지관리인 임명확인서·해양시설오염비상계획서(별표 1 제1호 해당 시설 한정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출 / 제2항 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항 '중요한 내용의 변경'은 ① 소유자 변경(사업장 명칭·대표자 변경 포함) ② 설치 장소 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부(항 번호 미확정) / 제5항 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급. 최초신고의 기한을 정한 문언은 조문 요약에서 확인되지 않음(해양수산부 FAQ·구 국토해양부 안내만 '사업개시 후 30일 이내'). 별지 제12호서식(해양시설 (최초, 변경)신고서): 처리기간 '최초 7일·변경 5일'이 서식에 기재된 것으로 확인(정부24 안내, 인터뷰이 진술 일치). 서식의 구비서류란·담당공무원 확인사항란(행정정보 공동이용) 유무는 미확인. 「행정기본법」 제34조(수리 여부에 따른 신고의 효력): 법률에 신고의 수리가 필요하다고 명시되어 있는 경우(행정기관의 내부 업무 처리 절차로서 수리를 규정한 경우는 제외)에는 행정청이 수리하여야 효력이 발생. 「행정절차법」 제40조제2항: 형식상 요건을 갖춘 신고는 접수기관에 도달된 때 의무 이행, 제3항·제4항 보완 요구 후 미보완 시 반려. 「민원 처리에 관한 법률」 제19조: 처리기간이 5일 이하면 '시간' 단위, 6일 이상이면 '일' 단위(첫날 산입)로 계산하고 토요일·공휴일은 산입하지 않음. 같은 법 시행령 제24조(보완 요구)·제25조(기간 내 미보완 시 이유를 밝혀 반려). 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(구 국토해양부 안내도 '적정여부 검토, 수리' 단계를 둠). 법 문언과 실무상 법적 성격이 다르다. ② 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어, 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조상 시간 단위로 계산되는 등 적용 기준이 불명확하다. ③ 행정청이 어디까지 심사하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ④ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항(보완 요구)·민원처리법상 접수 원칙과 어긋난다. ⑤ 시행령의 위임 조문(구판)은 지방해양수산청장에게 신고의 '접수'만 위임하는 문언인데 시행규칙 제17조제2항은 지방해양수산청장이 신고증명서를 발급하도록 하여, 수리·증명서 발급 권한의 소재가 법령 간에 정합하지 않을 가능성이 있다(현행 원문 확인 필요).
-[논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
-[개정 방향] ① (법률) 법 제33조에 "해양수산부장관은 제1항에 따른 신고 또는 변경신고를 받은 날부터 ○일 이내에 신고수리 여부를 신고인에게 통지하여야 한다"와 "그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 그 기간이 끝난 날의 다음 날에 수리한 것으로 본다"는 수리 통지·수리 간주 조항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 7~9와 연계). ② (부령) 시행규칙 제17조제2항에 처리기한을 본문으로 옮기고, 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시한다. ③ (시행령) 위임 조문의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항과 맞춘다. 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
-[유의] 인터뷰이는 수리형 유지에 찬성하면서 제도 완화에는 신중한 입장("사회재난 같은 것들이 더 중요시되는 상황에서 제도를 갑자기 완화해 버리면 문제가 발생하지 않을까")이므로, 수리 간주는 '수리형 유지 + 기한 명확화'로 설명하는 것이 입법사실과 부합한다. [교차확인] 연번 4(포항청)·연번 5(부산청)와 동일 쟁점. 법 제33조·시행규칙 제17조·별지 제12호서식·시행령 위임 조문의 현행 원문을 받아 재대조해야 하며, 법률에 수리 문언이 이미 있다면 본 행의 결론이 바뀐다. 처리기한을 법률에 둘 때 민원처리법 제19조의 계산 방식(토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다.</t>
+          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
+[논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
+[개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 8~10과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
+[유의] 인터뷰이는 수리형 유지에 찬성하면서 제도 완화에는 신중한 입장("사회재난 같은 것들이 더 중요시되는 상황에서 제도를 갑자기 완화해 버리면 문제가 발생하지 않을까")이므로, 수리 간주는 '수리형 유지 + 기한 명확화'로 설명하는 것이 입법사실과 부합한다. [교차확인] 연번 4(포항청)·연번 5(부산청)와 동일 쟁점. 처리기한을 정할 때 민원처리법 제19조의 계산 방식(5일 이하 시간 단위, 토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다. 국가관리연안항 해양시설은 법 제33조제1항제1호에서 해양수산부장관 관할로 두면서 시행령 제94조제6항제2호가 접수를 시·도지사에게 위임하고 있어 ③ 정비 시 함께 검토한다.</t>
         </is>
       </c>
     </row>
@@ -661,13 +662,14 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>「해양환경관리법」 제33조제1항·제2항(원문 미대조)
-시행규칙 제17조제1항·제2항·제5항(원문 미대조)
-시행규칙 별지 제12호서식(처리기간 최초 7일·변경 5일 기재, 원문 미대조)
-시행령 권한 위임 조문(구판 제94조제4항: 신고·변경신고의 '접수' 위임, 현행 조문 번호 미확인)
+          <t>「해양환경관리법」 제33조제1항·제2항
+법 제38조제3항(오염물질저장시설 신고의 수리 여부 통지, 2023.10.24. 신설 — 비교 조문)
+시행령 제94조제4항제2호·제2호의3, 제6항제2호(권한 위임)
+시행규칙 제17조제1항·제2항·제4항·제5항
+시행규칙 별지 제12호서식(처리기간 최초 7일·변경 5일, 처리절차)·별지 제14호서식(신고증명서)
 「행정기본법」 제34조
-「행정절차법」 제40조
-「민원 처리에 관한 법률」 제19조, 같은 법 시행령 제24조·제25조</t>
+「행정절차법」 제40조제2항~제4항
+「민원 처리에 관한 법률」 제19조·제22조제1항, 같은 법 시행령 제24조·제25조</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -678,11 +680,11 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 그 시설을 임대하는 경우에는 시설임차인)는 해양수산부장관에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(변경신고 후단은 2017.3.21. 개정으로 도입, 법률 번호는 2차 자료 간 상충). 제2항: 신고내용·변경신고 대상·신고 절차 등은 해양수산부령으로 정함. 현행 법률 판본: 2차 자료에 법률 제21065호(2025.10.1. 시행, 타법개정), 2026.1.2. 시행 판본, 법률 제21416호(2026.2.27. 일부개정)가 함께 검색되어 최신 공포번호·시행일은 원문으로 확정 필요. 수리 여부, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 법률에서 확인되지 않음. 시행규칙 제17조(해양시설의 신고 등): 제1항 소유자는 별지 제12호서식 신고서(전자문서 포함)에 설치명세서, 도면·위치도(2만5천분의 1 지형도), 해양오염방지관리인 임명확인서·해양시설오염비상계획서(별표 1 제1호 해당 시설 한정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출 / 제2항 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항 '중요한 내용의 변경'은 ① 소유자 변경(사업장 명칭·대표자 변경 포함) ② 설치 장소 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부(항 번호 미확정) / 제5항 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급. 최초신고의 기한을 정한 문언은 조문 요약에서 확인되지 않음(해양수산부 FAQ·구 국토해양부 안내만 '사업개시 후 30일 이내'). 별지 제12호서식(해양시설 (최초, 변경)신고서): 처리기간 '최초 7일·변경 5일'이 서식에 기재된 것으로 확인(정부24 안내, 인터뷰이 진술 일치). 서식의 구비서류란·담당공무원 확인사항란(행정정보 공동이용) 유무는 미확인. 「행정기본법」 제34조(수리 여부에 따른 신고의 효력): 법률에 신고의 수리가 필요하다고 명시되어 있는 경우(행정기관의 내부 업무 처리 절차로서 수리를 규정한 경우는 제외)에는 행정청이 수리하여야 효력이 발생. 「행정절차법」 제40조제2항: 형식상 요건을 갖춘 신고는 접수기관에 도달된 때 의무 이행, 제3항·제4항 보완 요구 후 미보완 시 반려. 「민원 처리에 관한 법률」 제19조: 처리기간이 5일 이하면 '시간' 단위, 6일 이상이면 '일' 단위(첫날 산입)로 계산하고 토요일·공휴일은 산입하지 않음. 같은 법 시행령 제24조(보완 요구)·제25조(기간 내 미보완 시 이유를 밝혀 반려). 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(구 국토해양부 안내도 '적정여부 검토, 수리' 단계를 둠). 법 문언과 실무상 법적 성격이 다르다. ② 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어, 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조상 시간 단위로 계산되는 등 적용 기준이 불명확하다. ③ 행정청이 어디까지 심사하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ④ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항(보완 요구)·민원처리법상 접수 원칙과 어긋난다. ⑤ 시행령의 위임 조문(구판)은 지방해양수산청장에게 신고의 '접수'만 위임하는 문언인데 시행규칙 제17조제2항은 지방해양수산청장이 신고증명서를 발급하도록 하여, 수리·증명서 발급 권한의 소재가 법령 간에 정합하지 않을 가능성이 있다(현행 원문 확인 필요).
-[논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
-[개정 방향] ① (법률) 법 제33조에 "해양수산부장관은 제1항에 따른 신고 또는 변경신고를 받은 날부터 ○일 이내에 신고수리 여부를 신고인에게 통지하여야 한다"와 "그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 그 기간이 끝난 날의 다음 날에 수리한 것으로 본다"는 수리 통지·수리 간주 조항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 7~9와 연계). ② (부령) 시행규칙 제17조제2항에 처리기한을 본문으로 옮기고, 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시한다. ③ (시행령) 위임 조문의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항과 맞춘다. 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
-[유의] 인터뷰이는 처음에는 규정 추가가 "굳이 그럴 필요까지는 없을 것 같"다고 했다가 명시하면 더 명확해진다고 답했고, 자기완결형 전환에는 부정적(사전 검토 과정 상실 우려)이므로 수리형 유지를 전제로 한 정비임을 밝혀야 한다. 인터뷰이가 '민원처리법상 법정 처리기간 7일'이라고 한 부분은 민원처리법이 아니라 서식 기재 기간으로 보이며, 검토메모에 차이를 기록했다. [교차확인] 연번 3(군산청)·연번 5(부산청)와 동일 쟁점. 법 제33조·시행규칙 제17조·별지 제12호서식·시행령 위임 조문의 현행 원문을 받아 재대조해야 하며, 법률에 수리 문언이 이미 있다면 본 행의 결론이 바뀐다. 처리기한을 법률에 둘 때 민원처리법 제19조의 계산 방식(토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다.</t>
+          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
+[논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
+[개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 8~10과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
+[유의] 인터뷰이는 처음에는 규정 추가가 "굳이 그럴 필요까지는 없을 것 같"다고 했다가 명시하면 더 명확해진다고 답했고, 자기완결형 전환에는 부정적(사전 검토 과정 상실 우려)이므로 수리형 유지를 전제로 한 정비임을 밝혀야 한다. 인터뷰이가 '민원처리법상 법정 처리기간 7일'이라고 한 부분은 민원처리법이 아니라 별지 제12호서식 기재 기간으로 확인되며, 검토메모에 차이를 기록했다. [교차확인] 연번 3(군산청)·연번 5(부산청)와 동일 쟁점. 처리기한을 정할 때 민원처리법 제19조의 계산 방식(5일 이하 시간 단위, 토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다. 국가관리연안항 해양시설은 법 제33조제1항제1호에서 해양수산부장관 관할로 두면서 시행령 제94조제6항제2호가 접수를 시·도지사에게 위임하고 있어 ③ 정비 시 함께 검토한다.</t>
         </is>
       </c>
     </row>
@@ -708,13 +710,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>「해양환경관리법」 제33조제1항·제2항(원문 미대조)
-시행규칙 제17조제1항·제2항·제5항(원문 미대조)
-시행규칙 별지 제12호서식(처리기간 최초 7일·변경 5일 기재, 원문 미대조)
-시행령 권한 위임 조문(구판 제94조제4항: 신고·변경신고의 '접수' 위임, 현행 조문 번호 미확인)
+          <t>「해양환경관리법」 제33조제1항·제2항
+법 제38조제3항(오염물질저장시설 신고의 수리 여부 통지, 2023.10.24. 신설 — 비교 조문)
+시행령 제94조제4항제2호·제2호의3, 제6항제2호(권한 위임)
+시행규칙 제17조제1항·제2항·제4항·제5항
+시행규칙 별지 제12호서식(처리기간 최초 7일·변경 5일, 처리절차)·별지 제14호서식(신고증명서)
 「행정기본법」 제34조
-「행정절차법」 제40조
-「민원 처리에 관한 법률」 제19조, 같은 법 시행령 제24조·제25조</t>
+「행정절차법」 제40조제2항~제4항
+「민원 처리에 관한 법률」 제19조·제22조제1항, 같은 법 시행령 제24조·제25조</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -725,15 +728,15 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 그 시설을 임대하는 경우에는 시설임차인)는 해양수산부장관에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(변경신고 후단은 2017.3.21. 개정으로 도입, 법률 번호는 2차 자료 간 상충). 제2항: 신고내용·변경신고 대상·신고 절차 등은 해양수산부령으로 정함. 현행 법률 판본: 2차 자료에 법률 제21065호(2025.10.1. 시행, 타법개정), 2026.1.2. 시행 판본, 법률 제21416호(2026.2.27. 일부개정)가 함께 검색되어 최신 공포번호·시행일은 원문으로 확정 필요. 수리 여부, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 법률에서 확인되지 않음. 시행규칙 제17조(해양시설의 신고 등): 제1항 소유자는 별지 제12호서식 신고서(전자문서 포함)에 설치명세서, 도면·위치도(2만5천분의 1 지형도), 해양오염방지관리인 임명확인서·해양시설오염비상계획서(별표 1 제1호 해당 시설 한정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출 / 제2항 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항 '중요한 내용의 변경'은 ① 소유자 변경(사업장 명칭·대표자 변경 포함) ② 설치 장소 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부(항 번호 미확정) / 제5항 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급. 최초신고의 기한을 정한 문언은 조문 요약에서 확인되지 않음(해양수산부 FAQ·구 국토해양부 안내만 '사업개시 후 30일 이내'). 별지 제12호서식(해양시설 (최초, 변경)신고서): 처리기간 '최초 7일·변경 5일'이 서식에 기재된 것으로 확인(정부24 안내, 인터뷰이 진술 일치). 서식의 구비서류란·담당공무원 확인사항란(행정정보 공동이용) 유무는 미확인. 「행정기본법」 제34조(수리 여부에 따른 신고의 효력): 법률에 신고의 수리가 필요하다고 명시되어 있는 경우(행정기관의 내부 업무 처리 절차로서 수리를 규정한 경우는 제외)에는 행정청이 수리하여야 효력이 발생. 「행정절차법」 제40조제2항: 형식상 요건을 갖춘 신고는 접수기관에 도달된 때 의무 이행, 제3항·제4항 보완 요구 후 미보완 시 반려. 「민원 처리에 관한 법률」 제19조: 처리기간이 5일 이하면 '시간' 단위, 6일 이상이면 '일' 단위(첫날 산입)로 계산하고 토요일·공휴일은 산입하지 않음. 같은 법 시행령 제24조(보완 요구)·제25조(기간 내 미보완 시 이유를 밝혀 반려). 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(구 국토해양부 안내도 '적정여부 검토, 수리' 단계를 둠). 법 문언과 실무상 법적 성격이 다르다. ② 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어, 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조상 시간 단위로 계산되는 등 적용 기준이 불명확하다. ③ 행정청이 어디까지 심사하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ④ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항(보완 요구)·민원처리법상 접수 원칙과 어긋난다. ⑤ 시행령의 위임 조문(구판)은 지방해양수산청장에게 신고의 '접수'만 위임하는 문언인데 시행규칙 제17조제2항은 지방해양수산청장이 신고증명서를 발급하도록 하여, 수리·증명서 발급 권한의 소재가 법령 간에 정합하지 않을 가능성이 있다(현행 원문 확인 필요).
-[논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
-[개정 방향] ① (법률) 법 제33조에 "해양수산부장관은 제1항에 따른 신고 또는 변경신고를 받은 날부터 ○일 이내에 신고수리 여부를 신고인에게 통지하여야 한다"와 "그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 그 기간이 끝난 날의 다음 날에 수리한 것으로 본다"는 수리 통지·수리 간주 조항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 7~9와 연계). ② (부령) 시행규칙 제17조제2항에 처리기한을 본문으로 옮기고, 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시한다. ③ (시행령) 위임 조문의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항과 맞춘다. 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
-[유의] 부산청의 '서류 완비 전 미접수' 운영은 법령 정비와 별개로 민원처리법·행정절차법에 따라 바로잡을 운영 사항이며(검토메모), 본 행은 그 원인이 되는 법적 성격·절차 규정의 공백을 다룬다. 인터뷰이는 효력에 대해 "신고를 했기 때문에 과태료를 받지 않는다는 정도"라고 하여 수리의 실익이 크지 않다고 보므로, 경미 사항의 수리 불요 전환(연번 7)과 함께 설계해야 한다. [교차확인] 연번 3(군산청)·연번 4(포항청)와 동일 쟁점. 법 제33조·시행규칙 제17조·별지 제12호서식·시행령 위임 조문의 현행 원문을 받아 재대조해야 하며, 법률에 수리 문언이 이미 있다면 본 행의 결론이 바뀐다. 처리기한을 법률에 둘 때 민원처리법 제19조의 계산 방식(토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="357" customHeight="1">
+          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
+[논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
+[개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 8~10과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
+[유의] 부산청의 '서류 완비 전 미접수' 운영은 법령 정비와 별개로 민원처리법 제22조제1항·행정절차법 제40조제3항에 따라 바로잡을 운영 사항이며(검토메모), 본 행은 그 원인이 되는 법적 성격·절차 규정의 공백을 다룬다. 인터뷰이는 효력에 대해 "신고를 했기 때문에 과태료를 받지 않는다는 정도"라고 하여 수리의 실익이 크지 않다고 보므로, 경미 사항의 수리 불요 전환(연번 8)과 함께 설계해야 한다. [교차확인] 연번 3(군산청)·연번 4(포항청)와 동일 쟁점. 처리기한을 정할 때 민원처리법 제19조의 계산 방식(5일 이하 시간 단위, 토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다. 국가관리연안항 해양시설은 법 제33조제1항제1호에서 해양수산부장관 관할로 두면서 시행령 제94조제6항제2호가 접수를 시·도지사에게 위임하고 있어 ③ 정비 시 함께 검토한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="330" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -755,10 +758,10 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>「해양환경관리법」 제33조제1항(신고 의무, 기한 문언 없음)
-법 제132조제2항제2호(원문 미대조)
-시행령 제98조·별표 19(과태료 개별기준, 개정 2023.4.18.)
-시행규칙 제17조제1항(최초신고 기한 문언 유무 미확인)·변경신고 30일(항 번호 미확정)
+          <t>「해양환경관리법」 제33조제1항(신고 의무, 기한 문언 없음)·제2항
+법 제132조제2항제2호
+시행령 제98조·별표 19 너목(개정 2026.6.30.)
+시행규칙 제17조제1항(최초신고: 기한 없음)·제4항(변경신고: 30일)·제7항(폐업신고: 기한 없음)
 「질서위반행위규제법」 제6조(질서위반행위 법정주의)</t>
         </is>
       </c>
@@ -770,15 +773,15 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않는다. 시행규칙 제17조는 변경신고(변경사유 발생일부터 30일 이내)와 폐업신고(폐업일부터 30일 이내, 2차 자료)에는 기한을 두지만, 최초신고의 기한은 조문 요약에서 확인되지 않는다(해양수산부 FAQ와 구 국토해양부 안내는 '사업개시 후 30일 이내'라고 하나 근거 조문이 제시되지 않음). 법 제132조제2항제2호(2011년 판본 기준 '500만원 이하의 과태료', 현행 상한 원문 미대조) → 시행령 제98조·별표 19(개정 2023.4.18.) 개별기준: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 일반기준: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 해당하면 2분의 1 범위에서 감경 가능. 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 최초신고의 의무 발생 시점(설치 완료, 사용 개시, 공사 중 일부 가동)이 법령에 없어, 담당자가 "완공이 되어야 한다"고 안내하고 민원인은 "신고 시점이 법에 나와 있지 않다"고 이의를 제기한다. 배수관처럼 수 킬로미터 공정 중 일부만 가동되는 시설은 신고 시점을 특정할 수 없다. ② 반면 변경신고에는 30일 기한이 있어, 같은 조항의 과태료(별표 19: 신고·변경신고 미이행 동일 250만원)가 변경신고에는 적용 시점이 분명하고 최초신고에는 불분명한 비대칭이 생긴다. ③ 서류 미비로 수리되지 않은 경우를 "최초 신고를 지연한 상황"으로 보고 과태료를 검토하는데, 기한이 없으니 지연 여부 자체를 판단할 수 없어 부과가 "애매"해진다.
-[논거] 과태료의 구성요건인 '신고를 하지 아니한' 상태는 신고 의무의 이행 기한이 있어야 성립 시점이 확정된다. 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 못하며(「질서위반행위규제법」 제6조) 그 요건은 명확해야 하므로, 기한 없는 의무에 제재를 결부한 현행 구조는 명확성 원칙에 비추어 정비 대상이다. 행정안내(FAQ)로 30일을 운용하는 것은 법령 근거 없이 제재 요건을 보충하는 것이어서 해석·지침으로 해결할 수 없다. 인터뷰이(군산)의 '상식 사항' 견해는 민원인이 실제로 다투고 있다는 같은 인터뷰이의 진술과 상충한다.
-[개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항에 같은 기산점을 반영하고, 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 개별기준에서 최초신고 미이행·변경신고 미이행·기한 경과 후 신고를 구분한다(연번 7~9와 연계). 최소 정비안은 ②이나, 의무의 내용(기한)은 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
-[유의] 시행규칙 제17조에 최초신고 기한이 이미 있는지 원문으로 반드시 확인해야 한다. 있다면 본 행은 '안내 부족' 운영 문제로 바뀌어 검토메모로 이동한다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 6 참조). 인터뷰이가 말한 '변경 신고 처리 기한'은 맥락상 신고인의 변경신고 기한(30일)을 가리키는 것으로 보이며, 행정청의 처리기간(5일)과 구분하여 검토메모에 기록했다. [교차확인] 연번 6(군산청 인터뷰)과 동일 쟁점(단, 군산청 인터뷰이는 입법 불요 의견).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="357" customHeight="1">
+          <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않으며, 제2항은 신고내용·절차를 부령에 위임한다. 시행규칙 제17조제1항은 "법 제33조제1항 전단에 따라 해양시설의 신고를 하려는 경우에는" 최초신고서를 제출하도록 할 뿐 기한을 두지 않고, 제4항은 변경신고에만 '변경사유가 발생한 날부터 30일 이내'를 두며, 제7항의 폐업신고에도 기한이 없다(해양수산부 FAQ와 구 국토해양부 안내의 '최초신고는 사업개시 후 30일 이내', '폐업신고는 폐업일부터 30일 이내'는 현행 조문에 근거가 없다). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 「질서위반행위규제법」 제6조: 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 최초신고의 의무 발생 시점(설치 완료, 사용 개시, 공사 중 일부 가동)이 법령에 없어, 담당자가 "완공이 되어야 한다"고 안내하고 민원인은 "신고 시점이 법에 나와 있지 않다"고 이의를 제기한다. 배수관처럼 수 킬로미터 공정 중 일부만 가동되는 시설은 신고 시점을 특정할 수 없다. ② 변경신고에는 30일 기한이 있어, 같은 호의 과태료(별표 19 너목: 신고·변경신고 미이행 동일 250만원)가 변경신고에는 적용 시점이 분명하고 최초신고에는 불분명한 비대칭이 생긴다. ③ 서류 미비로 증명서가 발급되지 않은 경우를 "최초 신고를 지연한 상황"으로 보고 과태료를 검토하는데, 기한이 없으니 지연 여부 자체를 판단할 수 없어 부과가 "애매"해진다. ④ 행정안내(FAQ)가 조문에 없는 30일 기한을 안내하고 있어, 수범자는 안내문을, 담당자는 조문을 기준으로 삼는 불일치가 있다.
+[논거] 과태료의 구성요건인 '신고를 하지 아니한' 상태는 신고 의무의 이행 기한이 있어야 성립 시점이 확정된다. 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 못하며(「질서위반행위규제법」 제6조) 그 요건은 명확해야 하므로, 기한 없는 의무에 제재를 결부한 현행 구조는 명확성 원칙에 비추어 정비 대상이다. 행정안내로 30일을 운용하는 것은 법령 근거 없이 제재 요건을 보충하는 것이어서 해석·지침으로 해결할 수 없다. 인터뷰이(군산)의 '상식 사항' 견해는 민원인이 실제로 다투고 있다는 같은 인터뷰이의 진술과 상충한다.
+[개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항·제7항에 같은 기산점을 반영하고(폐업신고 기한도 함께), 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행·변경신고 미이행·기한 경과 후 신고로 구분한다(연번 8~10과 연계). 최소 정비안은 ②이나, 의무의 내용(기한)이 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
+[유의] 원문 확인 결과 시행규칙 제17조에 최초신고 기한이 없음이 확정되어 본 행은 본표에 유지한다(1차 보고의 '안내 부족 문제로 바뀔 수 있음' 유보는 해소). 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 7 참조). 인터뷰이가 말한 '변경 신고 처리 기한'은 맥락상 신고인의 변경신고 기한(시행규칙 제17조제4항, 30일)을 가리키는 것으로 보이며, 행정청의 처리기간(서식 5일)과 구분하여 검토메모에 기록했다. [교차확인] 연번 7(군산청 인터뷰)과 동일 쟁점(단, 군산청 인터뷰이는 입법 불요 의견).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="330" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -800,10 +803,10 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>「해양환경관리법」 제33조제1항(신고 의무, 기한 문언 없음)
-법 제132조제2항제2호(원문 미대조)
-시행령 제98조·별표 19(과태료 개별기준, 개정 2023.4.18.)
-시행규칙 제17조제1항(최초신고 기한 문언 유무 미확인)·변경신고 30일(항 번호 미확정)
+          <t>「해양환경관리법」 제33조제1항(신고 의무, 기한 문언 없음)·제2항
+법 제132조제2항제2호
+시행령 제98조·별표 19 너목(개정 2026.6.30.)
+시행규칙 제17조제1항(최초신고: 기한 없음)·제4항(변경신고: 30일)·제7항(폐업신고: 기한 없음)
 「질서위반행위규제법」 제6조(질서위반행위 법정주의)</t>
         </is>
       </c>
@@ -815,15 +818,15 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않는다. 시행규칙 제17조는 변경신고(변경사유 발생일부터 30일 이내)와 폐업신고(폐업일부터 30일 이내, 2차 자료)에는 기한을 두지만, 최초신고의 기한은 조문 요약에서 확인되지 않는다(해양수산부 FAQ와 구 국토해양부 안내는 '사업개시 후 30일 이내'라고 하나 근거 조문이 제시되지 않음). 법 제132조제2항제2호(2011년 판본 기준 '500만원 이하의 과태료', 현행 상한 원문 미대조) → 시행령 제98조·별표 19(개정 2023.4.18.) 개별기준: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 일반기준: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 해당하면 2분의 1 범위에서 감경 가능. 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 최초신고의 의무 발생 시점(설치 완료, 사용 개시, 공사 중 일부 가동)이 법령에 없어, 담당자가 "완공이 되어야 한다"고 안내하고 민원인은 "신고 시점이 법에 나와 있지 않다"고 이의를 제기한다. 배수관처럼 수 킬로미터 공정 중 일부만 가동되는 시설은 신고 시점을 특정할 수 없다. ② 반면 변경신고에는 30일 기한이 있어, 같은 조항의 과태료(별표 19: 신고·변경신고 미이행 동일 250만원)가 변경신고에는 적용 시점이 분명하고 최초신고에는 불분명한 비대칭이 생긴다. ③ 서류 미비로 수리되지 않은 경우를 "최초 신고를 지연한 상황"으로 보고 과태료를 검토하는데, 기한이 없으니 지연 여부 자체를 판단할 수 없어 부과가 "애매"해진다.
-[논거] 과태료의 구성요건인 '신고를 하지 아니한' 상태는 신고 의무의 이행 기한이 있어야 성립 시점이 확정된다. 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 못하며(「질서위반행위규제법」 제6조) 그 요건은 명확해야 하므로, 기한 없는 의무에 제재를 결부한 현행 구조는 명확성 원칙에 비추어 정비 대상이다. 행정안내(FAQ)로 30일을 운용하는 것은 법령 근거 없이 제재 요건을 보충하는 것이어서 해석·지침으로 해결할 수 없다. 인터뷰이(군산)의 '상식 사항' 견해는 민원인이 실제로 다투고 있다는 같은 인터뷰이의 진술과 상충한다.
-[개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항에 같은 기산점을 반영하고, 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 개별기준에서 최초신고 미이행·변경신고 미이행·기한 경과 후 신고를 구분한다(연번 7~9와 연계). 최소 정비안은 ②이나, 의무의 내용(기한)은 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
-[유의] 시행규칙 제17조에 최초신고 기한이 이미 있는지 원문으로 반드시 확인해야 한다. 있다면 본 행은 '안내 부족' 운영 문제로 바뀌어 검토메모로 이동한다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 6 참조). 본 행의 인터뷰이는 입법 불요 의견이므로 입법사실로는 '시점 불명확으로 인한 민원 혼선'만 사용하고, 개정 필요성의 판단 근거는 연번 6(부산청)의 과태료 집행 문제에 둔다. [교차확인] 연번 6(부산청 인터뷰)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="343.5" customHeight="1">
+          <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않으며, 제2항은 신고내용·절차를 부령에 위임한다. 시행규칙 제17조제1항은 "법 제33조제1항 전단에 따라 해양시설의 신고를 하려는 경우에는" 최초신고서를 제출하도록 할 뿐 기한을 두지 않고, 제4항은 변경신고에만 '변경사유가 발생한 날부터 30일 이내'를 두며, 제7항의 폐업신고에도 기한이 없다(해양수산부 FAQ와 구 국토해양부 안내의 '최초신고는 사업개시 후 30일 이내', '폐업신고는 폐업일부터 30일 이내'는 현행 조문에 근거가 없다). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 「질서위반행위규제법」 제6조: 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 최초신고의 의무 발생 시점(설치 완료, 사용 개시, 공사 중 일부 가동)이 법령에 없어, 담당자가 "완공이 되어야 한다"고 안내하고 민원인은 "신고 시점이 법에 나와 있지 않다"고 이의를 제기한다. 배수관처럼 수 킬로미터 공정 중 일부만 가동되는 시설은 신고 시점을 특정할 수 없다. ② 변경신고에는 30일 기한이 있어, 같은 호의 과태료(별표 19 너목: 신고·변경신고 미이행 동일 250만원)가 변경신고에는 적용 시점이 분명하고 최초신고에는 불분명한 비대칭이 생긴다. ③ 서류 미비로 증명서가 발급되지 않은 경우를 "최초 신고를 지연한 상황"으로 보고 과태료를 검토하는데, 기한이 없으니 지연 여부 자체를 판단할 수 없어 부과가 "애매"해진다. ④ 행정안내(FAQ)가 조문에 없는 30일 기한을 안내하고 있어, 수범자는 안내문을, 담당자는 조문을 기준으로 삼는 불일치가 있다.
+[논거] 과태료의 구성요건인 '신고를 하지 아니한' 상태는 신고 의무의 이행 기한이 있어야 성립 시점이 확정된다. 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 못하며(「질서위반행위규제법」 제6조) 그 요건은 명확해야 하므로, 기한 없는 의무에 제재를 결부한 현행 구조는 명확성 원칙에 비추어 정비 대상이다. 행정안내로 30일을 운용하는 것은 법령 근거 없이 제재 요건을 보충하는 것이어서 해석·지침으로 해결할 수 없다. 인터뷰이(군산)의 '상식 사항' 견해는 민원인이 실제로 다투고 있다는 같은 인터뷰이의 진술과 상충한다.
+[개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항·제7항에 같은 기산점을 반영하고(폐업신고 기한도 함께), 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행·변경신고 미이행·기한 경과 후 신고로 구분한다(연번 8~10과 연계). 최소 정비안은 ②이나, 의무의 내용(기한)이 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
+[유의] 원문 확인 결과 시행규칙 제17조에 최초신고 기한이 없음이 확정되어 본 행은 본표에 유지한다(1차 보고의 '안내 부족 문제로 바뀔 수 있음' 유보는 해소). 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 7 참조). 본 행의 인터뷰이는 입법 불요 의견이므로 입법사실로는 '시점 불명확으로 인한 민원 혼선'만 사용하고, 개정 필요성의 판단 근거는 연번 6(부산청)의 과태료 집행 문제에 둔다. [교차확인] 연번 6(부산청 인터뷰)과 동일 쟁점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="330" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -846,11 +849,12 @@
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>「해양환경관리법」 제33조제1항 후단('해양수산부령으로 정하는 중요한 내용'의 변경신고)·제2항
-법 제132조제2항제2호(원문 미대조)
-시행령 제98조·별표 19(신고·변경신고 미이행 동일 250만원, 일반기준 2분의 1 감경)
-시행규칙 제17조제3항(소유자 변경에 사업장 명칭·대표자 변경 포함)·제5항(변경신고 시 신고증명서 발급)·변경신고 30일(항 번호 미확정)
+법 제132조제2항제2호(500만원 이하)·제4항제6호의7(관리인 임명 신고 미이행, 100만원 이하 — 비교)
+시행령 제98조·별표 19 너목(250만원)·더목(30만원 — 비교), 일반기준 나목·다목
+시행규칙 제17조제3항제1호(소유자 변경에 사업장 명칭·대표자 변경 포함)·제4항(30일)·제5항(변경신고 시 신고증명서 발급)
+시행규칙 제19조제4항제1호·제5항(대표자 변경 시 비상계획서 변경검인 — 비교)
 「행정기본법」 제34조
-「민원 처리에 관한 법률」 제10조제3항(공동이용으로 확인 가능한 서류 요구 금지)</t>
+「민원 처리에 관한 법률」 제10조제3항제3호</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -861,15 +865,15 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 소유자 변경(사업장 명칭·대표자 변경 포함) ② 설치 장소 변경 ③ 규모의 50% 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고, 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제17조제5항). 법 제132조제2항제2호(2011년 판본 기준 '500만원 이하의 과태료', 현행 상한 원문 미대조) → 시행령 제98조·별표 19(개정 2023.4.18.) 개별기준: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 일반기준: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 해당하면 2분의 1 범위에서 감경 가능. 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장).
+          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 같은 별표에서 관리인 임명 신고 미이행은 30만원이다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항제3호), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장). ⑤ 300㎘ 이상 저장시설은 대표자 변경 하나에 해양수산부(변경신고)와 해양경찰(변경검인) 두 절차를 각각 30일 내에 밟아야 하는 중복이 있다.
 [논거] 하위법령이 법률의 위임 문언('중요한 내용')을 넘어 형식적 사항까지 수리형 변경신고 대상으로 정한 것은 위임 범위의 문제이고, 경미한 변경에 중대한 변경과 같은 절차·제재를 결부한 것은 비례원칙(필요 최소한의 절차·제재)에 어긋난다. 과태료 금액은 시행령 별표 19가 정하므로 금액 차등은 시행령 개정으로 가능하고, 신고 유형의 구분은 「행정기본법」 제34조에 따라 법률에서 수리 필요 여부를 명시해야 완결된다. 규제를 완화·세분하는 방향이므로 규제 신설이 아니다.
-[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항에서 대표자·명칭 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 10·11과 연계). ③ (시행령) 별표 19 개별기준을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
-[유의] 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준에 이미 질서위반행위규제법 시행령 제2조의2 사유 등이 있어 검토메모로 분리했다. 별표 19 금액 단위(만원)와 현행 법 제132조제2항 상한은 원문 미대조. [교차확인] 연번 8(군산청)·연번 9(포항청)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="357" customHeight="1">
+[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 11·12와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
+[유의] 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준 나목·다목(2026.6.30. 소상공인 감경 신설)에 이미 있어 검토메모로 분리했다. ⑤의 해경 변경검인 중복은 법령 대조 중 발견한 사항으로 인터뷰이가 직접 제기하지 않았으므로 연계 정비로만 제시하며, 해양경찰청과 협의가 필요하다. [교차확인] 연번 9(군산청)·연번 10(포항청)과 동일 쟁점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="330" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -892,11 +896,12 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>「해양환경관리법」 제33조제1항 후단('해양수산부령으로 정하는 중요한 내용'의 변경신고)·제2항
-법 제132조제2항제2호(원문 미대조)
-시행령 제98조·별표 19(신고·변경신고 미이행 동일 250만원, 일반기준 2분의 1 감경)
-시행규칙 제17조제3항(소유자 변경에 사업장 명칭·대표자 변경 포함)·제5항(변경신고 시 신고증명서 발급)·변경신고 30일(항 번호 미확정)
+법 제132조제2항제2호(500만원 이하)·제4항제6호의7(관리인 임명 신고 미이행, 100만원 이하 — 비교)
+시행령 제98조·별표 19 너목(250만원)·더목(30만원 — 비교), 일반기준 나목·다목
+시행규칙 제17조제3항제1호(소유자 변경에 사업장 명칭·대표자 변경 포함)·제4항(30일)·제5항(변경신고 시 신고증명서 발급)
+시행규칙 제19조제4항제1호·제5항(대표자 변경 시 비상계획서 변경검인 — 비교)
 「행정기본법」 제34조
-「민원 처리에 관한 법률」 제10조제3항(공동이용으로 확인 가능한 서류 요구 금지)</t>
+「민원 처리에 관한 법률」 제10조제3항제3호</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -907,15 +912,15 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 소유자 변경(사업장 명칭·대표자 변경 포함) ② 설치 장소 변경 ③ 규모의 50% 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고, 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제17조제5항). 법 제132조제2항제2호(2011년 판본 기준 '500만원 이하의 과태료', 현행 상한 원문 미대조) → 시행령 제98조·별표 19(개정 2023.4.18.) 개별기준: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 일반기준: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 해당하면 2분의 1 범위에서 감경 가능. 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장).
+          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 같은 별표에서 관리인 임명 신고 미이행은 30만원이다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항제3호), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장). ⑤ 300㎘ 이상 저장시설은 대표자 변경 하나에 해양수산부(변경신고)와 해양경찰(변경검인) 두 절차를 각각 30일 내에 밟아야 하는 중복이 있다.
 [논거] 하위법령이 법률의 위임 문언('중요한 내용')을 넘어 형식적 사항까지 수리형 변경신고 대상으로 정한 것은 위임 범위의 문제이고, 경미한 변경에 중대한 변경과 같은 절차·제재를 결부한 것은 비례원칙(필요 최소한의 절차·제재)에 어긋난다. 과태료 금액은 시행령 별표 19가 정하므로 금액 차등은 시행령 개정으로 가능하고, 신고 유형의 구분은 「행정기본법」 제34조에 따라 법률에서 수리 필요 여부를 명시해야 완결된다. 규제를 완화·세분하는 방향이므로 규제 신설이 아니다.
-[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항에서 대표자·명칭 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 10·11과 연계). ③ (시행령) 별표 19 개별기준을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
-[유의] 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준에 이미 질서위반행위규제법 시행령 제2조의2 사유 등이 있어 검토메모로 분리했다. 별표 19 금액 단위(만원)와 현행 법 제132조제2항 상한은 원문 미대조. 군산청 인터뷰이는 과태료 금액에 대해서는 언급하지 않았으므로 본 행의 입법사실은 '소유자 변경의 수리 불요 전환'에 한정된다. [교차확인] 연번 7(부산청)·연번 9(포항청)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="357" customHeight="1">
+[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 11·12와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
+[유의] 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준 나목·다목(2026.6.30. 소상공인 감경 신설)에 이미 있어 검토메모로 분리했다. ⑤의 해경 변경검인 중복은 법령 대조 중 발견한 사항으로 인터뷰이가 직접 제기하지 않았으므로 연계 정비로만 제시하며, 해양경찰청과 협의가 필요하다. 군산청 인터뷰이는 과태료 금액에 대해서는 언급하지 않았으므로 본 행의 입법사실은 '소유자 변경의 수리 불요 전환'에 한정된다. [교차확인] 연번 8(부산청)·연번 10(포항청)과 동일 쟁점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="330" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -938,11 +943,12 @@
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>「해양환경관리법」 제33조제1항 후단('해양수산부령으로 정하는 중요한 내용'의 변경신고)·제2항
-법 제132조제2항제2호(원문 미대조)
-시행령 제98조·별표 19(신고·변경신고 미이행 동일 250만원, 일반기준 2분의 1 감경)
-시행규칙 제17조제3항(소유자 변경에 사업장 명칭·대표자 변경 포함)·제5항(변경신고 시 신고증명서 발급)·변경신고 30일(항 번호 미확정)
+법 제132조제2항제2호(500만원 이하)·제4항제6호의7(관리인 임명 신고 미이행, 100만원 이하 — 비교)
+시행령 제98조·별표 19 너목(250만원)·더목(30만원 — 비교), 일반기준 나목·다목
+시행규칙 제17조제3항제1호(소유자 변경에 사업장 명칭·대표자 변경 포함)·제4항(30일)·제5항(변경신고 시 신고증명서 발급)
+시행규칙 제19조제4항제1호·제5항(대표자 변경 시 비상계획서 변경검인 — 비교)
 「행정기본법」 제34조
-「민원 처리에 관한 법률」 제10조제3항(공동이용으로 확인 가능한 서류 요구 금지)</t>
+「민원 처리에 관한 법률」 제10조제3항제3호</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -953,15 +959,15 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 소유자 변경(사업장 명칭·대표자 변경 포함) ② 설치 장소 변경 ③ 규모의 50% 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고, 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제17조제5항). 법 제132조제2항제2호(2011년 판본 기준 '500만원 이하의 과태료', 현행 상한 원문 미대조) → 시행령 제98조·별표 19(개정 2023.4.18.) 개별기준: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 일반기준: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 해당하면 2분의 1 범위에서 감경 가능. 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장).
+          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 같은 별표에서 관리인 임명 신고 미이행은 30만원이다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항제3호), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장). ⑤ 300㎘ 이상 저장시설은 대표자 변경 하나에 해양수산부(변경신고)와 해양경찰(변경검인) 두 절차를 각각 30일 내에 밟아야 하는 중복이 있다.
 [논거] 하위법령이 법률의 위임 문언('중요한 내용')을 넘어 형식적 사항까지 수리형 변경신고 대상으로 정한 것은 위임 범위의 문제이고, 경미한 변경에 중대한 변경과 같은 절차·제재를 결부한 것은 비례원칙(필요 최소한의 절차·제재)에 어긋난다. 과태료 금액은 시행령 별표 19가 정하므로 금액 차등은 시행령 개정으로 가능하고, 신고 유형의 구분은 「행정기본법」 제34조에 따라 법률에서 수리 필요 여부를 명시해야 완결된다. 규제를 완화·세분하는 방향이므로 규제 신설이 아니다.
-[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항에서 대표자·명칭 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 10·11과 연계). ③ (시행령) 별표 19 개별기준을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
-[유의] 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준에 이미 질서위반행위규제법 시행령 제2조의2 사유 등이 있어 검토메모로 분리했다. 별표 19 금액 단위(만원)와 현행 법 제132조제2항 상한은 원문 미대조. 포항청 인터뷰이의 '신고 의무 유지' 의견을 반영하여 본 행의 개정 방향은 의무 존치 + 절차 간소화로 한정된다. [교차확인] 연번 7(부산청)·연번 8(군산청)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="384" customHeight="1">
+[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 11·12와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
+[유의] 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준 나목·다목(2026.6.30. 소상공인 감경 신설)에 이미 있어 검토메모로 분리했다. ⑤의 해경 변경검인 중복은 법령 대조 중 발견한 사항으로 인터뷰이가 직접 제기하지 않았으므로 연계 정비로만 제시하며, 해양경찰청과 협의가 필요하다. 포항청 인터뷰이의 '신고 의무 유지' 의견을 반영하여 본 행의 개정 방향은 의무 존치 + 절차 간소화로 한정된다. [교차확인] 연번 8(부산청)·연번 9(군산청)와 동일 쟁점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="316.5" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -983,11 +989,10 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 제17조제1항(최초신고 첨부서류)·변경신고 첨부서류('변경내용을 증명하는 서류', 항 번호 미확정)
-시행규칙 제17조의 행정정보 공동이용 확인 조항(대상 서류 미확인, 항 번호 미확정)
-시행규칙 별지 제12호서식(구비서류란·담당공무원 확인사항란 유무 미확인, 원문 미대조)
-「민원 처리에 관한 법률」 제10조제1항·제3항
-「전자정부법」 제36조제1항(원문 미대조; 시행규칙 제17조는 구 제21조제1항을 인용)
+          <t>시행규칙 제17조제1항(최초신고 첨부서류)·제4항제2호('변경내용을 증명하는 서류')
+시행규칙 별지 제12호서식(개정 2024.6.28.: 신고인란에 상호·대표자·생년월일 기재, 첨부서류란만 있고 담당 공무원 확인사항란·공동이용 동의란 없음, 첨부서류 2번의 근거 조문을 '법 제32조'로 오기)
+「민원 처리에 관한 법률」 제10조제1항·제3항제3호·제7항
+「전자정부법」 제36조제1항
 「해양환경관리법」 제33조제1항(신고 주체: 소유자·설치운영자·임차인)</t>
         </is>
       </c>
@@ -999,15 +1004,15 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서, 도면·위치도, (해당 시설에 한해) 해양오염방지관리인 임명확인서·해양시설오염비상계획서이고, 변경신고는 신고증명서와 '변경내용을 증명하는 서류'이다(2차 자료 기준). 사업자등록증·법인 등기사항증명서는 첨부서류 목록에 없다. 한편 시행규칙 제17조에는 "해당 공무원은 「전자정부법」 제21조제1항에 따른 행정정보의 공동이용을 통하여 첨부서류에 대한 정보를 확인하여야 한다"는 조항이 있는 것으로 확인되나(인천지방해양수산청 안내 전재, 2008~2010년 개정 표기), 어느 첨부서류를 공동이용으로 확인하는지와 별지 제12호서식에 담당 공무원 확인사항란·동의란이 있는지는 확인되지 않았다. 인용된 「전자정부법」 제21조제1항은 구 조문 번호로서 현행 공동이용 근거 조문(제36조제1항)과 다르다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항은 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있는 사항은 서류 제출을 요구하지 말고 담당자가 직접 확인하도록 한다. 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 신고 주체(법 제33조제1항: 소유자·설치운영자·임차인)와 변경신고 대상(대표자 변경)의 확인은 신고 처리에 실제로 필요한 심사 사항인데, 법령이 이를 확인할 서류나 확인 방법을 정하지 않아 부산청은 사업자등록증·법인 등기부등본을 법정 외 서류로 요구하고, 포항청도 "확인 목적"으로 제출받는다. 이는 민원처리법 제10조제1항에 반하는 상태가 법령 공백 때문에 상시화된 것이다. ② 두 서류 모두 행정정보 공동이용 대상(행정기관 발급 증명)이므로 제10조제3항에 따라 담당자가 직접 확인해야 하고, 시행규칙 제17조도 공동이용 확인 의무를 두고 있으나 그 대상 서류가 법인 등기사항증명서·사업자등록증명을 포함하는지 문언상 특정되지 않아(미확인) 조항이 실무에서 작동하지 않는다(부산청은 공동이용 시스템을 이용한 적이 없음). 시행규칙이 인용하는 「전자정부법」 제21조제1항은 조문 번호 개편 전의 것이어서 인용 조문도 정비 대상이다. ③ 변경신고의 '변경내용을 증명하는 서류'는 무엇을 내야 하는지 특정되지 않아 가장 빈번한 보완 사유가 된다.
-[논거] 지침 6절의 구분에 따르면 신고 주체의 동일성·대표자 확인이라는 실질 심사의 근거는 법률(제33조제1항의 신고 주체 규정)에 있고, 이를 확인할 서류·방법이 하위법령에 빠져 있는 유형이다. 법령에 없는 서류를 요구하는 실무를 법령에 맞추는 방법은 두 가지인데, 서류 요구를 중단하는 것은 심사를 불가능하게 하므로, 실무상 이미 요구되는 확인 사항을 서식의 '담당 공무원 확인사항'으로 옮겨 공동이용으로 대체하는 것이 민원처리법 제10조제3항·전자정부법 제36조의 취지에 맞는 정비이다. 신고인에게 새로운 서류를 추가하는 것이 아니라 기존 요구 서류를 공동이용으로 대체하는 것이므로 규제 신설이 아니다.
-[개정 방향] ① (부령) 시행규칙 제17조의 공동이용 확인 조항을 "신고인이 법인인 경우 법인 등기사항증명서, 사업자인 경우 사업자등록증명은 담당 공무원이 「전자정부법」 제36조제1항에 따른 행정정보의 공동이용을 통하여 확인하여야 하며, 신고인이 확인에 동의하지 아니하는 경우에는 그 서류를 첨부하게 한다"로 대상 서류를 특정하여 고치고, 인용 조문을 현행 「전자정부법」 제36조제1항으로 바로잡는다. ② (부령) 별지 제12호서식에 '담당 공무원 확인사항'란과 '행정정보 공동이용 동의서'란을 신설한다. ③ (부령) 변경신고의 '변경내용을 증명하는 서류'를 변경 사유별로 예시한다(대표자 변경: 법인 등기사항증명서로 확인, 장소·규모 변경: 변경된 설치명세서·도면). 모두 부령만으로 가능하다.
-[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 하며, 시행규칙 제17조의 공동이용 확인 조항이 이미 법인 등기사항증명서·사업자등록증명을 대상으로 특정하고 있거나 서식에 확인사항란이 있다면, 본 행은 소관 부령 자체를 위반한 운영 문제(기준 1)로 검토메모로 이동하고 인용 조문 정비만 부수 정비로 남긴다. 확인 조항의 대상 서류와 서식 원문을 받아 재판단해야 하며, 채팅 보고의 판단 필요 항목에 올렸다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. 행정안전부(공동이용 대상 정보)와 협의가 필요하다. [교차확인] 연번 11(포항청 인터뷰)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="397.5" customHeight="1">
+          <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서·도면·위치도, (해당 시설에 한해) 법 제36조에 따른 관리인 임명확인서, 법 제35조에 따른 해양시설오염비상계획서이고, 제4항의 변경신고 첨부서류는 신고증명서와 '변경내용을 증명하는 서류'이다. 사업자등록증·법인 등기사항증명서는 어디에도 없고, 제17조에는 행정정보 공동이용으로 확인한다는 조항이 없다. 별지 제12호서식(개정 2024.6.28.)은 신고인란에 상호(사업장 명칭)·성명(대표자)·생년월일을 적게 하면서 첨부서류란만 두고 담당 공무원 확인사항란과 행정정보 공동이용 동의란이 없으며, 첨부서류 2번의 근거 조문을 '「해양환경관리법」 제32조에 따른 해양오염방지관리인'(선박 관리인 조문)으로 적어 제17조제1항제2호(법 제36조)와 어긋난다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항제3호는 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있으면 서류 제출을 요구할 수 없고 담당자가 직접 확인·처리하도록 하며, 제7항은 변경·갱신 신청 시 기제출 서류의 재요구를 금지한다. 「전자정부법」 제36조제1항은 다른 행정기관으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있으면 같은 정보를 따로 수집하지 못하게 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 신고 주체(법 제33조제1항: 소유자·설치운영자·임차인)의 동일성과 변경신고 대상인 대표자 변경(시행규칙 제17조제3항제1호)의 확인은 신고 처리에 실제로 필요한 심사 사항인데, 법령이 이를 확인할 서류나 확인 방법을 정하지 않아 부산청은 사업자등록증·법인 등기부등본을 법정 외 서류로 요구하고, 포항청도 "확인 목적"으로 제출받는다. 이는 민원처리법 제10조제1항에 반하는 상태가 법령 공백 때문에 상시화된 것이다. ② 두 서류 모두 행정정보 공동이용으로 확인 가능한 행정기관 발급 정보이므로 제10조제3항제3호에 따라 담당자가 직접 확인해야 하나, 시행규칙과 서식 어디에도 확인 조항·확인란·동의란이 없어 공동이용 절차를 시작할 근거가 없다(부산청은 공동이용 시스템을 이용한 적이 없음). ③ 변경신고의 '변경내용을 증명하는 서류'는 무엇을 내야 하는지 특정되지 않아 가장 빈번한 보완 사유가 된다. ④ 서식의 근거 조문 오기(제32조)는 신고인이 선박 관리인 조문을 찾게 하는 정합성 흠결이다.
+[논거] 신고 주체의 동일성·대표자 확인이라는 실질 확인의 근거는 법률(제33조제1항의 신고 주체 규정)과 부령(제17조제3항제1호)에 있고, 이를 확인할 서류·방법만 하위법령에 빠져 있는 유형이다. 법령에 없는 서류를 요구하는 실무를 법령에 맞추는 방법은 두 가지인데, 서류 요구를 중단하는 것은 확인을 불가능하게 하므로, 실무상 이미 요구되는 확인 사항을 서식의 '담당 공무원 확인사항'으로 옮겨 공동이용으로 대체하는 것이 민원처리법 제10조제3항·전자정부법 제36조제1항의 취지에 맞는 정비이다. 신고인에게 새로운 서류를 추가하는 것이 아니라 기존 요구 서류를 공동이용으로 대체하는 것이므로 규제 신설이 아니다.
+[개정 방향] ① (부령) 시행규칙 제17조에 "지방해양수산청장 또는 시·도지사는 「전자정부법」 제36조제1항에 따른 행정정보의 공동이용을 통하여 신고인의 법인 등기사항증명서(법인인 경우) 또는 사업자등록증명을 확인하여야 하며, 신고인이 확인에 동의하지 아니하는 경우에는 그 서류를 첨부하게 하여야 한다"는 확인 조항을 신설한다. ② (부령) 별지 제12호서식에 '담당 공무원 확인사항'란과 '행정정보 공동이용 동의서'란을 신설하고, 첨부서류 2번의 근거 조문을 '법 제36조'로 바로잡는다. ③ (부령) 제17조제4항제2호의 '변경내용을 증명하는 서류'를 변경 사유별로 예시한다(대표자·명칭 변경: ①의 공동이용 확인으로 갈음, 장소·규모 변경: 변경된 설치명세서·도면). 모두 부령만으로 가능하다.
+[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 한다. 1차 보고에서 '시행규칙 제17조에 공동이용 확인 조항이 있는 것으로 확인된다'고 적었던 서술은 지방해양수산청 안내문에 전재된 구 조문을 현행으로 오인한 것이며, 현행 제17조 원문에는 그러한 조항이 없음을 확인하여 바로잡았다. 법인 등기사항증명서·사업자등록증명이 지방해양수산청의 공동이용 대상 정보인지는 행정안전부(행정정보공동이용센터) 확인이 필요하며, 대상이 아니면 ①은 '신고인이 첨부' 방식으로만 정비한다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. [교차확인] 연번 12(포항청 인터뷰)와 동일 쟁점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="330" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1029,11 +1034,10 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 제17조제1항(최초신고 첨부서류)·변경신고 첨부서류('변경내용을 증명하는 서류', 항 번호 미확정)
-시행규칙 제17조의 행정정보 공동이용 확인 조항(대상 서류 미확인, 항 번호 미확정)
-시행규칙 별지 제12호서식(구비서류란·담당공무원 확인사항란 유무 미확인, 원문 미대조)
-「민원 처리에 관한 법률」 제10조제1항·제3항
-「전자정부법」 제36조제1항(원문 미대조; 시행규칙 제17조는 구 제21조제1항을 인용)
+          <t>시행규칙 제17조제1항(최초신고 첨부서류)·제4항제2호('변경내용을 증명하는 서류')
+시행규칙 별지 제12호서식(개정 2024.6.28.: 신고인란에 상호·대표자·생년월일 기재, 첨부서류란만 있고 담당 공무원 확인사항란·공동이용 동의란 없음, 첨부서류 2번의 근거 조문을 '법 제32조'로 오기)
+「민원 처리에 관한 법률」 제10조제1항·제3항제3호·제7항
+「전자정부법」 제36조제1항
 「해양환경관리법」 제33조제1항(신고 주체: 소유자·설치운영자·임차인)</t>
         </is>
       </c>
@@ -1045,11 +1049,11 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서, 도면·위치도, (해당 시설에 한해) 해양오염방지관리인 임명확인서·해양시설오염비상계획서이고, 변경신고는 신고증명서와 '변경내용을 증명하는 서류'이다(2차 자료 기준). 사업자등록증·법인 등기사항증명서는 첨부서류 목록에 없다. 한편 시행규칙 제17조에는 "해당 공무원은 「전자정부법」 제21조제1항에 따른 행정정보의 공동이용을 통하여 첨부서류에 대한 정보를 확인하여야 한다"는 조항이 있는 것으로 확인되나(인천지방해양수산청 안내 전재, 2008~2010년 개정 표기), 어느 첨부서류를 공동이용으로 확인하는지와 별지 제12호서식에 담당 공무원 확인사항란·동의란이 있는지는 확인되지 않았다. 인용된 「전자정부법」 제21조제1항은 구 조문 번호로서 현행 공동이용 근거 조문(제36조제1항)과 다르다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항은 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있는 사항은 서류 제출을 요구하지 말고 담당자가 직접 확인하도록 한다. 근거 자료의 확인 상태: 이 작업 환경에서는 국가법령정보센터 등 법령DB 직접 접속이 차단되어 모든 조문을 웹 검색 요약(2차 자료)으로만 확인함. 본 행의 조문 번호·항·문언은 복수 출처가 일치하는 범위에서 기재했으며 원문 대조 전까지 잠정임(참조 시트·notes/evidence_log.md 참조).
-[문제점] ① 신고 주체(법 제33조제1항: 소유자·설치운영자·임차인)와 변경신고 대상(대표자 변경)의 확인은 신고 처리에 실제로 필요한 심사 사항인데, 법령이 이를 확인할 서류나 확인 방법을 정하지 않아 부산청은 사업자등록증·법인 등기부등본을 법정 외 서류로 요구하고, 포항청도 "확인 목적"으로 제출받는다. 이는 민원처리법 제10조제1항에 반하는 상태가 법령 공백 때문에 상시화된 것이다. ② 두 서류 모두 행정정보 공동이용 대상(행정기관 발급 증명)이므로 제10조제3항에 따라 담당자가 직접 확인해야 하고, 시행규칙 제17조도 공동이용 확인 의무를 두고 있으나 그 대상 서류가 법인 등기사항증명서·사업자등록증명을 포함하는지 문언상 특정되지 않아(미확인) 조항이 실무에서 작동하지 않는다(부산청은 공동이용 시스템을 이용한 적이 없음). 시행규칙이 인용하는 「전자정부법」 제21조제1항은 조문 번호 개편 전의 것이어서 인용 조문도 정비 대상이다. ③ 변경신고의 '변경내용을 증명하는 서류'는 무엇을 내야 하는지 특정되지 않아 가장 빈번한 보완 사유가 된다.
-[논거] 지침 6절의 구분에 따르면 신고 주체의 동일성·대표자 확인이라는 실질 심사의 근거는 법률(제33조제1항의 신고 주체 규정)에 있고, 이를 확인할 서류·방법이 하위법령에 빠져 있는 유형이다. 법령에 없는 서류를 요구하는 실무를 법령에 맞추는 방법은 두 가지인데, 서류 요구를 중단하는 것은 심사를 불가능하게 하므로, 실무상 이미 요구되는 확인 사항을 서식의 '담당 공무원 확인사항'으로 옮겨 공동이용으로 대체하는 것이 민원처리법 제10조제3항·전자정부법 제36조의 취지에 맞는 정비이다. 신고인에게 새로운 서류를 추가하는 것이 아니라 기존 요구 서류를 공동이용으로 대체하는 것이므로 규제 신설이 아니다.
-[개정 방향] ① (부령) 시행규칙 제17조의 공동이용 확인 조항을 "신고인이 법인인 경우 법인 등기사항증명서, 사업자인 경우 사업자등록증명은 담당 공무원이 「전자정부법」 제36조제1항에 따른 행정정보의 공동이용을 통하여 확인하여야 하며, 신고인이 확인에 동의하지 아니하는 경우에는 그 서류를 첨부하게 한다"로 대상 서류를 특정하여 고치고, 인용 조문을 현행 「전자정부법」 제36조제1항으로 바로잡는다. ② (부령) 별지 제12호서식에 '담당 공무원 확인사항'란과 '행정정보 공동이용 동의서'란을 신설한다. ③ (부령) 변경신고의 '변경내용을 증명하는 서류'를 변경 사유별로 예시한다(대표자 변경: 법인 등기사항증명서로 확인, 장소·규모 변경: 변경된 설치명세서·도면). 모두 부령만으로 가능하다.
-[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 하며, 시행규칙 제17조의 공동이용 확인 조항이 이미 법인 등기사항증명서·사업자등록증명을 대상으로 특정하고 있거나 서식에 확인사항란이 있다면, 본 행은 소관 부령 자체를 위반한 운영 문제(기준 1)로 검토메모로 이동하고 인용 조문 정비만 부수 정비로 남긴다. 확인 조항의 대상 서류와 서식 원문을 받아 재판단해야 하며, 채팅 보고의 판단 필요 항목에 올렸다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. 행정안전부(공동이용 대상 정보)와 협의가 필요하다. 포항청 인터뷰이의 발언은 면담자의 유도 질문('실제로는 다 제출받으시는 거네요')에 대한 짧은 긍정이므로 입법사실의 강도는 부산청보다 약하다. [교차확인] 연번 10(부산청 인터뷰)과 동일 쟁점.</t>
+          <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서·도면·위치도, (해당 시설에 한해) 법 제36조에 따른 관리인 임명확인서, 법 제35조에 따른 해양시설오염비상계획서이고, 제4항의 변경신고 첨부서류는 신고증명서와 '변경내용을 증명하는 서류'이다. 사업자등록증·법인 등기사항증명서는 어디에도 없고, 제17조에는 행정정보 공동이용으로 확인한다는 조항이 없다. 별지 제12호서식(개정 2024.6.28.)은 신고인란에 상호(사업장 명칭)·성명(대표자)·생년월일을 적게 하면서 첨부서류란만 두고 담당 공무원 확인사항란과 행정정보 공동이용 동의란이 없으며, 첨부서류 2번의 근거 조문을 '「해양환경관리법」 제32조에 따른 해양오염방지관리인'(선박 관리인 조문)으로 적어 제17조제1항제2호(법 제36조)와 어긋난다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항제3호는 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있으면 서류 제출을 요구할 수 없고 담당자가 직접 확인·처리하도록 하며, 제7항은 변경·갱신 신청 시 기제출 서류의 재요구를 금지한다. 「전자정부법」 제36조제1항은 다른 행정기관으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있으면 같은 정보를 따로 수집하지 못하게 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+[문제점] ① 신고 주체(법 제33조제1항: 소유자·설치운영자·임차인)의 동일성과 변경신고 대상인 대표자 변경(시행규칙 제17조제3항제1호)의 확인은 신고 처리에 실제로 필요한 심사 사항인데, 법령이 이를 확인할 서류나 확인 방법을 정하지 않아 부산청은 사업자등록증·법인 등기부등본을 법정 외 서류로 요구하고, 포항청도 "확인 목적"으로 제출받는다. 이는 민원처리법 제10조제1항에 반하는 상태가 법령 공백 때문에 상시화된 것이다. ② 두 서류 모두 행정정보 공동이용으로 확인 가능한 행정기관 발급 정보이므로 제10조제3항제3호에 따라 담당자가 직접 확인해야 하나, 시행규칙과 서식 어디에도 확인 조항·확인란·동의란이 없어 공동이용 절차를 시작할 근거가 없다(부산청은 공동이용 시스템을 이용한 적이 없음). ③ 변경신고의 '변경내용을 증명하는 서류'는 무엇을 내야 하는지 특정되지 않아 가장 빈번한 보완 사유가 된다. ④ 서식의 근거 조문 오기(제32조)는 신고인이 선박 관리인 조문을 찾게 하는 정합성 흠결이다.
+[논거] 신고 주체의 동일성·대표자 확인이라는 실질 확인의 근거는 법률(제33조제1항의 신고 주체 규정)과 부령(제17조제3항제1호)에 있고, 이를 확인할 서류·방법만 하위법령에 빠져 있는 유형이다. 법령에 없는 서류를 요구하는 실무를 법령에 맞추는 방법은 두 가지인데, 서류 요구를 중단하는 것은 확인을 불가능하게 하므로, 실무상 이미 요구되는 확인 사항을 서식의 '담당 공무원 확인사항'으로 옮겨 공동이용으로 대체하는 것이 민원처리법 제10조제3항·전자정부법 제36조제1항의 취지에 맞는 정비이다. 신고인에게 새로운 서류를 추가하는 것이 아니라 기존 요구 서류를 공동이용으로 대체하는 것이므로 규제 신설이 아니다.
+[개정 방향] ① (부령) 시행규칙 제17조에 "지방해양수산청장 또는 시·도지사는 「전자정부법」 제36조제1항에 따른 행정정보의 공동이용을 통하여 신고인의 법인 등기사항증명서(법인인 경우) 또는 사업자등록증명을 확인하여야 하며, 신고인이 확인에 동의하지 아니하는 경우에는 그 서류를 첨부하게 하여야 한다"는 확인 조항을 신설한다. ② (부령) 별지 제12호서식에 '담당 공무원 확인사항'란과 '행정정보 공동이용 동의서'란을 신설하고, 첨부서류 2번의 근거 조문을 '법 제36조'로 바로잡는다. ③ (부령) 제17조제4항제2호의 '변경내용을 증명하는 서류'를 변경 사유별로 예시한다(대표자·명칭 변경: ①의 공동이용 확인으로 갈음, 장소·규모 변경: 변경된 설치명세서·도면). 모두 부령만으로 가능하다.
+[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 한다. 1차 보고에서 '시행규칙 제17조에 공동이용 확인 조항이 있는 것으로 확인된다'고 적었던 서술은 지방해양수산청 안내문에 전재된 구 조문을 현행으로 오인한 것이며, 현행 제17조 원문에는 그러한 조항이 없음을 확인하여 바로잡았다. 법인 등기사항증명서·사업자등록증명이 지방해양수산청의 공동이용 대상 정보인지는 행정안전부(행정정보공동이용센터) 확인이 필요하며, 대상이 아니면 ①은 '신고인이 첨부' 방식으로만 정비한다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. 포항청 인터뷰이의 발언은 면담자의 유도 질문('실제로는 다 제출받으시는 거네요')에 대한 짧은 긍정이므로 입법사실의 강도는 부산청보다 약하다. [교차확인] 연번 11(부산청 인터뷰)과 동일 쟁점.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>「행정절차법」 제40조제3항·제4항(보완 요구 → 미보완 시 이유를 밝혀 되돌려 보냄), 「민원 처리에 관한 법률 시행령」 제24조(보완 요구)·제25조(기간 내 미보완 시 반려)에 일반 근거가 이미 있음(2차 자료 확인).</t>
+          <t>「행정절차법」 제40조제3항(보완 요구)·제4항(미보완 시 이유를 밝혀 되돌려 보냄), 「민원 처리에 관한 법률」 제22조제1항(보완 요구), 같은 법 시행령 제24조(보완 절차·기간 연장 2회)·제25조제1항(기간 내 미보완 시 반려)에 일반 근거가 있음(원문 확인).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1142,7 +1146,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>민원처리법·행정절차법 제40조제3항은 접수 후 보완 요구를 예정함. 부산청 운영은 법령 근거 없이 접수를 보류하는 것으로 일반법과 다름.</t>
+          <t>민원처리법 제22조제1항은 '접수한 민원문서'에 보완을 요구하도록 하고, 행정절차법 제40조제3항도 제출된 신고서에 대한 보완 요구를 예정함. 부산청 운영은 법령 근거 없이 접수를 보류하는 것으로 일반법과 다름.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1167,7 +1171,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>민원처리법에는 개별 민원의 처리기간(7일)이 없고, 처리기간은 별지 제12호서식(최초 7일·변경 5일, 정부24 안내 일치)에 기재된 것으로 확인됨. 조호영의 '민원처리법상 7일'은 서식 기재 기간으로 보임(발언은 고치지 않음).</t>
+          <t>민원처리법에는 개별 민원의 처리기간(7일)이 없고, 처리기간은 별지 제12호서식 상단에 '(최초)7일 (변경)5일'로 기재된 것을 원문으로 확인함. 조호영의 '민원처리법상 7일'은 서식 기재 기간으로 보임(발언은 고치지 않음). 폐업신고서(별지 제16호)는 처리기간 3일.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1176,7 +1180,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="46.5" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -1192,7 +1196,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>맥락(과태료 부과)상 행정청의 처리기간(서식 5일)이 아니라 신고인의 변경신고 기한(시행규칙, 변경사유 발생일부터 30일)을 가리키는 것으로 해석됨.</t>
+          <t>맥락(과태료 부과)상 행정청의 처리기간(서식 5일)이 아니라 신고인의 변경신고 기한(시행규칙 제17조제4항, 변경사유 발생일부터 30일)을 가리키는 것으로 해석됨. 최초신고 기한이 없음은 제17조제1항 원문으로 확인.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1201,301 +1205,351 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="46.5" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>안전점검 후 시정조치·유지보수 명령 근거 부재(군산)</t>
+          <t>해양수산부 FAQ·지방청 안내의 '최초신고 사업개시 후 30일, 폐업신고 폐업일부터 30일'(2차 자료)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>신재민: "해양시설을 안전점검해야 한다는 규정이 너무 모호하게 되어 있습니다. 시정조치를 하게끔 하는 규정도 없고" / "후속 조치를 할 수 있는 조항이 부재하다는 것"</t>
+          <t>(인터뷰이 발언 없음 — 법령 대조 중 발견)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>법 제36조의2(소유자 안전점검 의무·결과 보고·장관 직접 점검), 시행규칙 제20조의3(대상·중대한 결함, 2018.5.1. 신설)까지 확인. 시정명령·사용제한 조항은 확인되지 않음(현행 원문 미대조).</t>
+          <t>현행 시행규칙 제17조제1항(최초신고)·제7항(폐업신고)에는 기한이 없음(원문 확인). 안내문의 30일은 조문 근거가 없는 것으로 확인됨.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>기준 3(신고제도 범위 밖, 시정명령 신설은 규제 신설·규제영향분석 대상). 제외. 사후관리 과제로 별도 검토 권고.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="73.5" customHeight="1">
+          <t>입법사실 없음. 본표 연번 6·7의 [현행 규정]·[유의]에 반영. 해양수산부에 안내문 수정 필요성을 전달할 사항.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100.5" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>위험도에 따른 신고·등록·허가 차등, 대상 재정립(포항·군산·부산)</t>
+          <t>안전점검 후 시정조치·유지보수 명령 근거 부재(군산)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>조호영: "허가 정도로 하고 그 아래는 등록, 그 아래는 신고로 차등을 두는 정도는 괜찮다고 생각합니다." / 신재민: "대상을 다시 정립해서, 규제를 한다면 규제의 정도를 바꾸는 게 더 바람직" / 윤혜림: "해양오염 위험도의 기준을 정하는 것 자체가 다소 어려울 것 같습니다."</t>
+          <t>신재민: "해양시설을 안전점검해야 한다는 규정이 너무 모호하게 되어 있습니다. 시정조치를 하게끔 하는 규정도 없고" / "후속 조치를 할 수 있는 조항이 부재하다는 것"</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>허가·등록 도입은 규제 신설·강화. 저위험 시설의 접수형 간소화 부분만 본표 연번 7~9(경미 변경의 수리 불요화)에 반영.</t>
+          <t>법 제36조의2(제1항 소유자 안전점검 의무, 제2항 중대한 결함 시 지체 없이 보고(2017.10.31.), 제3항 3년 보관, 제4항 장관 직접 점검, 제5항 대행), 시행규칙 제20조의3(대상: 별표 1 제1호 가목·나목, 중대한 결함: 침하·균열, 해저송유관·호스·저장탱크·돌핀·원유송유용 부이 결함). 시정명령·사용제한 조항 없음(원문 확인). 같은 법 제38조의3은 오염물질저장시설에 대해서는 개선·운영정지·폐쇄명령을 둠.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>기준 3. 제외(간소화 부분만 본표 반영).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="87" customHeight="1">
+          <t>기준 3(신고제도 범위 밖, 시정명령 신설은 규제 신설·규제영향분석 대상). 제외. 제38조의3과의 균형 차원에서 사후관리 과제로 별도 검토 권고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="73.5" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>공유수면 점용·사용허가와의 연계·의제, 서류 공유</t>
+          <t>위험도에 따른 신고·등록·허가 차등, 대상 재정립(포항·군산·부산)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>조호영: "의제 규정이 없으면, 법률이 개정되지 않는 이상 그건 어려울 것 같습니다." / "의제가 되면 따로 신고를 안 받아도 되니까 좋을 것 같습니다." / 신재민: "아직 거기까지 구축하기에는 다른 우선순위가 더 많다고 생각합니다." / 윤혜림: "두 절차를 무조건 연계하는 것은 적절하지 않은 것 같고"</t>
+          <t>조호영: "허가 정도로 하고 그 아래는 등록, 그 아래는 신고로 차등을 두는 정도는 괜찮다고 생각합니다." / 신재민: "대상을 다시 정립해서, 규제를 한다면 규제의 정도를 바꾸는 게 더 바람직" / 윤혜림: "해양오염 위험도의 기준을 정하는 것 자체가 다소 어려울 것 같습니다."</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>공유수면법과 해양환경관리법은 목적·대상이 달라 허가 대상이 반드시 해양시설은 아님(윤혜림). 의제 신설은 정책 판단 사항이며 인터뷰이 의견이 갈림.</t>
+          <t>허가·등록 도입은 규제 신설·강화. 저위험 시설의 접수형 간소화 부분만 본표 연번 8~10(경미 변경의 수리 불요화)에 반영.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>기준 2·3(정책 사항, 면담자 질문에서 파생). 제외. 다만 민원처리법 제10조제4항(변경·갱신 시 기제출 서류 재요구 금지)은 같은 법령 내 절차에만 적용되므로 법령 간 서류 공유는 입법 사항임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46.5" customHeight="1">
+          <t>기준 3. 제외(간소화 부분만 본표 반영).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="87" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>온라인(정부24) 접수 미실시, 방문·우편·메일·팩스 접수</t>
+          <t>공유수면 점용·사용허가와의 연계·의제, 서류 공유</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>신재민: "방문이요." / 조호영: "해양환경관리법에도 온라인으로만 받아야 한다는 규정은 없어서" / 윤혜림: "메일, 방문, 팩스 등을 통해 제출받고 있습니다."</t>
+          <t>조호영: "의제 규정이 없으면, 법률이 개정되지 않는 이상 그건 어려울 것 같습니다." / "의제가 되면 따로 신고를 안 받아도 되니까 좋을 것 같습니다." / 신재민: "아직 거기까지 구축하기에는 다른 우선순위가 더 많다고 생각합니다." / 윤혜림: "두 절차를 무조건 연계하는 것은 적절하지 않은 것 같고"</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 제17조제1항은 '전자문서로 된 신고서를 포함'하여 이미 전자 신고를 허용(2차 자료). 정부24 안내도 인터넷 신청 가능으로 표시.</t>
+          <t>공유수면법과 해양환경관리법은 목적·대상이 달라 허가 대상이 반드시 해양시설은 아님(윤혜림). 의제 신설은 정책 판단 사항이며 인터뷰이 의견이 갈림. 민원처리법 제10조제7항(변경·갱신 시 기제출 서류 재요구 금지)은 같은 민원의 변경·갱신에만 적용되므로 법령 간 서류 공유는 입법 사항.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>기준 1(시스템·운영 문제). 제외.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+          <t>기준 2·3(정책 사항, 면담자 질문에서 파생). 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46.5" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>해양시설 신고(해수부)와 해양오염방지관리인 임명 신고·비상계획서 검인(해경)의 이원화</t>
+          <t>온라인(정부24) 접수 미실시, 방문·우편·메일·팩스 접수</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>조호영: "해경에서 먼저 자체 방제계획서 승인을 받고, 그걸 첨부해서 저희한테 신고하게끔 법이 되어 있습니다." / 윤혜림: "분리되어 있는 현재 구조에서 해경 쪽이 관리하는 것이 오히려 효율적일 수도 있다고 생각합니다."</t>
+          <t>신재민: "방문이요." / 조호영: "해양환경관리법에도 온라인으로만 받아야 한다는 규정은 없어서" / 윤혜림: "메일, 방문, 팩스 등을 통해 제출받고 있습니다."</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>법 제35조(해양시설오염비상계획서, 해양경찰청장 검인), 제36조(해양오염방지관리인 임명 신고, 해양경찰청장), 시행규칙 제17조제1항(임명확인서·비상계획서 첨부). 법령상 설계된 절차이며 인터뷰이는 통합 필요성을 주장하지 않음.</t>
+          <t>시행규칙 제17조제1항·제4항은 '전자문서로 된 신고서를 포함'하여 이미 전자 신고를 허용(원문 확인).</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>기준 2·3(정책·조직 사항). 제외. 조호영이 말한 '자체 방제계획서'는 법령상 '해양시설오염비상계획서'로 보임(발언은 고치지 않음).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>기준 1(시스템·운영 문제). 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="87" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>최초신고 시 해양오염방지관리인 교육 이수 요구로 인한 보완(부산)</t>
+          <t>해양시설 신고(해수부)와 해양오염방지관리인 임명 신고·비상계획서 검인(해경)의 이원화</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>윤혜림: "해양오염방지교육을 이수해야 하는데 이 부분이 누락되거나 교육 신청이 늦어지는 경우가 많아, 최초 신고 시 바로 접수되는 경우는 없고 서류 보완을 요청하는 경우가 많습니다."</t>
+          <t>조호영: "해경에서 먼저 자체 방제계획서 승인을 받고, 그걸 첨부해서 저희한테 신고하게끔 법이 되어 있습니다." / 윤혜림: "분리되어 있는 현재 구조에서 해경 쪽이 관리하는 것이 오히려 효율적일 수도 있다고 생각합니다."</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>법 제36조(관리인 임명)·제121조(관리인 교육), 시행규칙 제17조제1항(임명확인서 첨부, 별표 1 제1호 시설 한정)에 근거가 있는 것으로 확인(2차 자료). 교육 이수는 관리인 자격 요건이므로 첨부서류 요구는 법령 범위 안.</t>
+          <t>법 제35조(해양시설오염비상계획서, 해양경찰청장 검인), 제36조제2항(관리인 임명 신고, 해양경찰청장), 시행령 제94조제5항제1호·제1호의2(해양경찰서장에게 검인·임명신고 수리 위임), 시행규칙 제17조제1항제2호·제3호(임명확인서·비상계획서 첨부), 제19조제3항(해양경찰서장에게 검인 신청). 법령상 설계된 절차이며 인터뷰이는 통합 필요성을 주장하지 않음.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>기준 1(법령 근거 있음, 사전 안내 문제). 제외.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46.5" customHeight="1">
+          <t>기준 2·3(정책·조직 사항). 제외. 조호영이 말한 '자체 방제계획서'는 법령상 '해양시설오염비상계획서'로 보임(발언은 고치지 않음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>과태료 감경 사유의 구체화 요청(부산)</t>
+          <t>대표자 변경 시 해양수산부 변경신고와 해양경찰 비상계획서 변경검인의 중복(법령 대조 중 발견)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>윤혜림: 감경 사유 구체화 "네, 맞습니다."(면담자 질문에 대한 동의)</t>
+          <t>(인터뷰이 발언 없음)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>시행령 별표 19 일반기준에 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력, 위반 정도·동기 등에 따른 2분의 1 범위 감경 기준이 이미 있음(2차 자료).</t>
+          <t>시행규칙 제17조제3항제1호(소유자·명칭·대표자 변경 → 변경신고 30일)와 제19조제4항제1호·제5항(소유자·명칭·대표자·관리자 정보 변경 → 비상계획서 변경검인 30일)이 같은 사유에 두 절차를 둠(300㎘ 이상 저장시설).</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>기준 2(이미 규정, 재량 통일은 지침 사항). 제외. 금액 차등은 본표 연번 7에 반영.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+          <t>입법사실 없음. [부수 정비 검토 가능] 본표 연번 8~10 정비 시 연계(해양경찰청 협의).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="73.5" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>폐업·철거 후 신고 잔존, 주기적 확인 규정 부재(군산)</t>
+          <t>최초신고 시 해양오염방지관리인 교육 이수 요구로 인한 보완(부산)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>신재민: "신고했던 것은 그대로 남아 있는 경우가 있습니다." / "몇 년에 한 번씩 확인해야 한다는 규정이 없다 보니 그런 부분을 놓칠 수도 있다는 측면이 있습니다."</t>
+          <t>윤혜림: "해양오염방지교육을 이수해야 하는데 이 부분이 누락되거나 교육 신청이 늦어지는 경우가 많아, 최초 신고 시 바로 접수되는 경우는 없고 서류 보완을 요청하는 경우가 많습니다."</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>폐업신고(폐업일부터 30일, 별지 제16호서식)는 시행규칙에 있으나(2차 자료) 법 제33조 문언에 폐업신고가 있는지 미확인. 주기적 현황 확인 의무 신설은 행정청 내부 사무.</t>
+          <t>법 제36조제1항(대통령령으로 정하는 자격을 갖춘 관리인 임명·보유)·제2항(해경에 임명 신고), 제121조제2호(관리인 자격 관련 교육·훈련과정), 시행규칙 제17조제1항제2호(임명확인서 첨부, 별표 1 제1호 시설 한정)에 근거가 있음(원문 확인). 교육 이수는 관리인 자격 요건이므로 첨부서류 요구는 법령 범위 안.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>기준 1·3. 제외. [부수 정비 검토 가능] 법 제33조에 폐업 문언이 없다면 폐업신고 의무의 법률 근거를 보강할 필요가 있으므로 원문 확인 후 연번 3~5 정비 시 함께 검토.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46.5" customHeight="1">
+          <t>기준 1(법령 근거 있음, 사전 안내 문제). 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>신고증명서 재발급 신청서의 '분실 사유' 기재(군산)</t>
+          <t>과태료 감경 사유의 구체화 요청(부산)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>신재민: "아니요, 의미 없습니다."(재발급 심사 기준 여부)</t>
+          <t>윤혜림: 감경 사유 구체화 "네, 맞습니다."(면담자 질문에 대한 동의)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>재발급 서식·조문은 미확인. 사유 기재는 심사 요건이 아니라 서식 항목으로 보임.</t>
+          <t>시행령 별표 19 일반기준 나목(질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력, 위반 정도·동기 등 2분의 1 범위 감경), 다목(2026.6.30. 신설: 고의·중과실 없는 소상공인 100분의 70 범위 감경)이 이미 있음(원문 확인).</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>기준 2(서식 정비 사항, 입법사실 미약). 제외. [부수 정비 검토 가능] 서식 개정 시 삭제 검토.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="73.5" customHeight="1">
+          <t>기준 2(이미 규정, 재량 통일은 지침 사항). 제외. 금액 차등은 본표 연번 8에 반영.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 제17조의 「전자정부법」 인용 조문 번호 불일치(법령 대조 중 발견)</t>
+          <t>폐업·철거 후 신고 잔존, 주기적 확인 규정 부재(군산)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>(인터뷰이 발언 없음)</t>
+          <t>신재민: "신고했던 것은 그대로 남아 있는 경우가 있습니다." / "몇 년에 한 번씩 확인해야 한다는 규정이 없다 보니 그런 부분을 놓칠 수도 있다는 측면이 있습니다."</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 제17조의 공동이용 확인 조항이 「전자정부법」 제21조제1항을 인용하는 것으로 확인되나(2차 자료, 2008~2010년 개정 표기), 현행 전자정부법의 공동이용 근거 조문은 제36조이고 민원처리법 제10조제3항도 제36조제1항을 인용함. 현행 시행규칙이 이미 정비되었는지 원문 미대조.</t>
+          <t>폐업신고는 시행규칙 제17조제7항(별지 제16호서식, 기한 없음)에만 있고 법 제33조에는 폐업 신고 문언이 없음(원문 확인). 법 제33조제2항의 위임은 '신고·변경신고 절차'이므로 폐업신고 의무의 법률 근거가 불분명함. 주기적 현황 확인 의무 신설은 행정청 내부 사무.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>입법사실 없음. [부수 정비 검토 가능] 본표 연번 10·11 정비 시 인용 조문을 함께 바로잡을 것.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="87" customHeight="1">
+          <t>기준 1·3. 제외. [부수 정비 검토 가능] 법 제33조에 폐업신고 근거와 기한을 두는 정비를 연번 3~7과 함께 검토.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46.5" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>시행령 위임 조문과 시행규칙의 권한 주체 불일치 가능성(법령 대조 중 발견)</t>
+          <t>신고증명서 재발급 신청서의 '분실 사유' 기재(군산)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>(인터뷰이 발언 없음)</t>
+          <t>신재민: "아니요, 의미 없습니다."(재발급 심사 기준 여부)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>시행령 구판 제94조제4항은 지방해양수산청장에게 신고·변경신고의 '접수'만 위임하는 문언이고, 시행규칙 제17조제2항은 지방해양수산청장 또는 시·도지사가 신고증명서를 발급하도록 함. 법 제33조제1항은 '해양수산부장관에게' 신고하도록 하여 시·도지사 관할의 근거도 미확인. 현행 위임 조문 번호는 2차 자료가 상충(삭제 2024.1.2. 표시 vs 존속).</t>
+          <t>시행규칙 제17조제6항(별지 제15호서식 재발급신청서)에 심사 요건 없음(원문 확인). 사유 기재는 서식 항목으로 보임(서식 본문 미조회).</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>입법사실 없음. [부수 정비 검토 가능] 본표 연번 3~5의 개정 시 위임 조문의 '접수'를 '접수·수리·증명서 발급'으로 정비하고 시·도지사 관할 근거를 확인.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="127.5" customHeight="1">
+          <t>기준 2(서식 정비 사항, 입법사실 미약). 제외. [부수 정비 검토 가능] 서식 개정 시 삭제 검토.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="73.5" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>별지 제12호서식 첨부서류란의 근거 조문 오기(법령 대조 중 발견)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>(인터뷰이 발언 없음)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>별지 제12호서식(개정 2024.6.28.) 첨부서류 2번은 '「해양환경관리법」 제32조에 따른 해양오염방지관리인의 임명확인서'로 적혀 있으나 제32조는 선박 해양오염방지관리인 조문이고, 시행규칙 제17조제1항제2호는 '법 제36조에 따른 해양시설해양오염방지관리인'을 인용함(원문 확인).</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>입법사실 없음. [부수 정비 검토 가능] 본표 연번 11·12의 서식 정비 시 함께 바로잡을 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="100.5" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>시행령 위임 조문('접수')과 시행규칙의 증명서 발급 권한(법령 대조 중 발견)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>(인터뷰이 발언 없음)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>시행령 제94조제4항제2호·제6항제2호는 해양시설 신고·변경신고의 '접수'만 지방해양수산청장·시·도지사에게 위임하고, 제4항제2호의3은 오염물질저장시설 신고에 대해 '수리'를 위임함. 시행규칙 제17조제2항·제5항은 지방해양수산청장·시·도지사가 신고증명서를 발급하도록 함(원문 확인). 법 제33조제1항제1호는 국가관리연안항을 해양수산부장관 관할로 두는데 시행령 제6항제2호가 그 접수를 시·도지사에게 위임함.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>입법사실 없음. 본표 연번 3~5 [문제점] ⑥·[개정 방향] ③에 반영.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="127.5" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>4절 기준으로 제외한 쟁점 요약</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>기준 1(운영·시스템): 서류 미비 시 접수 보류, 온라인 접수 미실시, 공동이용 시스템 미이용, 관리인 교육 사전 안내, 처리 현황 안내, 국민신문고 등록 방식, 현장 확인 시 기업 출입 협조. / 기준 2(해석·지침): 보완 불응 대응 규정, 과태료 감경 기준 구체화, 재발급 사유 기재, 공유수면 연계. / 기준 3(범위 밖·규제 신설): 안전점검 후 시정조치 권한, 허가·등록 단계 도입, 위험도별 차등 관리 체계, 주기적 현황 확인 의무, 거짓 신고 사례("그런 사례는 없었던 것 같습니다"), 관할 중첩 사례("그런 사례는 없었습니다"), 민원인 불순응 사례("그런 사례는 보통 없습니다").</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>포항청 조호영은 별표 1 대상 판단에 어려움이 없다고 하여("저희는 그런 시설은 거의 없고, 취수·배수시설과 기름 저장탱크 같은 게 많은데, 저장탱크는 보면 바로 알 수 있습니다.") 연번 1·2의 반대 사례로 기록함.</t>
         </is>
@@ -1512,7 +1566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1537,241 +1591,207 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="87" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>확인 방법 공통</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 korean-law MCP 커넥터)로 현행본 조회</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>이 세션의 실행 환경은 law.go.kr 등 웹 직접 접속이 차단되어, 1차(2026.10.12. 오전)는 웹 검색 요약(2차 자료)으로만 작성했고, 2차(같은 날 오후)에 커넥터로 조문·별표·서식 원문을 조회해 전부 재대조함. 아래 '원문'은 커넥터가 반환한 법제처 DB 본문을 뜻함. 근거 로그: notes/evidence_log.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="73.5" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>해양환경관리법</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>법률 제21065호(2025.10.1. 시행, 타법개정) 외에 2026.1.2. 시행 판본(국가법령정보센터)과 법률 제21416호(2026.2.27. 일부개정, 로앤비)가 검색됨 — 최신 공포번호·시행일 미확정</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>제2조제17호(해양시설 정의), 제33조제1항·제2항(신고·변경신고, 부령 위임), 제35조(비상계획서 검인·해경), 제36조(관리인 임명 신고·해경), 제36조의2(안전점검), 제121조(교육), 제123조(위임), 제132조제2항제2호(과태료). 확인 상태: 모두 2차 자료(복수 출처 일치 범위). 조문 본문은 2008·2011·2013 개정 표기 구판 요약이 많아 현행 문언(특히 제33조에 수리·기한 문언 유무, 제132조제2항 상한, 제36조의2 현행 항 구성)은 원문 미대조.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="100.5" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026.2.27. 공포, 2026.8.28. 시행(현행, 법령ID 010379). 법률 번호는 2차 자료(로앤비) 기준 제21416호</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>원문 확인: 제2조제17호, 제33조(제1항 각 호 구분 2020.2.18. 개정, 변경신고 후단 2016.12.27. 개정, 제2항 2016.12.27. 개정), 제35조, 제36조, 제36조의2, 제38조제3항(2023.10.24. 신설), 제38조의3, 제121조, 제123조, 제132조(제2항 500만원 이하, 제2호). 연혁 대조: 2015.12.23. 시행본은 변경신고·시·도지사 구분 없음, 2019.8.20. 시행본은 변경신고 있음·시·도지사 구분 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>해양환경관리법 시행령</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>대통령령 제35426호(2025.4.1. 일부개정, 2025.6.21. 시행), 대통령령 제36478호(2026.6.30. 일부개정, 2026.7.1. 시행, 형식승인 신고 관련 별표 문구 개정) — 검색 요약. 별표 19는 2023.4.18. 개정본</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>제98조·별표 19(과태료 부과기준: 신고·변경신고 미이행 250만원, 법 제132조제2항제2호; 일반기준 2분의 1 감경). 권한 위임 조문: 구판 제94조제4항(지방해양수산청장에게 국가관리무역항·EEZ 해양시설 신고·변경신고의 '접수' 위임)만 확인, 현행 조문 번호는 출처 상충(삭제 2024.1.2. 표시 vs 존속) — 원문 미대조.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="100.5" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026.6.30. 공포, 2026.7.1. 시행(현행, 법령ID 010632; 대통령령 제36478호는 2차 자료). 별표 19는 2026.6.30. 개정</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>원문 확인: 제94조(권한의 위임) 제4항제2호·제2호의3·제25호, 제5항제1호·제1호의2, 제6항제2호·제4호(제1항은 2014.11.19. 삭제; 2차 자료의 '제94조 삭제'는 오류), 제98조, 별표 19 일반기준 가~다목·개별기준 너목(250만원)·더목(30만원)·러목~버목.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>해양환경관리법 시행규칙</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>현행 해양수산부령 번호·최근 개정일 미확인(komsa 규정관리시스템 페이지에 공란)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>제17조(해양시설의 신고 등) 제1항 신고서·첨부서류·제출처, 제2항 신고대장·신고증명서 발급, 제3항 중요한 내용의 변경(소유자·명칭·대표자, 장소, 규모 50%), 변경신고 30일·첨부서류(항 번호 미확정), 제5항 변경 시 증명서 기재·발급, 폐업신고 30일(항 미확인). 제20조의3(안전점검 대상·중대한 결함, 2018.5.1. 신설). 행정정보 공동이용 확인 조항(「전자정부법」 제21조제1항 인용, 대상 서류 미확인). 최초신고 기한 문언 유무 미확인(해수부 FAQ '사업개시 후 30일'의 조문 근거 불명). 변경신고 도입 시기는 2013년(개정이유서 언급)과 2017.3.21.(한국선급 안내)로 출처 상충. 확인 상태: 2차 자료, 원문 미대조.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="73.5" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>시행규칙 별표 1 해양시설의 범위</t>
-        </is>
-      </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>검색된 파일은 '개정 2013.3.24.(제3조 관련)' 표기본. 현행본 개정일 미확인</t>
+          <t>2026.10.6. 공포·시행(현행, 법령ID 010636; 해양수산부령 번호 미확인)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>제1호 가목(계류시설(돌핀)·이송설비·저장시설·자가처리시설), 라목('해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트 포함)'), 선박 건조·수리·해체시설, 제2호(연면적 100㎡ 이상 해상관광·주거·음식점(선박안전법상 선박 제외), 관경 600㎜ 이상 취수·배수시설(배관 포함), 유어장, 가두리낚시터). 면적 단위가 출처 간 ㎡/㎥로 다름. 제3호 유무 미확인. 라목이 재위임한 고시의 제정 여부 미확인.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46.5" customHeight="1">
+          <t>원문 확인: 제3조(별표 1 인용), 제17조 제1항~제7항(제1항제3호 2024.6.28. 개정, 제3~5항 2017.6.28. 신설; 최초신고·폐업신고 기한 없음, 공동이용 확인 조항 없음), 제19조 제1항·제3항~제6항, 제20조의3. 2023.12.28. 시행본과 대조: 제17조는 제1항제3호의 대상 표현만 바뀜.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="73.5" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 별지 제12호·제13호·제14호·제16호서식</t>
+          <t>시행규칙 별표 1 해양시설의 범위(제3조 관련)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>서식 개정일 미확인</t>
+          <t>개정 2020.12.4.(현행). 2020.6.1. 기준 조회본은 개정 2013.3.24. 표기</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>제12호 해양시설 (최초, 변경)신고서: 처리기간 최초 7일·변경 5일 기재(정부24 안내·인터뷰이 진술 일치). 구비서류란·담당공무원 확인사항란·공동이용 동의란 유무 미확인. 제13호 신고대장, 제14호 (변경)신고증명서, 제16호 폐업신고서는 서식 목록으로만 확인.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1">
+          <t>원문 확인(전문). 제1호 가~마목, 제2호 가~라목(라목 '그 밖의 시설': 해상송전철탑·해저광케이블·해상부유구조물), 제3호 종합해양과학기지, 비고 1·2. 2013년 개정본과의 차이는 제1호 마목의 인용 법령명(해양폐기물 및 해양오염퇴적물관리법)뿐. 제1호 라목이 재위임한 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비' 고시는 행정규칙 DB 검색('해양시설' 고시 10건, '하역설비' 0건, '계류시설' 1건)에서 확인되지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="73.5" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>행정기본법 제34조</t>
+          <t>시행규칙 별지 제12호·제14호·제16호서식</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2023.3.24. 시행 조항(검색 요약)</t>
+          <t>제12호 개정 2024.6.28., 제14호 개정 2015.1.8., 제16호 개정 2021.1.7.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 복수 출처(LBOX·lawnb·논문) 일치. 원문 미대조.</t>
+          <t>원문 확인. 제12호: 처리기간 (최초)7일 (변경)5일, 신고인란·신고내용란·첨부서류란(최초 3종, 변경 2종), 담당 공무원 확인사항란·공동이용 동의란 없음, 첨부서류 2번 근거 조문 '법 제32조' 오기, 뒤쪽 처리절차(접수→검토→결재→신고증명서 발급). 제14호: '신고하였음을 증명합니다', 뒤쪽 변경사항란. 제16호: 처리기간 3일, 구비서류 신고증명서 원본, 수수료 없음. 제13호·제15호는 서식 목록으로만 확인.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>행정기본법 제34조</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2025.3.18. 공포본(법령ID 014041)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>원문 확인. 문언은 본표 [현행 규정]과 같음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="33" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>행정절차법 제40조</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>현행 조문(검색 요약, 개정일 미확인)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>제2항 형식 요건 충족 시 도달로 의무 이행, 제3항 보완 요구, 제4항 미보완 시 반려. 복수 출처 일치. 원문 미대조.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>민원 처리에 관한 법률 제10조·제19조, 같은 법 시행령 제24조·제25조</t>
-        </is>
-      </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>현행 조문(검색 요약, 개정일 미확인)</t>
+          <t>2022.1.11. 공포, 2022.7.12. 시행본(법령ID 001362)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>제10조제1항 관계법령등 외 서류 요구 금지, 제3항 공동이용으로 확인 가능한 서류 요구 금지·직접 확인, 제4항 변경·갱신 시 기제출 서류 재요구 금지. 제19조 처리기간 계산(5일 이하 시간 단위, 6일 이상 일 단위, 토·공휴일 불산입). 시행령 제24조 보완 요구, 제25조 반려. 복수 출처 일치. 원문 미대조.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46.5" customHeight="1">
+          <t>원문 확인. 제1항~제4항.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>전자정부법 제36조</t>
+          <t>민원 처리에 관한 법률 제10조·제19조·제22조, 같은 법 시행령 제24조·제25조</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>법률 제20654호(2025.1.7. 일부개정, 2025.7.8. 시행) — 소관 안내 기준</t>
+          <t>법률 2022.1.11. 공포본(법령ID 001359; 2026.12.3. 시행 예정 타법개정 있음), 시행령 2026.5.6. 공포·시행본</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>행정정보 공동이용 근거 조문이라는 점만 확인(행안부 소관 안내, 민원처리법 제10조제3항의 인용). 문언 미확인.</t>
+          <t>원문 확인. 제10조제1항·제3항(제3호: 전자정부법 제36조제1항 공동이용)·제7항(변경·갱신 시 재요구 금지; 1차 보고의 '제4항' 표기는 오류), 제19조제1항·제2항, 제22조제1항, 시행령 제24조제1항~제3항, 제25조제1항.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>전자정부법 제36조</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026.2.27. 공포, 2026.8.28. 시행본(법령ID 009199)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>원문 확인. 제1항: 다른 행정기관등으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있는 경우 같은 내용의 정보를 따로 수집하여서는 아니 됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="33" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>질서위반행위규제법 제6조</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>현행 조문(검색 요약, 개정일 미확인)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>제6조(질서위반행위 법정주의): 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니함. 복수 출처 일치. 원문 미대조.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2차 자료: 해양수산부 FAQ '해양시설이란 무엇이고, 신고시 구비서류는 어떻게 됩니까?'(군산지방해양수산청 안내 전재)</t>
-        </is>
-      </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>mof.go.kr docSeq=7532, 작성일 미확인</t>
+          <t>2026.3.24. 공포, 2026.10.2. 시행본(법령ID 010592)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>최초신고 '사업개시 후 30일 이내', 변경신고 30일, 폐업신고 30일, 첨부서류, 변경신고 대상. 근거를 '시행규칙 제17조제3항'으로 인용. 최초신고 30일은 조문에서 확인되지 않아 원문과 다를 가능성 있음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="33" customHeight="1">
+          <t>원문 확인. '법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="87" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2차 자료: 정부24 '해양시설 최초(변경)신고'</t>
+          <t>2차 자료: 해양수산부 FAQ '해양시설이란 무엇이고, 신고시 구비서류는'(군산청 안내 전재), 정부24 '해양시설 최초(변경)신고', 국토교통부 정책정보(구 국토해양부 업무 안내), 목포·인천·군산청 안내</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gov.kr CappBizCD=16110000004</t>
+          <t>작성일 미확인</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>처리기간 최초 총7일·변경 총5일, 수수료 없음, 인터넷·방문·우편 신청 가능, '담당 공무원은 행정정보 공동이용을 통하여 첨부서류 정보를 확인' 문구(서식 기재인지 공통 문구인지 미확인).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2차 자료: 국토교통부 정책정보(구 국토해양부 해양시설 신고 업무 안내)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>molit.go.kr policyData id=516, 2009년경 자료로 추정(면담자 언급)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>업무흐름 '신고 → 적정여부 검토, 수리 → 신고대장 작성·신고증명서 발급 → 변경·폐업신고', 관할구역. '수리'는 안내문상 단계이며 법령 문언이 아님.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46.5" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2차 자료: 목포·인천지방해양수산청 해양시설 신고 안내, 한국선급 법 개정 안내, 해양환경공단 교육 안내</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>각 기관 홈페이지</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>관할(국가관리항·EEZ는 지방청, 그 밖은 지자체), 별표 1 항목 일부, 2017.3.21. 변경신고 도입, 관리인 교육 5년 주기. 보조 확인용.</t>
+          <t>원문과 다른 내용: ① '최초신고 사업개시 후 30일 이내', '폐업신고 폐업일부터 30일 이내'는 현행 조문에 없음. ② 인천청 안내에 전재된 '전자정부법 제21조제1항에 따른 공동이용 확인' 조문은 현행 시행규칙 제17조에 없음. ③ 변경신고 도입을 2013년 또는 2017.3.21.로 적은 자료는 오류(2016.12.27. 법률 개정, 2017.6.28. 시행규칙 신설). ④ 일부 자료의 '시행령 제94조 삭제'는 오류. 처리기간 7일·5일, 첨부서류, 변경신고 대상·30일은 원문과 일치.</t>
         </is>
       </c>
     </row>

--- a/해양시설신고/output/261012_입법영향분석_해양시설신고_법령개정_필요사항.xlsx
+++ b/해양시설신고/output/261012_입법영향분석_해양시설신고_법령개정_필요사항.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="384" customHeight="1">
+    <row r="2" ht="343.5" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -525,7 +525,7 @@
 법 제132조제2항제2호(신고 미이행 과태료)
 시행규칙 제3조(법 제2조제17호의 시설 = 별표 1)
 시행규칙 별표 1 해양시설의 범위(제3조 관련, 개정 2020.12.4.) 제1호 가목·다목·라목, 제2호 가목·나목·라목
-별표 1 제1호 라목이 재위임한 해양수산부 고시(국가법령정보센터 행정규칙 DB에서 확인되지 않음)
+별표 1 제1호 라목이 재위임한 해양수산부 고시(제정 여부 확인되지 않음)
 시행령 별표 19(과태료 부과기준)</t>
         </is>
       </c>
@@ -537,15 +537,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 규정에 따른 항만을 포함한다)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제3조가 이를 별표 1의 시설로 정한다. 별표 1(개정 2020.12.4.)은 ① 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 목적 시설)에 가목 기름·유해액체물질 저장시설 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 나목 법 제38조의 오염물질저장시설, 다목 선박 건조·수리·해체시설 '저장시설, 상가시설 및 수리시설(이동식 시설은 제외)', 라목 시멘트·석탄·사료·곡물·고철·광석·목재·토사의 하역시설 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 마목 폐기물해양배출업자의 폐기물저장시설을, ② 제2호(해양레저·관광·주거·해수이용 등 목적 시설)에 가목 연면적 100㎡ 이상 해상관광·주거·음식점 시설(범위: 해역 안 시설, 해역과 육지 사이 연속 시설은 취수·배수 시설(배관 포함)), 나목 관경 600㎜ 이상 취수·배수시설, 다목 유어장, 라목 '그 밖의 시설'의 범위로 '해상송전철탑, 해저광케이블, 해상부유구조물'을, ③ 제3호에 종합해양과학기지를 열거한다. 라목의 계류시설·하역설비를 정하는 해양수산부 고시는 2026.10.12. 국가법령정보센터 행정규칙 DB 검색('해양시설'(고시), '하역설비', '계류시설')에서 확인되지 않았다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 규정에 따른 항만을 포함한다)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제3조가 이를 별표 1의 시설로 정한다. 별표 1(개정 2020.12.4.)은 ① 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 목적 시설)에 가목 기름·유해액체물질 저장시설 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 나목 법 제38조의 오염물질저장시설, 다목 선박 건조·수리·해체시설 '저장시설, 상가시설 및 수리시설(이동식 시설은 제외)', 라목 시멘트·석탄·사료·곡물·고철·광석·목재·토사의 하역시설 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 마목 폐기물해양배출업자의 폐기물저장시설을, ② 제2호(해양레저·관광·주거·해수이용 등 목적 시설)에 가목 연면적 100㎡ 이상 해상관광·주거·음식점 시설(범위: 해역 안 시설, 해역과 육지 사이 연속 시설은 취수·배수 시설(배관 포함)), 나목 관경 600㎜ 이상 취수·배수시설, 다목 유어장, 라목 '그 밖의 시설'의 범위로 '해상송전철탑, 해저광케이블, 해상부유구조물'을, ③ 제3호에 종합해양과학기지를 열거한다. 라목의 계류시설·하역설비를 정하는 해양수산부 고시는 국가법령정보센터 행정규칙 검색에서 확인되지 않았다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다.
 [문제점] ① 별표 1의 '계류시설(돌핀)', '하역설비', '저장시설', '상가시설' 등은 「항만법」(항만시설), 「항만운송사업법」(항만하역), 「위험물안전관리법」 등 다른 법령의 시설 분류와 연계 없이 일반 용어로만 기재되어 있어, 같은 물적 시설이 신고 대상인지 담당자마다 판단이 갈린다(인터뷰이: "이 법에서만 이런 용어를 쓰는 것 같아서"). ② 제1호 라목은 대상 특정을 해양수산부 고시에 재위임하는데 해당 고시가 확인되지 않는다. 고시가 없으면 별표 문언만으로는 "고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐"는 범위 문제가 생긴다(위임사항 미이행). ③ 별표는 제2호 가목에 대해서만 해역·육지 연속 시설의 신고 범위 기준(취수·배수 시설)을 두고, 제2호 라목 '그 밖의 시설'은 '해상송전철탑, 해저광케이블, 해상부유구조물'의 닫힌 열거여서 육상 철탑 사이를 해상으로 지나는 송전선로처럼 해역과 육지에 걸친 시설의 어느 부분이 신고 대상인지 판단 기준이 없다. ④ 제2호 가목은 「선박안전법」상 선박을 제외하는 등 제외 규정을 두면서 제1호 시설에는 다른 법령에 따른 안전관리 대상과의 중복 처리 기준이 없어 "다른 법령과 중복이 되어도 되는 건지" 불명확하다. ⑤ 신고 대상 여부가 과태료 부과의 구성요건이므로 대상 범위의 불명확은 곧 제재 요건의 불명확이다.
 [논거] 법 제2조제17호가 대상 시설의 특정을 부령에 포괄 위임하고 별표 1이 다시 고시에 재위임하는 구조에서, 최종 단계(고시)가 비어 있거나 문언이 열려 있으면 신고 의무(법 제33조제1항)와 과태료(법 제132조제2항제2호, 「질서위반행위규제법」 제6조의 법정주의)의 적용 범위가 법령 문언으로 확정되지 않는다. 의무 부과·제재의 구성요건은 수범자가 예측할 수 있을 정도로 명확해야 한다는 명확성 원칙과 위임입법의 한계(위임받은 사항을 하위법령이 정하지 않은 상태) 문제이며, 담당자 해석이나 질의회신으로 보충할 사항이 아니라 별표·고시 문언 자체의 정비 사항이다. 인터뷰이가 유사 시설에 대해 담당자별 판단이 달라질 수 있다고 인정한 점("조금 있다고 볼 수 있습니다")은 평등 원칙 차원의 문제이기도 하다.
 [개정 방향] ① (부령) 별표 1 각 항목에 근거 법령상 시설 분류를 인용하도록 문언을 고친다. 예: 계류시설은 「항만법」상 항만시설 중 계류시설의 세부 종류로, 하역시설은 「항만운송사업법」상 항만하역 시설로 특정하고, 그 밖의 시설은 '○○법 제○조에 따른 ○○시설' 형식으로 쓴다. ② (부령·고시) 제1호 라목의 '해양수산부장관이 정하여 고시하는' 부분은 고시를 제정하거나, 고시 없이 별표에 직접 열거하는 방식으로 재위임을 해소한다. ③ (부령) 제2호 가목에만 있는 해역·육지 연속 시설의 범위 기준을 별표 비고로 옮겨 제1호·제2호 전체에 적용되는 공통 기준(예: 해역 안에 설치된 부분과 그에 연속한 배관·선로)으로 두고, 다른 법령에 따른 안전관리 대상 시설과의 관계(중복 적용 여부, 제외 사유)를 비고에 명시한다. ④ (법률, 선택) 법 제2조제17호의 포괄 위임을 완화하여 시설 유형(기름·유해액체물질의 저장·이송·계류, 취수·배수, 해양레저·관광 등)을 법률에 예시로 열거하고 세부를 부령에 위임한다. 최소 정비안은 ①~③(부령·고시)만으로 가능하다. 연번 2(부산청)와 연계.
-[유의] 별표 1 현행본(개정 2020.12.4.)은 원문으로 확인했고, 2013.3.24. 개정본과 비교해 제1호 마목의 인용 법령명만 바뀌었을 뿐 '해상송전철탑' 등은 2013년부터 열거되어 있었다. 고시는 국가법령정보센터 행정규칙 DB에 등재되지 않은 것일 수 있으므로 해양수산부(해양보전과)에 제정 여부를 확인해야 한다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 인터뷰이는 돌핀·하역설비의 정의 연계를 희망하면서도 "그정도까지 복잡한 것은 아니"라고 하여 입법사실의 규모는 크지 않다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="397.5" customHeight="1">
+[유의] 별표 1(개정 2020.12.4.)은 2013.3.24. 개정본과 비교해 제1호 마목의 인용 법령명만 바뀌었을 뿐 '해상송전철탑' 등은 2013년부터 열거되어 있었다. 고시는 국가법령정보센터에 등재되지 않은 것일 수 있으므로 해양수산부에 제정 여부를 확인해야 한다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 인터뷰이는 돌핀·하역설비의 정의 연계를 희망하면서도 "그정도까지 복잡한 것은 아니"라고 하여 입법사실의 규모는 크지 않다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="370.5" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -572,7 +572,7 @@
 법 제132조제2항제2호(신고 미이행 과태료)
 시행규칙 제3조(법 제2조제17호의 시설 = 별표 1)
 시행규칙 별표 1 해양시설의 범위(제3조 관련, 개정 2020.12.4.) 제1호 가목·다목·라목, 제2호 가목·나목·라목
-별표 1 제1호 라목이 재위임한 해양수산부 고시(국가법령정보센터 행정규칙 DB에서 확인되지 않음)
+별표 1 제1호 라목이 재위임한 해양수산부 고시(제정 여부 확인되지 않음)
 시행령 별표 19(과태료 부과기준)</t>
         </is>
       </c>
@@ -584,11 +584,11 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 규정에 따른 항만을 포함한다)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제3조가 이를 별표 1의 시설로 정한다. 별표 1(개정 2020.12.4.)은 ① 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 목적 시설)에 가목 기름·유해액체물질 저장시설 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 나목 법 제38조의 오염물질저장시설, 다목 선박 건조·수리·해체시설 '저장시설, 상가시설 및 수리시설(이동식 시설은 제외)', 라목 시멘트·석탄·사료·곡물·고철·광석·목재·토사의 하역시설 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 마목 폐기물해양배출업자의 폐기물저장시설을, ② 제2호(해양레저·관광·주거·해수이용 등 목적 시설)에 가목 연면적 100㎡ 이상 해상관광·주거·음식점 시설(범위: 해역 안 시설, 해역과 육지 사이 연속 시설은 취수·배수 시설(배관 포함)), 나목 관경 600㎜ 이상 취수·배수시설, 다목 유어장, 라목 '그 밖의 시설'의 범위로 '해상송전철탑, 해저광케이블, 해상부유구조물'을, ③ 제3호에 종합해양과학기지를 열거한다. 라목의 계류시설·하역설비를 정하는 해양수산부 고시는 2026.10.12. 국가법령정보센터 행정규칙 DB 검색('해양시설'(고시), '하역설비', '계류시설')에서 확인되지 않았다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 규정에 따른 항만을 포함한다)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제3조가 이를 별표 1의 시설로 정한다. 별표 1(개정 2020.12.4.)은 ① 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 목적 시설)에 가목 기름·유해액체물질 저장시설 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 나목 법 제38조의 오염물질저장시설, 다목 선박 건조·수리·해체시설 '저장시설, 상가시설 및 수리시설(이동식 시설은 제외)', 라목 시멘트·석탄·사료·곡물·고철·광석·목재·토사의 하역시설 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 마목 폐기물해양배출업자의 폐기물저장시설을, ② 제2호(해양레저·관광·주거·해수이용 등 목적 시설)에 가목 연면적 100㎡ 이상 해상관광·주거·음식점 시설(범위: 해역 안 시설, 해역과 육지 사이 연속 시설은 취수·배수 시설(배관 포함)), 나목 관경 600㎜ 이상 취수·배수시설, 다목 유어장, 라목 '그 밖의 시설'의 범위로 '해상송전철탑, 해저광케이블, 해상부유구조물'을, ③ 제3호에 종합해양과학기지를 열거한다. 라목의 계류시설·하역설비를 정하는 해양수산부 고시는 국가법령정보센터 행정규칙 검색에서 확인되지 않았다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다.
 [문제점] ① 별표 1의 '계류시설(돌핀)', '하역설비', '저장시설', '상가시설' 등은 「항만법」(항만시설), 「항만운송사업법」(항만하역), 「위험물안전관리법」 등 다른 법령의 시설 분류와 연계 없이 일반 용어로만 기재되어 있어, 같은 물적 시설이 신고 대상인지 담당자마다 판단이 갈린다(인터뷰이: "이 법에서만 이런 용어를 쓰는 것 같아서"). ② 제1호 라목은 대상 특정을 해양수산부 고시에 재위임하는데 해당 고시가 확인되지 않는다. 고시가 없으면 별표 문언만으로는 "고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐"는 범위 문제가 생긴다(위임사항 미이행). ③ 별표는 제2호 가목에 대해서만 해역·육지 연속 시설의 신고 범위 기준(취수·배수 시설)을 두고, 제2호 라목 '그 밖의 시설'은 '해상송전철탑, 해저광케이블, 해상부유구조물'의 닫힌 열거여서 육상 철탑 사이를 해상으로 지나는 송전선로처럼 해역과 육지에 걸친 시설의 어느 부분이 신고 대상인지 판단 기준이 없다. ④ 제2호 가목은 「선박안전법」상 선박을 제외하는 등 제외 규정을 두면서 제1호 시설에는 다른 법령에 따른 안전관리 대상과의 중복 처리 기준이 없어 "다른 법령과 중복이 되어도 되는 건지" 불명확하다. ⑤ 신고 대상 여부가 과태료 부과의 구성요건이므로 대상 범위의 불명확은 곧 제재 요건의 불명확이다.
 [논거] 법 제2조제17호가 대상 시설의 특정을 부령에 포괄 위임하고 별표 1이 다시 고시에 재위임하는 구조에서, 최종 단계(고시)가 비어 있거나 문언이 열려 있으면 신고 의무(법 제33조제1항)와 과태료(법 제132조제2항제2호, 「질서위반행위규제법」 제6조의 법정주의)의 적용 범위가 법령 문언으로 확정되지 않는다. 의무 부과·제재의 구성요건은 수범자가 예측할 수 있을 정도로 명확해야 한다는 명확성 원칙과 위임입법의 한계(위임받은 사항을 하위법령이 정하지 않은 상태) 문제이며, 담당자 해석이나 질의회신으로 보충할 사항이 아니라 별표·고시 문언 자체의 정비 사항이다. 인터뷰이가 유사 시설에 대해 담당자별 판단이 달라질 수 있다고 인정한 점("조금 있다고 볼 수 있습니다")은 평등 원칙 차원의 문제이기도 하다.
 [개정 방향] ① (부령) 별표 1 각 항목에 근거 법령상 시설 분류를 인용하도록 문언을 고친다. 예: 계류시설은 「항만법」상 항만시설 중 계류시설의 세부 종류로, 하역시설은 「항만운송사업법」상 항만하역 시설로 특정하고, 그 밖의 시설은 '○○법 제○조에 따른 ○○시설' 형식으로 쓴다. ② (부령·고시) 제1호 라목의 '해양수산부장관이 정하여 고시하는' 부분은 고시를 제정하거나, 고시 없이 별표에 직접 열거하는 방식으로 재위임을 해소한다. ③ (부령) 제2호 가목에만 있는 해역·육지 연속 시설의 범위 기준을 별표 비고로 옮겨 제1호·제2호 전체에 적용되는 공통 기준(예: 해역 안에 설치된 부분과 그에 연속한 배관·선로)으로 두고, 다른 법령에 따른 안전관리 대상 시설과의 관계(중복 적용 여부, 제외 사유)를 비고에 명시한다. ④ (법률, 선택) 법 제2조제17호의 포괄 위임을 완화하여 시설 유형(기름·유해액체물질의 저장·이송·계류, 취수·배수, 해양레저·관광 등)을 법률에 예시로 열거하고 세부를 부령에 위임한다. 최소 정비안은 ①~③(부령·고시)만으로 가능하다. 연번 1(군산청)과 연계. 부산청의 한전 사례는 별표 1 제2호 라목이 '해상송전철탑'만 열거하고 육상 철탑 사이의 해상 선로 구간을 어떻게 볼지 기준이 없는 데서 생긴 것이므로 ③의 공통 범위 기준이 직접 대응한다.
-[유의] 별표 1 현행본(개정 2020.12.4.)은 원문으로 확인했고, 2013.3.24. 개정본과 비교해 제1호 마목의 인용 법령명만 바뀌었을 뿐 '해상송전철탑' 등은 2013년부터 열거되어 있었다. 고시는 국가법령정보센터 행정규칙 DB에 등재되지 않은 것일 수 있으므로 해양수산부(해양보전과)에 제정 여부를 확인해야 한다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 한전 송전철탑 사례는 인터뷰이가 다른 지방청의 처리 결과를 전해 들은 것이므로 교차 확인이 필요하다. 인터뷰이는 '등' 같은 예시 표현을 희망했으나 예시 규정은 대상 확대로 읽힐 수 있어 근거 법령 인용과 범위 기준 명시가 더 안전하다. [교차확인] 연번 1(군산청 인터뷰)과 동일 쟁점.</t>
+[유의] 별표 1(개정 2020.12.4.)은 2013.3.24. 개정본과 비교해 제1호 마목의 인용 법령명만 바뀌었을 뿐 '해상송전철탑' 등은 2013년부터 열거되어 있었다. 고시는 국가법령정보센터에 등재되지 않은 것일 수 있으므로 해양수산부에 제정 여부를 확인해야 한다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 한전 송전철탑 사례는 인터뷰이가 다른 지방청의 처리 결과를 전해 들은 것이므로 교차 확인이 필요하다. 인터뷰이는 '등' 같은 예시 표현을 희망했으나 예시 규정은 대상 확대로 읽힐 수 있어 근거 법령 인용과 범위 기준 명시가 더 안전하다. [교차확인] 연번 1(군산청 인터뷰)과 동일 쟁점.</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려.
 [문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
 [논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
 [개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 8~10과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
@@ -680,7 +680,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려.
 [문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
 [논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
 [개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 8~10과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
@@ -728,7 +728,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려.
 [문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
 [논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
 [개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 8~10과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
@@ -736,7 +736,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="330" customHeight="1">
+    <row r="7" ht="289.5" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -773,15 +773,15 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않으며, 제2항은 신고내용·절차를 부령에 위임한다. 시행규칙 제17조제1항은 "법 제33조제1항 전단에 따라 해양시설의 신고를 하려는 경우에는" 최초신고서를 제출하도록 할 뿐 기한을 두지 않고, 제4항은 변경신고에만 '변경사유가 발생한 날부터 30일 이내'를 두며, 제7항의 폐업신고에도 기한이 없다(해양수산부 FAQ와 구 국토해양부 안내의 '최초신고는 사업개시 후 30일 이내', '폐업신고는 폐업일부터 30일 이내'는 현행 조문에 근거가 없다). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 「질서위반행위규제법」 제6조: 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않으며, 제2항은 신고내용·절차를 부령에 위임한다. 시행규칙 제17조제1항은 "법 제33조제1항 전단에 따라 해양시설의 신고를 하려는 경우에는" 최초신고서를 제출하도록 할 뿐 기한을 두지 않고, 제4항은 변경신고에만 '변경사유가 발생한 날부터 30일 이내'를 두며, 제7항의 폐업신고에도 기한이 없다(해양수산부 FAQ와 구 국토해양부 안내의 '최초신고는 사업개시 후 30일 이내', '폐업신고는 폐업일부터 30일 이내'는 현행 조문에 근거가 없다). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 「질서위반행위규제법」 제6조: 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다.
 [문제점] ① 최초신고의 의무 발생 시점(설치 완료, 사용 개시, 공사 중 일부 가동)이 법령에 없어, 담당자가 "완공이 되어야 한다"고 안내하고 민원인은 "신고 시점이 법에 나와 있지 않다"고 이의를 제기한다. 배수관처럼 수 킬로미터 공정 중 일부만 가동되는 시설은 신고 시점을 특정할 수 없다. ② 변경신고에는 30일 기한이 있어, 같은 호의 과태료(별표 19 너목: 신고·변경신고 미이행 동일 250만원)가 변경신고에는 적용 시점이 분명하고 최초신고에는 불분명한 비대칭이 생긴다. ③ 서류 미비로 증명서가 발급되지 않은 경우를 "최초 신고를 지연한 상황"으로 보고 과태료를 검토하는데, 기한이 없으니 지연 여부 자체를 판단할 수 없어 부과가 "애매"해진다. ④ 행정안내(FAQ)가 조문에 없는 30일 기한을 안내하고 있어, 수범자는 안내문을, 담당자는 조문을 기준으로 삼는 불일치가 있다.
 [논거] 과태료의 구성요건인 '신고를 하지 아니한' 상태는 신고 의무의 이행 기한이 있어야 성립 시점이 확정된다. 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 못하며(「질서위반행위규제법」 제6조) 그 요건은 명확해야 하므로, 기한 없는 의무에 제재를 결부한 현행 구조는 명확성 원칙에 비추어 정비 대상이다. 행정안내로 30일을 운용하는 것은 법령 근거 없이 제재 요건을 보충하는 것이어서 해석·지침으로 해결할 수 없다. 인터뷰이(군산)의 '상식 사항' 견해는 민원인이 실제로 다투고 있다는 같은 인터뷰이의 진술과 상충한다.
 [개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항·제7항에 같은 기산점을 반영하고(폐업신고 기한도 함께), 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행·변경신고 미이행·기한 경과 후 신고로 구분한다(연번 8~10과 연계). 최소 정비안은 ②이나, 의무의 내용(기한)이 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
-[유의] 원문 확인 결과 시행규칙 제17조에 최초신고 기한이 없음이 확정되어 본 행은 본표에 유지한다(1차 보고의 '안내 부족 문제로 바뀔 수 있음' 유보는 해소). 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 7 참조). 인터뷰이가 말한 '변경 신고 처리 기한'은 맥락상 신고인의 변경신고 기한(시행규칙 제17조제4항, 30일)을 가리키는 것으로 보이며, 행정청의 처리기간(서식 5일)과 구분하여 검토메모에 기록했다. [교차확인] 연번 7(군산청 인터뷰)과 동일 쟁점(단, 군산청 인터뷰이는 입법 불요 의견).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="330" customHeight="1">
+[유의] 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 7 참조). 인터뷰이가 말한 '변경 신고 처리 기한'은 맥락상 신고인의 변경신고 기한(시행규칙 제17조제4항, 30일)을 가리키는 것으로 보이며, 행정청의 처리기간(서식 5일)과 구분하여 검토메모에 기록했다. [교차확인] 연번 7(군산청 인터뷰)과 동일 쟁점(단, 군산청 인터뷰이는 입법 불요 의견).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="289.5" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -818,15 +818,15 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않으며, 제2항은 신고내용·절차를 부령에 위임한다. 시행규칙 제17조제1항은 "법 제33조제1항 전단에 따라 해양시설의 신고를 하려는 경우에는" 최초신고서를 제출하도록 할 뿐 기한을 두지 않고, 제4항은 변경신고에만 '변경사유가 발생한 날부터 30일 이내'를 두며, 제7항의 폐업신고에도 기한이 없다(해양수산부 FAQ와 구 국토해양부 안내의 '최초신고는 사업개시 후 30일 이내', '폐업신고는 폐업일부터 30일 이내'는 현행 조문에 근거가 없다). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 「질서위반행위규제법」 제6조: 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않으며, 제2항은 신고내용·절차를 부령에 위임한다. 시행규칙 제17조제1항은 "법 제33조제1항 전단에 따라 해양시설의 신고를 하려는 경우에는" 최초신고서를 제출하도록 할 뿐 기한을 두지 않고, 제4항은 변경신고에만 '변경사유가 발생한 날부터 30일 이내'를 두며, 제7항의 폐업신고에도 기한이 없다(해양수산부 FAQ와 구 국토해양부 안내의 '최초신고는 사업개시 후 30일 이내', '폐업신고는 폐업일부터 30일 이내'는 현행 조문에 근거가 없다). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 「질서위반행위규제법」 제6조: 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다.
 [문제점] ① 최초신고의 의무 발생 시점(설치 완료, 사용 개시, 공사 중 일부 가동)이 법령에 없어, 담당자가 "완공이 되어야 한다"고 안내하고 민원인은 "신고 시점이 법에 나와 있지 않다"고 이의를 제기한다. 배수관처럼 수 킬로미터 공정 중 일부만 가동되는 시설은 신고 시점을 특정할 수 없다. ② 변경신고에는 30일 기한이 있어, 같은 호의 과태료(별표 19 너목: 신고·변경신고 미이행 동일 250만원)가 변경신고에는 적용 시점이 분명하고 최초신고에는 불분명한 비대칭이 생긴다. ③ 서류 미비로 증명서가 발급되지 않은 경우를 "최초 신고를 지연한 상황"으로 보고 과태료를 검토하는데, 기한이 없으니 지연 여부 자체를 판단할 수 없어 부과가 "애매"해진다. ④ 행정안내(FAQ)가 조문에 없는 30일 기한을 안내하고 있어, 수범자는 안내문을, 담당자는 조문을 기준으로 삼는 불일치가 있다.
 [논거] 과태료의 구성요건인 '신고를 하지 아니한' 상태는 신고 의무의 이행 기한이 있어야 성립 시점이 확정된다. 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 못하며(「질서위반행위규제법」 제6조) 그 요건은 명확해야 하므로, 기한 없는 의무에 제재를 결부한 현행 구조는 명확성 원칙에 비추어 정비 대상이다. 행정안내로 30일을 운용하는 것은 법령 근거 없이 제재 요건을 보충하는 것이어서 해석·지침으로 해결할 수 없다. 인터뷰이(군산)의 '상식 사항' 견해는 민원인이 실제로 다투고 있다는 같은 인터뷰이의 진술과 상충한다.
 [개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항·제7항에 같은 기산점을 반영하고(폐업신고 기한도 함께), 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행·변경신고 미이행·기한 경과 후 신고로 구분한다(연번 8~10과 연계). 최소 정비안은 ②이나, 의무의 내용(기한)이 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
-[유의] 원문 확인 결과 시행규칙 제17조에 최초신고 기한이 없음이 확정되어 본 행은 본표에 유지한다(1차 보고의 '안내 부족 문제로 바뀔 수 있음' 유보는 해소). 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 7 참조). 본 행의 인터뷰이는 입법 불요 의견이므로 입법사실로는 '시점 불명확으로 인한 민원 혼선'만 사용하고, 개정 필요성의 판단 근거는 연번 6(부산청)의 과태료 집행 문제에 둔다. [교차확인] 연번 6(부산청 인터뷰)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="330" customHeight="1">
+[유의] 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 7 참조). 본 행의 인터뷰이는 입법 불요 의견이므로 입법사실로는 '시점 불명확으로 인한 민원 혼선'만 사용하고, 개정 필요성의 판단 근거는 연번 6(부산청)의 과태료 집행 문제에 둔다. [교차확인] 연번 6(부산청 인터뷰)과 동일 쟁점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="316.5" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -865,7 +865,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다.
 [문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 같은 별표에서 관리인 임명 신고 미이행은 30만원이다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항제3호), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장). ⑤ 300㎘ 이상 저장시설은 대표자 변경 하나에 해양수산부(변경신고)와 해양경찰(변경검인) 두 절차를 각각 30일 내에 밟아야 하는 중복이 있다.
 [논거] 하위법령이 법률의 위임 문언('중요한 내용')을 넘어 형식적 사항까지 수리형 변경신고 대상으로 정한 것은 위임 범위의 문제이고, 경미한 변경에 중대한 변경과 같은 절차·제재를 결부한 것은 비례원칙(필요 최소한의 절차·제재)에 어긋난다. 과태료 금액은 시행령 별표 19가 정하므로 금액 차등은 시행령 개정으로 가능하고, 신고 유형의 구분은 「행정기본법」 제34조에 따라 법률에서 수리 필요 여부를 명시해야 완결된다. 규제를 완화·세분하는 방향이므로 규제 신설이 아니다.
 [개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 11·12와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
@@ -873,7 +873,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="330" customHeight="1">
+    <row r="10" ht="316.5" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -912,7 +912,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다.
 [문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 같은 별표에서 관리인 임명 신고 미이행은 30만원이다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항제3호), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장). ⑤ 300㎘ 이상 저장시설은 대표자 변경 하나에 해양수산부(변경신고)와 해양경찰(변경검인) 두 절차를 각각 30일 내에 밟아야 하는 중복이 있다.
 [논거] 하위법령이 법률의 위임 문언('중요한 내용')을 넘어 형식적 사항까지 수리형 변경신고 대상으로 정한 것은 위임 범위의 문제이고, 경미한 변경에 중대한 변경과 같은 절차·제재를 결부한 것은 비례원칙(필요 최소한의 절차·제재)에 어긋난다. 과태료 금액은 시행령 별표 19가 정하므로 금액 차등은 시행령 개정으로 가능하고, 신고 유형의 구분은 「행정기본법」 제34조에 따라 법률에서 수리 필요 여부를 명시해야 완결된다. 규제를 완화·세분하는 방향이므로 규제 신설이 아니다.
 [개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 11·12와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
@@ -920,7 +920,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="330" customHeight="1">
+    <row r="11" ht="316.5" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -959,7 +959,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다.
 [문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 같은 별표에서 관리인 임명 신고 미이행은 30만원이다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항제3호), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장). ⑤ 300㎘ 이상 저장시설은 대표자 변경 하나에 해양수산부(변경신고)와 해양경찰(변경검인) 두 절차를 각각 30일 내에 밟아야 하는 중복이 있다.
 [논거] 하위법령이 법률의 위임 문언('중요한 내용')을 넘어 형식적 사항까지 수리형 변경신고 대상으로 정한 것은 위임 범위의 문제이고, 경미한 변경에 중대한 변경과 같은 절차·제재를 결부한 것은 비례원칙(필요 최소한의 절차·제재)에 어긋난다. 과태료 금액은 시행령 별표 19가 정하므로 금액 차등은 시행령 개정으로 가능하고, 신고 유형의 구분은 「행정기본법」 제34조에 따라 법률에서 수리 필요 여부를 명시해야 완결된다. 규제를 완화·세분하는 방향이므로 규제 신설이 아니다.
 [개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 11·12와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
@@ -967,7 +967,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="316.5" customHeight="1">
+    <row r="12" ht="289.5" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1004,15 +1004,15 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서·도면·위치도, (해당 시설에 한해) 법 제36조에 따른 관리인 임명확인서, 법 제35조에 따른 해양시설오염비상계획서이고, 제4항의 변경신고 첨부서류는 신고증명서와 '변경내용을 증명하는 서류'이다. 사업자등록증·법인 등기사항증명서는 어디에도 없고, 제17조에는 행정정보 공동이용으로 확인한다는 조항이 없다. 별지 제12호서식(개정 2024.6.28.)은 신고인란에 상호(사업장 명칭)·성명(대표자)·생년월일을 적게 하면서 첨부서류란만 두고 담당 공무원 확인사항란과 행정정보 공동이용 동의란이 없으며, 첨부서류 2번의 근거 조문을 '「해양환경관리법」 제32조에 따른 해양오염방지관리인'(선박 관리인 조문)으로 적어 제17조제1항제2호(법 제36조)와 어긋난다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항제3호는 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있으면 서류 제출을 요구할 수 없고 담당자가 직접 확인·처리하도록 하며, 제7항은 변경·갱신 신청 시 기제출 서류의 재요구를 금지한다. 「전자정부법」 제36조제1항은 다른 행정기관으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있으면 같은 정보를 따로 수집하지 못하게 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서·도면·위치도, (해당 시설에 한해) 법 제36조에 따른 관리인 임명확인서, 법 제35조에 따른 해양시설오염비상계획서이고, 제4항의 변경신고 첨부서류는 신고증명서와 '변경내용을 증명하는 서류'이다. 사업자등록증·법인 등기사항증명서는 어디에도 없고, 제17조에는 행정정보 공동이용으로 확인한다는 조항이 없다. 별지 제12호서식(개정 2024.6.28.)은 신고인란에 상호(사업장 명칭)·성명(대표자)·생년월일을 적게 하면서 첨부서류란만 두고 담당 공무원 확인사항란과 행정정보 공동이용 동의란이 없으며, 첨부서류 2번의 근거 조문을 '「해양환경관리법」 제32조에 따른 해양오염방지관리인'(선박 관리인 조문)으로 적어 제17조제1항제2호(법 제36조)와 어긋난다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항제3호는 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있으면 서류 제출을 요구할 수 없고 담당자가 직접 확인·처리하도록 하며, 제7항은 변경·갱신 신청 시 기제출 서류의 재요구를 금지한다. 「전자정부법」 제36조제1항은 다른 행정기관으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있으면 같은 정보를 따로 수집하지 못하게 한다.
 [문제점] ① 신고 주체(법 제33조제1항: 소유자·설치운영자·임차인)의 동일성과 변경신고 대상인 대표자 변경(시행규칙 제17조제3항제1호)의 확인은 신고 처리에 실제로 필요한 심사 사항인데, 법령이 이를 확인할 서류나 확인 방법을 정하지 않아 부산청은 사업자등록증·법인 등기부등본을 법정 외 서류로 요구하고, 포항청도 "확인 목적"으로 제출받는다. 이는 민원처리법 제10조제1항에 반하는 상태가 법령 공백 때문에 상시화된 것이다. ② 두 서류 모두 행정정보 공동이용으로 확인 가능한 행정기관 발급 정보이므로 제10조제3항제3호에 따라 담당자가 직접 확인해야 하나, 시행규칙과 서식 어디에도 확인 조항·확인란·동의란이 없어 공동이용 절차를 시작할 근거가 없다(부산청은 공동이용 시스템을 이용한 적이 없음). ③ 변경신고의 '변경내용을 증명하는 서류'는 무엇을 내야 하는지 특정되지 않아 가장 빈번한 보완 사유가 된다. ④ 서식의 근거 조문 오기(제32조)는 신고인이 선박 관리인 조문을 찾게 하는 정합성 흠결이다.
 [논거] 신고 주체의 동일성·대표자 확인이라는 실질 확인의 근거는 법률(제33조제1항의 신고 주체 규정)과 부령(제17조제3항제1호)에 있고, 이를 확인할 서류·방법만 하위법령에 빠져 있는 유형이다. 법령에 없는 서류를 요구하는 실무를 법령에 맞추는 방법은 두 가지인데, 서류 요구를 중단하는 것은 확인을 불가능하게 하므로, 실무상 이미 요구되는 확인 사항을 서식의 '담당 공무원 확인사항'으로 옮겨 공동이용으로 대체하는 것이 민원처리법 제10조제3항·전자정부법 제36조제1항의 취지에 맞는 정비이다. 신고인에게 새로운 서류를 추가하는 것이 아니라 기존 요구 서류를 공동이용으로 대체하는 것이므로 규제 신설이 아니다.
 [개정 방향] ① (부령) 시행규칙 제17조에 "지방해양수산청장 또는 시·도지사는 「전자정부법」 제36조제1항에 따른 행정정보의 공동이용을 통하여 신고인의 법인 등기사항증명서(법인인 경우) 또는 사업자등록증명을 확인하여야 하며, 신고인이 확인에 동의하지 아니하는 경우에는 그 서류를 첨부하게 하여야 한다"는 확인 조항을 신설한다. ② (부령) 별지 제12호서식에 '담당 공무원 확인사항'란과 '행정정보 공동이용 동의서'란을 신설하고, 첨부서류 2번의 근거 조문을 '법 제36조'로 바로잡는다. ③ (부령) 제17조제4항제2호의 '변경내용을 증명하는 서류'를 변경 사유별로 예시한다(대표자·명칭 변경: ①의 공동이용 확인으로 갈음, 장소·규모 변경: 변경된 설치명세서·도면). 모두 부령만으로 가능하다.
-[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 한다. 1차 보고에서 '시행규칙 제17조에 공동이용 확인 조항이 있는 것으로 확인된다'고 적었던 서술은 지방해양수산청 안내문에 전재된 구 조문을 현행으로 오인한 것이며, 현행 제17조 원문에는 그러한 조항이 없음을 확인하여 바로잡았다. 법인 등기사항증명서·사업자등록증명이 지방해양수산청의 공동이용 대상 정보인지는 행정안전부(행정정보공동이용센터) 확인이 필요하며, 대상이 아니면 ①은 '신고인이 첨부' 방식으로만 정비한다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. [교차확인] 연번 12(포항청 인터뷰)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="330" customHeight="1">
+[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 한다. 일부 지방해양수산청 안내문에는 '담당 공무원은 전자정부법 제21조제1항에 따른 행정정보 공동이용으로 첨부서류 정보를 확인하여야 한다'는 구 조문이 실려 있으나 현행 제17조에는 그러한 조항이 없다. 법인 등기사항증명서·사업자등록증명이 지방해양수산청의 공동이용 대상 정보인지는 행정안전부(행정정보공동이용센터) 확인이 필요하며, 대상이 아니면 ①은 '신고인이 첨부' 방식으로만 정비한다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. [교차확인] 연번 12(포항청 인터뷰)와 동일 쟁점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="303" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서·도면·위치도, (해당 시설에 한해) 법 제36조에 따른 관리인 임명확인서, 법 제35조에 따른 해양시설오염비상계획서이고, 제4항의 변경신고 첨부서류는 신고증명서와 '변경내용을 증명하는 서류'이다. 사업자등록증·법인 등기사항증명서는 어디에도 없고, 제17조에는 행정정보 공동이용으로 확인한다는 조항이 없다. 별지 제12호서식(개정 2024.6.28.)은 신고인란에 상호(사업장 명칭)·성명(대표자)·생년월일을 적게 하면서 첨부서류란만 두고 담당 공무원 확인사항란과 행정정보 공동이용 동의란이 없으며, 첨부서류 2번의 근거 조문을 '「해양환경관리법」 제32조에 따른 해양오염방지관리인'(선박 관리인 조문)으로 적어 제17조제1항제2호(법 제36조)와 어긋난다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항제3호는 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있으면 서류 제출을 요구할 수 없고 담당자가 직접 확인·처리하도록 하며, 제7항은 변경·갱신 신청 시 기제출 서류의 재요구를 금지한다. 「전자정부법」 제36조제1항은 다른 행정기관으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있으면 같은 정보를 따로 수집하지 못하게 한다. 확인 상태: 본 행의 조문·별표·서식 문언은 2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 커넥터)에서 현행본을 직접 조회해 대조함. 현행 법령: 「해양환경관리법」(2026.2.27. 공포, 2026.8.28. 시행), 같은 법 시행령(2026.6.30. 공포, 2026.7.1. 시행), 같은 법 시행규칙(2026.10.6. 공포·시행).
+          <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서·도면·위치도, (해당 시설에 한해) 법 제36조에 따른 관리인 임명확인서, 법 제35조에 따른 해양시설오염비상계획서이고, 제4항의 변경신고 첨부서류는 신고증명서와 '변경내용을 증명하는 서류'이다. 사업자등록증·법인 등기사항증명서는 어디에도 없고, 제17조에는 행정정보 공동이용으로 확인한다는 조항이 없다. 별지 제12호서식(개정 2024.6.28.)은 신고인란에 상호(사업장 명칭)·성명(대표자)·생년월일을 적게 하면서 첨부서류란만 두고 담당 공무원 확인사항란과 행정정보 공동이용 동의란이 없으며, 첨부서류 2번의 근거 조문을 '「해양환경관리법」 제32조에 따른 해양오염방지관리인'(선박 관리인 조문)으로 적어 제17조제1항제2호(법 제36조)와 어긋난다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항제3호는 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있으면 서류 제출을 요구할 수 없고 담당자가 직접 확인·처리하도록 하며, 제7항은 변경·갱신 신청 시 기제출 서류의 재요구를 금지한다. 「전자정부법」 제36조제1항은 다른 행정기관으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있으면 같은 정보를 따로 수집하지 못하게 한다.
 [문제점] ① 신고 주체(법 제33조제1항: 소유자·설치운영자·임차인)의 동일성과 변경신고 대상인 대표자 변경(시행규칙 제17조제3항제1호)의 확인은 신고 처리에 실제로 필요한 심사 사항인데, 법령이 이를 확인할 서류나 확인 방법을 정하지 않아 부산청은 사업자등록증·법인 등기부등본을 법정 외 서류로 요구하고, 포항청도 "확인 목적"으로 제출받는다. 이는 민원처리법 제10조제1항에 반하는 상태가 법령 공백 때문에 상시화된 것이다. ② 두 서류 모두 행정정보 공동이용으로 확인 가능한 행정기관 발급 정보이므로 제10조제3항제3호에 따라 담당자가 직접 확인해야 하나, 시행규칙과 서식 어디에도 확인 조항·확인란·동의란이 없어 공동이용 절차를 시작할 근거가 없다(부산청은 공동이용 시스템을 이용한 적이 없음). ③ 변경신고의 '변경내용을 증명하는 서류'는 무엇을 내야 하는지 특정되지 않아 가장 빈번한 보완 사유가 된다. ④ 서식의 근거 조문 오기(제32조)는 신고인이 선박 관리인 조문을 찾게 하는 정합성 흠결이다.
 [논거] 신고 주체의 동일성·대표자 확인이라는 실질 확인의 근거는 법률(제33조제1항의 신고 주체 규정)과 부령(제17조제3항제1호)에 있고, 이를 확인할 서류·방법만 하위법령에 빠져 있는 유형이다. 법령에 없는 서류를 요구하는 실무를 법령에 맞추는 방법은 두 가지인데, 서류 요구를 중단하는 것은 확인을 불가능하게 하므로, 실무상 이미 요구되는 확인 사항을 서식의 '담당 공무원 확인사항'으로 옮겨 공동이용으로 대체하는 것이 민원처리법 제10조제3항·전자정부법 제36조제1항의 취지에 맞는 정비이다. 신고인에게 새로운 서류를 추가하는 것이 아니라 기존 요구 서류를 공동이용으로 대체하는 것이므로 규제 신설이 아니다.
 [개정 방향] ① (부령) 시행규칙 제17조에 "지방해양수산청장 또는 시·도지사는 「전자정부법」 제36조제1항에 따른 행정정보의 공동이용을 통하여 신고인의 법인 등기사항증명서(법인인 경우) 또는 사업자등록증명을 확인하여야 하며, 신고인이 확인에 동의하지 아니하는 경우에는 그 서류를 첨부하게 하여야 한다"는 확인 조항을 신설한다. ② (부령) 별지 제12호서식에 '담당 공무원 확인사항'란과 '행정정보 공동이용 동의서'란을 신설하고, 첨부서류 2번의 근거 조문을 '법 제36조'로 바로잡는다. ③ (부령) 제17조제4항제2호의 '변경내용을 증명하는 서류'를 변경 사유별로 예시한다(대표자·명칭 변경: ①의 공동이용 확인으로 갈음, 장소·규모 변경: 변경된 설치명세서·도면). 모두 부령만으로 가능하다.
-[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 한다. 1차 보고에서 '시행규칙 제17조에 공동이용 확인 조항이 있는 것으로 확인된다'고 적었던 서술은 지방해양수산청 안내문에 전재된 구 조문을 현행으로 오인한 것이며, 현행 제17조 원문에는 그러한 조항이 없음을 확인하여 바로잡았다. 법인 등기사항증명서·사업자등록증명이 지방해양수산청의 공동이용 대상 정보인지는 행정안전부(행정정보공동이용센터) 확인이 필요하며, 대상이 아니면 ①은 '신고인이 첨부' 방식으로만 정비한다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. 포항청 인터뷰이의 발언은 면담자의 유도 질문('실제로는 다 제출받으시는 거네요')에 대한 짧은 긍정이므로 입법사실의 강도는 부산청보다 약하다. [교차확인] 연번 11(부산청 인터뷰)과 동일 쟁점.</t>
+[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 한다. 일부 지방해양수산청 안내문에는 '담당 공무원은 전자정부법 제21조제1항에 따른 행정정보 공동이용으로 첨부서류 정보를 확인하여야 한다'는 구 조문이 실려 있으나 현행 제17조에는 그러한 조항이 없다. 법인 등기사항증명서·사업자등록증명이 지방해양수산청의 공동이용 대상 정보인지는 행정안전부(행정정보공동이용센터) 확인이 필요하며, 대상이 아니면 ①은 '신고인이 첨부' 방식으로만 정비한다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. 포항청 인터뷰이의 발언은 면담자의 유도 질문('실제로는 다 제출받으시는 거네요')에 대한 짧은 긍정이므로 입법사실의 강도는 부산청보다 약하다. [교차확인] 연번 11(부산청 인터뷰)과 동일 쟁점.</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>「행정절차법」 제40조제3항(보완 요구)·제4항(미보완 시 이유를 밝혀 되돌려 보냄), 「민원 처리에 관한 법률」 제22조제1항(보완 요구), 같은 법 시행령 제24조(보완 절차·기간 연장 2회)·제25조제1항(기간 내 미보완 시 반려)에 일반 근거가 있음(원문 확인).</t>
+          <t>「행정절차법」 제40조제3항(보완 요구)·제4항(미보완 시 이유를 밝혀 되돌려 보냄), 「민원 처리에 관한 법률」 제22조제1항(보완 요구), 같은 법 시행령 제24조(보완 절차·기간 연장 2회)·제25조제1항(기간 내 미보완 시 반려)에 일반 근거가 있음.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>해양수산부 FAQ·지방청 안내의 '최초신고 사업개시 후 30일, 폐업신고 폐업일부터 30일'(2차 자료)</t>
+          <t>해양수산부 FAQ·지방청 안내의 '최초신고 사업개시 후 30일, 폐업신고 폐업일부터 30일'(행정 안내문)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>현행 시행규칙 제17조제1항(최초신고)·제7항(폐업신고)에는 기한이 없음(원문 확인). 안내문의 30일은 조문 근거가 없는 것으로 확인됨.</t>
+          <t>현행 시행규칙 제17조제1항(최초신고)·제7항(폐업신고)에는 기한이 없음. 안내문의 30일은 조문 근거가 없음.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>법 제36조의2(제1항 소유자 안전점검 의무, 제2항 중대한 결함 시 지체 없이 보고(2017.10.31.), 제3항 3년 보관, 제4항 장관 직접 점검, 제5항 대행), 시행규칙 제20조의3(대상: 별표 1 제1호 가목·나목, 중대한 결함: 침하·균열, 해저송유관·호스·저장탱크·돌핀·원유송유용 부이 결함). 시정명령·사용제한 조항 없음(원문 확인). 같은 법 제38조의3은 오염물질저장시설에 대해서는 개선·운영정지·폐쇄명령을 둠.</t>
+          <t>법 제36조의2(제1항 소유자 안전점검 의무, 제2항 중대한 결함 시 지체 없이 보고(2017.10.31.), 제3항 3년 보관, 제4항 장관 직접 점검, 제5항 대행), 시행규칙 제20조의3(대상: 별표 1 제1호 가목·나목, 중대한 결함: 침하·균열, 해저송유관·호스·저장탱크·돌핀·원유송유용 부이 결함). 시정명령·사용제한 조항 없음. 같은 법 제38조의3은 오염물질저장시설에 대해서는 개선·운영정지·폐쇄명령을 둠.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 제17조제1항·제4항은 '전자문서로 된 신고서를 포함'하여 이미 전자 신고를 허용(원문 확인).</t>
+          <t>시행규칙 제17조제1항·제4항은 '전자문서로 된 신고서를 포함'하여 이미 전자 신고를 허용.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>법 제36조제1항(대통령령으로 정하는 자격을 갖춘 관리인 임명·보유)·제2항(해경에 임명 신고), 제121조제2호(관리인 자격 관련 교육·훈련과정), 시행규칙 제17조제1항제2호(임명확인서 첨부, 별표 1 제1호 시설 한정)에 근거가 있음(원문 확인). 교육 이수는 관리인 자격 요건이므로 첨부서류 요구는 법령 범위 안.</t>
+          <t>법 제36조제1항(대통령령으로 정하는 자격을 갖춘 관리인 임명·보유)·제2항(해경에 임명 신고), 제121조제2호(관리인 자격 관련 교육·훈련과정), 시행규칙 제17조제1항제2호(임명확인서 첨부, 별표 1 제1호 시설 한정)에 근거가 있음. 교육 이수는 관리인 자격 요건이므로 첨부서류 요구는 법령 범위 안.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>시행령 별표 19 일반기준 나목(질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력, 위반 정도·동기 등 2분의 1 범위 감경), 다목(2026.6.30. 신설: 고의·중과실 없는 소상공인 100분의 70 범위 감경)이 이미 있음(원문 확인).</t>
+          <t>시행령 별표 19 일반기준 나목(질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력, 위반 정도·동기 등 2분의 1 범위 감경), 다목(2026.6.30. 신설: 고의·중과실 없는 소상공인 100분의 70 범위 감경)이 이미 있음.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>폐업신고는 시행규칙 제17조제7항(별지 제16호서식, 기한 없음)에만 있고 법 제33조에는 폐업 신고 문언이 없음(원문 확인). 법 제33조제2항의 위임은 '신고·변경신고 절차'이므로 폐업신고 의무의 법률 근거가 불분명함. 주기적 현황 확인 의무 신설은 행정청 내부 사무.</t>
+          <t>폐업신고는 시행규칙 제17조제7항(별지 제16호서식, 기한 없음)에만 있고 법 제33조에는 폐업 신고 문언이 없음. 법 제33조제2항의 위임은 '신고·변경신고 절차'이므로 폐업신고 의무의 법률 근거가 불분명함. 주기적 현황 확인 의무 신설은 행정청 내부 사무.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 제17조제6항(별지 제15호서식 재발급신청서)에 심사 요건 없음(원문 확인). 사유 기재는 서식 항목으로 보임(서식 본문 미조회).</t>
+          <t>시행규칙 제17조제6항(별지 제15호서식 재발급신청서)에 심사 요건 없음. 사유 기재는 서식 항목으로 보임(서식 본문 미확인).</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>별지 제12호서식(개정 2024.6.28.) 첨부서류 2번은 '「해양환경관리법」 제32조에 따른 해양오염방지관리인의 임명확인서'로 적혀 있으나 제32조는 선박 해양오염방지관리인 조문이고, 시행규칙 제17조제1항제2호는 '법 제36조에 따른 해양시설해양오염방지관리인'을 인용함(원문 확인).</t>
+          <t>별지 제12호서식(개정 2024.6.28.) 첨부서류 2번은 '「해양환경관리법」 제32조에 따른 해양오염방지관리인의 임명확인서'로 적혀 있으나 제32조는 선박 해양오염방지관리인 조문이고, 시행규칙 제17조제1항제2호는 '법 제36조에 따른 해양시설해양오염방지관리인'을 인용함.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="100.5" customHeight="1">
+    <row r="18" ht="87" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>시행령 제94조제4항제2호·제6항제2호는 해양시설 신고·변경신고의 '접수'만 지방해양수산청장·시·도지사에게 위임하고, 제4항제2호의3은 오염물질저장시설 신고에 대해 '수리'를 위임함. 시행규칙 제17조제2항·제5항은 지방해양수산청장·시·도지사가 신고증명서를 발급하도록 함(원문 확인). 법 제33조제1항제1호는 국가관리연안항을 해양수산부장관 관할로 두는데 시행령 제6항제2호가 그 접수를 시·도지사에게 위임함.</t>
+          <t>시행령 제94조제4항제2호·제6항제2호는 해양시설 신고·변경신고의 '접수'만 지방해양수산청장·시·도지사에게 위임하고, 제4항제2호의3은 오염물질저장시설 신고에 대해 '수리'를 위임함. 시행규칙 제17조제2항·제5항은 지방해양수산청장·시·도지사가 신고증명서를 발급하도록 함. 법 제33조제1항제1호는 국가관리연안항을 해양수산부장관 관할로 두는데 시행령 제6항제2호가 그 접수를 시·도지사에게 위임함.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1591,207 +1591,190 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="87" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>확인 방법 공통</t>
+          <t>해양환경관리법</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026.10.12. 국가법령정보센터 DB(법제처 Open API 연동 korean-law MCP 커넥터)로 현행본 조회</t>
+          <t>2026.2.27. 공포, 2026.8.28. 시행(현행)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>이 세션의 실행 환경은 law.go.kr 등 웹 직접 접속이 차단되어, 1차(2026.10.12. 오전)는 웹 검색 요약(2차 자료)으로만 작성했고, 2차(같은 날 오후)에 커넥터로 조문·별표·서식 원문을 조회해 전부 재대조함. 아래 '원문'은 커넥터가 반환한 법제처 DB 본문을 뜻함. 근거 로그: notes/evidence_log.md.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="73.5" customHeight="1">
+          <t>확인 조문: 제2조제17호, 제33조(제1항 각 호 구분 2020.2.18. 개정, 변경신고 후단 2016.12.27. 개정, 제2항 2016.12.27. 개정), 제35조, 제36조, 제36조의2(제2항 2017.10.31. 개정), 제38조제3항(2023.10.24. 신설), 제38조의3, 제121조, 제123조, 제132조(제2항 500만원 이하, 제2호). 연혁: 2015.12.23. 시행본은 변경신고·시·도지사 구분 없음, 2019.8.20. 시행본은 변경신고 있음·시·도지사 구분 없음. 확인 상태: 현행 조문 원문.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="46.5" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>해양환경관리법</t>
+          <t>해양환경관리법 시행령</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026.2.27. 공포, 2026.8.28. 시행(현행, 법령ID 010379). 법률 번호는 2차 자료(로앤비) 기준 제21416호</t>
+          <t>2026.6.30. 공포, 2026.7.1. 시행(현행). 별표 19는 2026.6.30. 개정</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>원문 확인: 제2조제17호, 제33조(제1항 각 호 구분 2020.2.18. 개정, 변경신고 후단 2016.12.27. 개정, 제2항 2016.12.27. 개정), 제35조, 제36조, 제36조의2, 제38조제3항(2023.10.24. 신설), 제38조의3, 제121조, 제123조, 제132조(제2항 500만원 이하, 제2호). 연혁 대조: 2015.12.23. 시행본은 변경신고·시·도지사 구분 없음, 2019.8.20. 시행본은 변경신고 있음·시·도지사 구분 없음.</t>
+          <t>확인 조문: 제94조(권한의 위임) 제4항제2호·제2호의3·제25호, 제5항제1호·제1호의2, 제6항제2호·제4호(제1항은 2014.11.19. 삭제), 제98조, 별표 19 일반기준 가~다목·개별기준 너목(250만원)·더목(30만원)·러목~버목. 확인 상태: 현행 조문 원문.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>해양환경관리법 시행령</t>
+          <t>해양환경관리법 시행규칙</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026.6.30. 공포, 2026.7.1. 시행(현행, 법령ID 010632; 대통령령 제36478호는 2차 자료). 별표 19는 2026.6.30. 개정</t>
+          <t>2026.10.6. 공포·시행(현행)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>원문 확인: 제94조(권한의 위임) 제4항제2호·제2호의3·제25호, 제5항제1호·제1호의2, 제6항제2호·제4호(제1항은 2014.11.19. 삭제; 2차 자료의 '제94조 삭제'는 오류), 제98조, 별표 19 일반기준 가~다목·개별기준 너목(250만원)·더목(30만원)·러목~버목.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+          <t>확인 조문: 제3조(별표 1 인용), 제17조 제1항~제7항(제1항제3호 2024.6.28. 개정, 제3~5항 2017.6.28. 신설; 최초신고·폐업신고 기한 없음, 행정정보 공동이용 확인 조항 없음), 제19조 제1항·제3항~제6항, 제20조의3. 2023.12.28. 시행본과 대조하면 제17조는 제1항제3호의 대상 표현만 바뀜. 확인 상태: 현행 조문 원문.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="73.5" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>해양환경관리법 시행규칙</t>
+          <t>시행규칙 별표 1 해양시설의 범위(제3조 관련)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026.10.6. 공포·시행(현행, 법령ID 010636; 해양수산부령 번호 미확인)</t>
+          <t>개정 2020.12.4.(현행)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>원문 확인: 제3조(별표 1 인용), 제17조 제1항~제7항(제1항제3호 2024.6.28. 개정, 제3~5항 2017.6.28. 신설; 최초신고·폐업신고 기한 없음, 공동이용 확인 조항 없음), 제19조 제1항·제3항~제6항, 제20조의3. 2023.12.28. 시행본과 대조: 제17조는 제1항제3호의 대상 표현만 바뀜.</t>
+          <t>전문 확인. 제1호 가~마목, 제2호 가~라목(라목 '그 밖의 시설': 해상송전철탑·해저광케이블·해상부유구조물), 제3호 종합해양과학기지, 비고 1·2. 2013.3.24. 개정본과의 차이는 제1호 마목의 인용 법령명(해양폐기물 및 해양오염퇴적물관리법)뿐. 제1호 라목이 재위임한 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비' 고시는 국가법령정보센터 행정규칙 검색에서 확인되지 않음(해양수산부 확인 필요).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="73.5" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 별표 1 해양시설의 범위(제3조 관련)</t>
+          <t>시행규칙 별지 제12호·제14호·제16호서식</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>개정 2020.12.4.(현행). 2020.6.1. 기준 조회본은 개정 2013.3.24. 표기</t>
+          <t>제12호 개정 2024.6.28., 제14호 개정 2015.1.8., 제16호 개정 2021.1.7.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>원문 확인(전문). 제1호 가~마목, 제2호 가~라목(라목 '그 밖의 시설': 해상송전철탑·해저광케이블·해상부유구조물), 제3호 종합해양과학기지, 비고 1·2. 2013년 개정본과의 차이는 제1호 마목의 인용 법령명(해양폐기물 및 해양오염퇴적물관리법)뿐. 제1호 라목이 재위임한 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비' 고시는 행정규칙 DB 검색('해양시설' 고시 10건, '하역설비' 0건, '계류시설' 1건)에서 확인되지 않음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="73.5" customHeight="1">
+          <t>서식 원문 확인. 제12호: 처리기간 (최초)7일 (변경)5일, 신고인란·신고내용란·첨부서류란(최초 3종, 변경 2종), 담당 공무원 확인사항란·공동이용 동의란 없음, 첨부서류 2번 근거 조문 '법 제32조' 오기, 뒤쪽 처리절차(접수→검토→결재→신고증명서 발급). 제14호: '신고하였음을 증명합니다', 뒤쪽 변경사항란. 제16호: 처리기간 3일, 구비서류 신고증명서 원본, 수수료 없음. 제13호·제15호는 서식 제목만 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>시행규칙 별지 제12호·제14호·제16호서식</t>
+          <t>행정기본법 제34조</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>제12호 개정 2024.6.28., 제14호 개정 2015.1.8., 제16호 개정 2021.1.7.</t>
+          <t>2025.3.18. 공포본</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>원문 확인. 제12호: 처리기간 (최초)7일 (변경)5일, 신고인란·신고내용란·첨부서류란(최초 3종, 변경 2종), 담당 공무원 확인사항란·공동이용 동의란 없음, 첨부서류 2번 근거 조문 '법 제32조' 오기, 뒤쪽 처리절차(접수→검토→결재→신고증명서 발급). 제14호: '신고하였음을 증명합니다', 뒤쪽 변경사항란. 제16호: 처리기간 3일, 구비서류 신고증명서 원본, 수수료 없음. 제13호·제15호는 서식 목록으로만 확인.</t>
+          <t>조문 원문 확인. 문언은 본표 [현행 규정]과 같음.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>행정기본법 제34조</t>
+          <t>행정절차법 제40조</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2025.3.18. 공포본(법령ID 014041)</t>
+          <t>2022.1.11. 공포, 2022.7.12. 시행본</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>원문 확인. 문언은 본표 [현행 규정]과 같음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="33" customHeight="1">
+          <t>조문 원문 확인. 제1항~제4항.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46.5" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>행정절차법 제40조</t>
+          <t>민원 처리에 관한 법률 제10조·제19조·제22조, 같은 법 시행령 제24조·제25조</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2022.1.11. 공포, 2022.7.12. 시행본(법령ID 001362)</t>
+          <t>법률 2022.1.11. 공포본(2026.12.3. 시행 예정 타법개정 있음), 시행령 2026.5.6. 공포·시행본</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>원문 확인. 제1항~제4항.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+          <t>조문 원문 확인. 제10조제1항·제3항(제3호: 전자정부법 제36조제1항 공동이용)·제7항(변경·갱신 시 재요구 금지), 제19조제1항·제2항, 제22조제1항, 시행령 제24조제1항~제3항, 제25조제1항.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="33" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>민원 처리에 관한 법률 제10조·제19조·제22조, 같은 법 시행령 제24조·제25조</t>
+          <t>전자정부법 제36조</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>법률 2022.1.11. 공포본(법령ID 001359; 2026.12.3. 시행 예정 타법개정 있음), 시행령 2026.5.6. 공포·시행본</t>
+          <t>2026.2.27. 공포, 2026.8.28. 시행본</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>원문 확인. 제10조제1항·제3항(제3호: 전자정부법 제36조제1항 공동이용)·제7항(변경·갱신 시 재요구 금지; 1차 보고의 '제4항' 표기는 오류), 제19조제1항·제2항, 제22조제1항, 시행령 제24조제1항~제3항, 제25조제1항.</t>
+          <t>조문 원문 확인. 제1항: 다른 행정기관등으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있는 경우 같은 내용의 정보를 따로 수집하여서는 아니 됨.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>전자정부법 제36조</t>
+          <t>질서위반행위규제법 제6조</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026.2.27. 공포, 2026.8.28. 시행본(법령ID 009199)</t>
+          <t>2026.3.24. 공포, 2026.10.2. 시행본</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>원문 확인. 제1항: 다른 행정기관등으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있는 경우 같은 내용의 정보를 따로 수집하여서는 아니 됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="33" customHeight="1">
+          <t>조문 원문 확인. '법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="100.5" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>질서위반행위규제법 제6조</t>
+          <t>행정 안내 자료: 해양수산부 FAQ '해양시설이란 무엇이고, 신고시 구비서류는'(군산지방해양수산청 안내 전재), 정부24 '해양시설 최초(변경)신고', 국토교통부 정책정보(구 국토해양부 업무 안내), 목포·인천·군산지방해양수산청 홈페이지 안내</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026.3.24. 공포, 2026.10.2. 시행본(법령ID 010592)</t>
+          <t>작성일 미확인</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>원문 확인. '법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다.'</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="87" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2차 자료: 해양수산부 FAQ '해양시설이란 무엇이고, 신고시 구비서류는'(군산청 안내 전재), 정부24 '해양시설 최초(변경)신고', 국토교통부 정책정보(구 국토해양부 업무 안내), 목포·인천·군산청 안내</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>작성일 미확인</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>원문과 다른 내용: ① '최초신고 사업개시 후 30일 이내', '폐업신고 폐업일부터 30일 이내'는 현행 조문에 없음. ② 인천청 안내에 전재된 '전자정부법 제21조제1항에 따른 공동이용 확인' 조문은 현행 시행규칙 제17조에 없음. ③ 변경신고 도입을 2013년 또는 2017.3.21.로 적은 자료는 오류(2016.12.27. 법률 개정, 2017.6.28. 시행규칙 신설). ④ 일부 자료의 '시행령 제94조 삭제'는 오류. 처리기간 7일·5일, 첨부서류, 변경신고 대상·30일은 원문과 일치.</t>
+          <t>법령 원문과 다른 내용: ① '최초신고 사업개시 후 30일 이내', '폐업신고 폐업일부터 30일 이내'는 현행 조문에 없음. ② 인천청 안내에 실린 '전자정부법 제21조제1항에 따른 공동이용 확인' 조문은 현행 시행규칙 제17조에 없음. ③ 변경신고 도입 시기를 2013년 또는 2017.3.21.로 적은 자료는 오류(2016.12.27. 법률 개정, 2017.6.28. 시행규칙 신설). 처리기간 7일·5일, 첨부서류, 변경신고 대상·30일은 원문과 일치.</t>
         </is>
       </c>
     </row>

--- a/해양시설신고/output/261012_입법영향분석_해양시설신고_법령개정_필요사항.xlsx
+++ b/해양시설신고/output/261012_입법영향분석_해양시설신고_법령개정_필요사항.xlsx
@@ -449,15 +449,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="200" customWidth="1" min="6" max="6"/>
     <col width="250" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -498,13 +498,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="343.5" customHeight="1">
+    <row r="2" ht="384" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026.9.3.</t>
+          <t>2026.9.3.
+2026.9.8.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -514,8 +515,10 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>군산지방해양수산청 해양수산환경과 7급 주무관 신재민(해양시설 신고·변경신고 접수 및 등록·관리, 담당 1년 6개월)
-면담자: 오세영, 김현빈 / 비대면(ZOOM)</t>
+          <t>〈군산청〉 군산지방해양수산청 해양수산환경과 7급 주무관 신재민(해양시설 신고·변경신고 접수 및 등록·관리, 담당 1년 6개월)
+면담자: 오세영, 김현빈 / 비대면(ZOOM)
+〈부산청〉 부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
+면담자: 오세영, 김현빈 / 비대면(Webex)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -531,8 +534,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>[인터뷰 내용] 시행규칙 별표 1의 해양시설 범위가 '계류시설(돌핀)', '하역설비' 등 일반 용어만으로 기재되어 다른 법령(항만운송사업법 등)의 시설 정의와 연계가 없고, 표현이 열려 있어 여러 해석이 가능하다. 담당자가 바뀌면 유사 시설에 대한 판단이 달라질 여지가 조금 있다고 인정했다.
-[발언] 신재민: "법률 용어가 좀 더 명확하면 좋겠습니다." / 신재민: "해양시설의 범위라는 것에서, 계류시설 괄호 치고 '돌핀'이라고만 쓰여 있고, 이렇게 일반적인 용어들만 써 놓았습니다. 법에서 한번 정의를 하고 가면, 즉 '어떤 법의 어떤 시설'이라는 식으로 정하고 가는 게 더 낫지 않나 싶습니다." / 신재민: "법률 제2조 정의 규정에서도 다른 항만시설 관련 규정과 연계가 잘 안 되어 있는 것 같습니다. 이 법에서만 이런 용어를 쓰는 것 같아서, 다른 법과 유기적으로 연계되어야 '이 법이 어떤 시설물을 대상으로 하는구나'라는 게 명확해질 것 같습니다." / 신재민: "해양시설 쪽 범위에는 '해양수산부장관이 정하여 고시하는 계류시설·하역설비' 정도로만 나와 있습니다. 이게 어떤 법을 준용해서 하역시설이라고 하는 건지 명확하지 않고, '하역'이라는 말 자체도 너무 광범위합니다." / 신재민: "아예 정의를 하지 않다 보니, 고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐는 문제가 또 생길 수 있습니다." / 신재민: "여기 나와 있는 표현들이 좀 너무 열려 있다고 해야 할지, 여러 가지로 해석될 수 있는 여지가 있습니다." / (면담자 오세영) "동일하거나 유사한 시설에 대해 담당자가 달라지면 다른 판단이 내려질 수도 있다는 우려가 있으신가요?" / 신재민: "그정도까지 복잡한 것은 아니어서 조금 있다고 볼 수 있습니다."</t>
+          <t>〈군산청 인터뷰〉
+[인터뷰 내용] 시행규칙 별표 1의 해양시설 범위가 '계류시설(돌핀)', '하역설비' 등 일반 용어만으로 기재되어 다른 법령(항만운송사업법 등)의 시설 정의와 연계가 없고, 표현이 열려 있어 여러 해석이 가능하다. 담당자가 바뀌면 유사 시설에 대한 판단이 달라질 여지가 조금 있다고 인정했다.
+[발언] 신재민: "법률 용어가 좀 더 명확하면 좋겠습니다." / 신재민: "해양시설의 범위라는 것에서, 계류시설 괄호 치고 '돌핀'이라고만 쓰여 있고, 이렇게 일반적인 용어들만 써 놓았습니다. 법에서 한번 정의를 하고 가면, 즉 '어떤 법의 어떤 시설'이라는 식으로 정하고 가는 게 더 낫지 않나 싶습니다." / 신재민: "법률 제2조 정의 규정에서도 다른 항만시설 관련 규정과 연계가 잘 안 되어 있는 것 같습니다. 이 법에서만 이런 용어를 쓰는 것 같아서, 다른 법과 유기적으로 연계되어야 '이 법이 어떤 시설물을 대상으로 하는구나'라는 게 명확해질 것 같습니다." / 신재민: "해양시설 쪽 범위에는 '해양수산부장관이 정하여 고시하는 계류시설·하역설비' 정도로만 나와 있습니다. 이게 어떤 법을 준용해서 하역시설이라고 하는 건지 명확하지 않고, '하역'이라는 말 자체도 너무 광범위합니다." / 신재민: "아예 정의를 하지 않다 보니, 고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐는 문제가 또 생길 수 있습니다." / 신재민: "여기 나와 있는 표현들이 좀 너무 열려 있다고 해야 할지, 여러 가지로 해석될 수 있는 여지가 있습니다." / (면담자 오세영) "동일하거나 유사한 시설에 대해 담당자가 달라지면 다른 판단이 내려질 수도 있다는 우려가 있으신가요?" / 신재민: "그정도까지 복잡한 것은 아니어서 조금 있다고 볼 수 있습니다."
+〈부산청 인터뷰〉
+[인터뷰 내용] 해양시설 신고 대상 여부 문의가 많고 별표 1 문구가 애매하여 담당자 간에도 혼선이 있다. 육상 송전철탑과 바다 위 송전선로가 이어진 한전 시설처럼 육상·해상에 걸친 시설의 범위 판단이 어렵고, 해수부 본부도 다른 지방청에 문의하라고 안내하며 지방청마다 판단이 달라 어느 지방청에는 신고되고 어느 지방청에는 신고되지 않은 사례가 있었다. 범위가 모호한 점이 가장 큰 문제라고 했다.
+[발언] 윤혜림: "별표 1이 제가 보기에도 다소 애매하게 느껴져서 담당자들 사이에서도 혼선이 있는 경우가 많았습니다." / 윤혜림: "별표에 '등'이라는 표현이라도 있으면 예시로 안내해 드릴 수 있었을 텐데, 그런 표현 없이 항목만 나열되어 있다 보니 범위를 설명드리기가 애매했습니다." / 윤혜림: "해수부에 문의를 해도 실무를 직접 담당하지 않다 보니 본부에서도 다른 지방청에 문의해 보라고 안내하는 경우가 많고, 지방청마다 판단이 다 달라서 결국 애매한 상태로 남는 경우가 많습니다." / 윤혜림: "한전에서 어느 지방청에는 신청을 하고 어느 지방청에는 하지 않는 등, 저희 쪽에는 신청이 없고 다른 지방청에는 있는 상황이었다고 들었습니다. 담당자별로 완전히 다르게 처리된 사례였습니다." / 윤혜림: "우선 해양시설의 범위 자체가 모호하다는 점이 가장 큰 문제라고 생각합니다."</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -540,18 +547,19 @@
           <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 규정에 따른 항만을 포함한다)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제3조가 이를 별표 1의 시설로 정한다. 별표 1(개정 2020.12.4.)은 ① 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 목적 시설)에 가목 기름·유해액체물질 저장시설 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 나목 법 제38조의 오염물질저장시설, 다목 선박 건조·수리·해체시설 '저장시설, 상가시설 및 수리시설(이동식 시설은 제외)', 라목 시멘트·석탄·사료·곡물·고철·광석·목재·토사의 하역시설 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 마목 폐기물해양배출업자의 폐기물저장시설을, ② 제2호(해양레저·관광·주거·해수이용 등 목적 시설)에 가목 연면적 100㎡ 이상 해상관광·주거·음식점 시설(범위: 해역 안 시설, 해역과 육지 사이 연속 시설은 취수·배수 시설(배관 포함)), 나목 관경 600㎜ 이상 취수·배수시설, 다목 유어장, 라목 '그 밖의 시설'의 범위로 '해상송전철탑, 해저광케이블, 해상부유구조물'을, ③ 제3호에 종합해양과학기지를 열거한다. 라목의 계류시설·하역설비를 정하는 해양수산부 고시는 국가법령정보센터 행정규칙 검색에서 확인되지 않았다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다.
 [문제점] ① 별표 1의 '계류시설(돌핀)', '하역설비', '저장시설', '상가시설' 등은 「항만법」(항만시설), 「항만운송사업법」(항만하역), 「위험물안전관리법」 등 다른 법령의 시설 분류와 연계 없이 일반 용어로만 기재되어 있어, 같은 물적 시설이 신고 대상인지 담당자마다 판단이 갈린다(인터뷰이: "이 법에서만 이런 용어를 쓰는 것 같아서"). ② 제1호 라목은 대상 특정을 해양수산부 고시에 재위임하는데 해당 고시가 확인되지 않는다. 고시가 없으면 별표 문언만으로는 "고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐"는 범위 문제가 생긴다(위임사항 미이행). ③ 별표는 제2호 가목에 대해서만 해역·육지 연속 시설의 신고 범위 기준(취수·배수 시설)을 두고, 제2호 라목 '그 밖의 시설'은 '해상송전철탑, 해저광케이블, 해상부유구조물'의 닫힌 열거여서 육상 철탑 사이를 해상으로 지나는 송전선로처럼 해역과 육지에 걸친 시설의 어느 부분이 신고 대상인지 판단 기준이 없다. ④ 제2호 가목은 「선박안전법」상 선박을 제외하는 등 제외 규정을 두면서 제1호 시설에는 다른 법령에 따른 안전관리 대상과의 중복 처리 기준이 없어 "다른 법령과 중복이 되어도 되는 건지" 불명확하다. ⑤ 신고 대상 여부가 과태료 부과의 구성요건이므로 대상 범위의 불명확은 곧 제재 요건의 불명확이다.
 [논거] 법 제2조제17호가 대상 시설의 특정을 부령에 포괄 위임하고 별표 1이 다시 고시에 재위임하는 구조에서, 최종 단계(고시)가 비어 있거나 문언이 열려 있으면 신고 의무(법 제33조제1항)와 과태료(법 제132조제2항제2호, 「질서위반행위규제법」 제6조의 법정주의)의 적용 범위가 법령 문언으로 확정되지 않는다. 의무 부과·제재의 구성요건은 수범자가 예측할 수 있을 정도로 명확해야 한다는 명확성 원칙과 위임입법의 한계(위임받은 사항을 하위법령이 정하지 않은 상태) 문제이며, 담당자 해석이나 질의회신으로 보충할 사항이 아니라 별표·고시 문언 자체의 정비 사항이다. 인터뷰이가 유사 시설에 대해 담당자별 판단이 달라질 수 있다고 인정한 점("조금 있다고 볼 수 있습니다")은 평등 원칙 차원의 문제이기도 하다.
-[개정 방향] ① (부령) 별표 1 각 항목에 근거 법령상 시설 분류를 인용하도록 문언을 고친다. 예: 계류시설은 「항만법」상 항만시설 중 계류시설의 세부 종류로, 하역시설은 「항만운송사업법」상 항만하역 시설로 특정하고, 그 밖의 시설은 '○○법 제○조에 따른 ○○시설' 형식으로 쓴다. ② (부령·고시) 제1호 라목의 '해양수산부장관이 정하여 고시하는' 부분은 고시를 제정하거나, 고시 없이 별표에 직접 열거하는 방식으로 재위임을 해소한다. ③ (부령) 제2호 가목에만 있는 해역·육지 연속 시설의 범위 기준을 별표 비고로 옮겨 제1호·제2호 전체에 적용되는 공통 기준(예: 해역 안에 설치된 부분과 그에 연속한 배관·선로)으로 두고, 다른 법령에 따른 안전관리 대상 시설과의 관계(중복 적용 여부, 제외 사유)를 비고에 명시한다. ④ (법률, 선택) 법 제2조제17호의 포괄 위임을 완화하여 시설 유형(기름·유해액체물질의 저장·이송·계류, 취수·배수, 해양레저·관광 등)을 법률에 예시로 열거하고 세부를 부령에 위임한다. 최소 정비안은 ①~③(부령·고시)만으로 가능하다. 연번 2(부산청)와 연계.
-[유의] 별표 1(개정 2020.12.4.)은 2013.3.24. 개정본과 비교해 제1호 마목의 인용 법령명만 바뀌었을 뿐 '해상송전철탑' 등은 2013년부터 열거되어 있었다. 고시는 국가법령정보센터에 등재되지 않은 것일 수 있으므로 해양수산부에 제정 여부를 확인해야 한다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 인터뷰이는 돌핀·하역설비의 정의 연계를 희망하면서도 "그정도까지 복잡한 것은 아니"라고 하여 입법사실의 규모는 크지 않다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="370.5" customHeight="1">
+[개정 방향] ① (부령) 별표 1 각 항목에 근거 법령상 시설 분류를 인용하도록 문언을 고친다. 예: 계류시설은 「항만법」상 항만시설 중 계류시설의 세부 종류로, 하역시설은 「항만운송사업법」상 항만하역 시설로 특정하고, 그 밖의 시설은 '○○법 제○조에 따른 ○○시설' 형식으로 쓴다. ② (부령·고시) 제1호 라목의 '해양수산부장관이 정하여 고시하는' 부분은 고시를 제정하거나, 고시 없이 별표에 직접 열거하는 방식으로 재위임을 해소한다. ③ (부령) 제2호 가목에만 있는 해역·육지 연속 시설의 범위 기준을 별표 비고로 옮겨 제1호·제2호 전체에 적용되는 공통 기준(예: 해역 안에 설치된 부분과 그에 연속한 배관·선로)으로 두고, 다른 법령에 따른 안전관리 대상 시설과의 관계(중복 적용 여부, 제외 사유)를 비고에 명시한다. ④ (법률, 선택) 법 제2조제17호의 포괄 위임을 완화하여 시설 유형(기름·유해액체물질의 저장·이송·계류, 취수·배수, 해양레저·관광 등)을 법률에 예시로 열거하고 세부를 부령에 위임한다. 최소 정비안은 ①~③(부령·고시)만으로 가능하다.
+[유의] 부산청의 한전 사례는 별표 1 제2호 라목이 '해상송전철탑'만 열거하고 육상 철탑 사이의 해상 선로 구간을 어떻게 볼지 기준이 없는 데서 생긴 것이므로 [개정 방향] ③의 공통 범위 기준이 직접 대응한다. 한전 사례는 부산청 인터뷰이가 다른 지방청의 처리 결과를 전해 들은 것이므로 교차 확인이 필요하다. 부산청 인터뷰이는 '등' 같은 예시 표현을 희망했으나 예시 규정은 대상 확대로 읽힐 수 있어 근거 법령 인용과 범위 기준 명시가 더 안전하다. 별표 1(개정 2020.12.4.)은 2013.3.24. 개정본과 비교해 제1호 마목의 인용 법령명만 바뀌었을 뿐 '해상송전철탑' 등은 2013년부터 열거되어 있었다. 고시는 국가법령정보센터에 등재되지 않은 것일 수 있으므로 해양수산부에 제정 여부를 확인해야 한다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 군산청 인터뷰이는 돌핀·하역설비의 정의 연계를 희망하면서도 "그정도까지 복잡한 것은 아니"라고 하여 입법사실의 규모는 크지 않다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="409" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026.9.8.</t>
+          <t>2026.9.3.
+2026.9.8.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -561,58 +569,15 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
+          <t>〈군산청〉 군산지방해양수산청 해양수산환경과 7급 주무관 신재민(해양시설 신고·변경신고 접수 및 등록·관리, 담당 1년 6개월)
+면담자: 오세영, 김현빈 / 비대면(ZOOM)
+〈포항청〉 포항지방해양수산청 해양수산환경과 7급 주무관 조호영(해양시설 신고·변경신고, 담당 약 3년, 기술직)
+면담자: 오세영 / 근무지 방문
+〈부산청〉 부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
 면담자: 오세영, 김현빈 / 비대면(Webex)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>「해양환경관리법」 제2조제17호(해양시설 정의: 해양수산부령 위임)
-법 제33조제1항(신고 의무)
-법 제132조제2항제2호(신고 미이행 과태료)
-시행규칙 제3조(법 제2조제17호의 시설 = 별표 1)
-시행규칙 별표 1 해양시설의 범위(제3조 관련, 개정 2020.12.4.) 제1호 가목·다목·라목, 제2호 가목·나목·라목
-별표 1 제1호 라목이 재위임한 해양수산부 고시(제정 여부 확인되지 않음)
-시행령 별표 19(과태료 부과기준)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 해양시설 신고 대상 여부 문의가 많고 별표 1 문구가 애매하여 담당자 간에도 혼선이 있다. 육상 송전철탑과 바다 위 송전선로가 이어진 한전 시설처럼 육상·해상에 걸친 시설의 범위 판단이 어렵고, 해수부 본부도 다른 지방청에 문의하라고 안내하며 지방청마다 판단이 달라 어느 지방청에는 신고되고 어느 지방청에는 신고되지 않은 사례가 있었다. 범위가 모호한 점이 가장 큰 문제라고 했다.
-[발언] 윤혜림: "별표 1이 제가 보기에도 다소 애매하게 느껴져서 담당자들 사이에서도 혼선이 있는 경우가 많았습니다." / 윤혜림: "별표에 '등'이라는 표현이라도 있으면 예시로 안내해 드릴 수 있었을 텐데, 그런 표현 없이 항목만 나열되어 있다 보니 범위를 설명드리기가 애매했습니다." / 윤혜림: "해수부에 문의를 해도 실무를 직접 담당하지 않다 보니 본부에서도 다른 지방청에 문의해 보라고 안내하는 경우가 많고, 지방청마다 판단이 다 달라서 결국 애매한 상태로 남는 경우가 많습니다." / 윤혜림: "한전에서 어느 지방청에는 신청을 하고 어느 지방청에는 하지 않는 등, 저희 쪽에는 신청이 없고 다른 지방청에는 있는 상황이었다고 들었습니다. 담당자별로 완전히 다르게 처리된 사례였습니다." / 윤혜림: "우선 해양시설의 범위 자체가 모호하다는 점이 가장 큰 문제라고 생각합니다."</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 법 제2조제17호는 해양시설을 "해역(「항만법」 제2조제1호의 규정에 따른 항만을 포함한다)의 안 또는 해역과 육지 사이에 연속하여 설치·배치하거나 투입되는 시설 또는 구조물로서 해양수산부령이 정하는 것"으로 정의하고, 시행규칙 제3조가 이를 별표 1의 시설로 정한다. 별표 1(개정 2020.12.4.)은 ① 제1호(기름·유해액체물질·폐기물 등의 공급·처리·저장 목적 시설)에 가목 기름·유해액체물질 저장시설 '계류시설(돌핀), 선박과 저장시설을 연결하는 이송설비, 저장시설, 자가처리시설', 나목 법 제38조의 오염물질저장시설, 다목 선박 건조·수리·해체시설 '저장시설, 상가시설 및 수리시설(이동식 시설은 제외)', 라목 시멘트·석탄·사료·곡물·고철·광석·목재·토사의 하역시설 '해양수산부장관이 정하여 고시하는 계류시설, 하역설비(컨베이어 벨트를 포함한다)', 마목 폐기물해양배출업자의 폐기물저장시설을, ② 제2호(해양레저·관광·주거·해수이용 등 목적 시설)에 가목 연면적 100㎡ 이상 해상관광·주거·음식점 시설(범위: 해역 안 시설, 해역과 육지 사이 연속 시설은 취수·배수 시설(배관 포함)), 나목 관경 600㎜ 이상 취수·배수시설, 다목 유어장, 라목 '그 밖의 시설'의 범위로 '해상송전철탑, 해저광케이블, 해상부유구조물'을, ③ 제3호에 종합해양과학기지를 열거한다. 라목의 계류시설·하역설비를 정하는 해양수산부 고시는 국가법령정보센터 행정규칙 검색에서 확인되지 않았다. 신고 의무 위반은 법 제132조제2항제2호·시행령 별표 19에 따라 과태료 250만원 대상이다.
-[문제점] ① 별표 1의 '계류시설(돌핀)', '하역설비', '저장시설', '상가시설' 등은 「항만법」(항만시설), 「항만운송사업법」(항만하역), 「위험물안전관리법」 등 다른 법령의 시설 분류와 연계 없이 일반 용어로만 기재되어 있어, 같은 물적 시설이 신고 대상인지 담당자마다 판단이 갈린다(인터뷰이: "이 법에서만 이런 용어를 쓰는 것 같아서"). ② 제1호 라목은 대상 특정을 해양수산부 고시에 재위임하는데 해당 고시가 확인되지 않는다. 고시가 없으면 별표 문언만으로는 "고정식으로 쓰이는 하역설비면 전부 해양시설로 등록해야 하느냐"는 범위 문제가 생긴다(위임사항 미이행). ③ 별표는 제2호 가목에 대해서만 해역·육지 연속 시설의 신고 범위 기준(취수·배수 시설)을 두고, 제2호 라목 '그 밖의 시설'은 '해상송전철탑, 해저광케이블, 해상부유구조물'의 닫힌 열거여서 육상 철탑 사이를 해상으로 지나는 송전선로처럼 해역과 육지에 걸친 시설의 어느 부분이 신고 대상인지 판단 기준이 없다. ④ 제2호 가목은 「선박안전법」상 선박을 제외하는 등 제외 규정을 두면서 제1호 시설에는 다른 법령에 따른 안전관리 대상과의 중복 처리 기준이 없어 "다른 법령과 중복이 되어도 되는 건지" 불명확하다. ⑤ 신고 대상 여부가 과태료 부과의 구성요건이므로 대상 범위의 불명확은 곧 제재 요건의 불명확이다.
-[논거] 법 제2조제17호가 대상 시설의 특정을 부령에 포괄 위임하고 별표 1이 다시 고시에 재위임하는 구조에서, 최종 단계(고시)가 비어 있거나 문언이 열려 있으면 신고 의무(법 제33조제1항)와 과태료(법 제132조제2항제2호, 「질서위반행위규제법」 제6조의 법정주의)의 적용 범위가 법령 문언으로 확정되지 않는다. 의무 부과·제재의 구성요건은 수범자가 예측할 수 있을 정도로 명확해야 한다는 명확성 원칙과 위임입법의 한계(위임받은 사항을 하위법령이 정하지 않은 상태) 문제이며, 담당자 해석이나 질의회신으로 보충할 사항이 아니라 별표·고시 문언 자체의 정비 사항이다. 인터뷰이가 유사 시설에 대해 담당자별 판단이 달라질 수 있다고 인정한 점("조금 있다고 볼 수 있습니다")은 평등 원칙 차원의 문제이기도 하다.
-[개정 방향] ① (부령) 별표 1 각 항목에 근거 법령상 시설 분류를 인용하도록 문언을 고친다. 예: 계류시설은 「항만법」상 항만시설 중 계류시설의 세부 종류로, 하역시설은 「항만운송사업법」상 항만하역 시설로 특정하고, 그 밖의 시설은 '○○법 제○조에 따른 ○○시설' 형식으로 쓴다. ② (부령·고시) 제1호 라목의 '해양수산부장관이 정하여 고시하는' 부분은 고시를 제정하거나, 고시 없이 별표에 직접 열거하는 방식으로 재위임을 해소한다. ③ (부령) 제2호 가목에만 있는 해역·육지 연속 시설의 범위 기준을 별표 비고로 옮겨 제1호·제2호 전체에 적용되는 공통 기준(예: 해역 안에 설치된 부분과 그에 연속한 배관·선로)으로 두고, 다른 법령에 따른 안전관리 대상 시설과의 관계(중복 적용 여부, 제외 사유)를 비고에 명시한다. ④ (법률, 선택) 법 제2조제17호의 포괄 위임을 완화하여 시설 유형(기름·유해액체물질의 저장·이송·계류, 취수·배수, 해양레저·관광 등)을 법률에 예시로 열거하고 세부를 부령에 위임한다. 최소 정비안은 ①~③(부령·고시)만으로 가능하다. 연번 1(군산청)과 연계. 부산청의 한전 사례는 별표 1 제2호 라목이 '해상송전철탑'만 열거하고 육상 철탑 사이의 해상 선로 구간을 어떻게 볼지 기준이 없는 데서 생긴 것이므로 ③의 공통 범위 기준이 직접 대응한다.
-[유의] 별표 1(개정 2020.12.4.)은 2013.3.24. 개정본과 비교해 제1호 마목의 인용 법령명만 바뀌었을 뿐 '해상송전철탑' 등은 2013년부터 열거되어 있었다. 고시는 국가법령정보센터에 등재되지 않은 것일 수 있으므로 해양수산부에 제정 여부를 확인해야 한다. 별표 개정으로 대상 시설이 늘어나면 규제 신설에 해당하므로 정비는 기존 대상의 명확화에 한정해야 한다. 포항청 조호영은 관할 시설이 취수·배수시설과 저장탱크 위주여서 대상 판단에 어려움이 없다고 하였다(검토메모 참조). 한전 송전철탑 사례는 인터뷰이가 다른 지방청의 처리 결과를 전해 들은 것이므로 교차 확인이 필요하다. 인터뷰이는 '등' 같은 예시 표현을 희망했으나 예시 규정은 대상 확대로 읽힐 수 있어 근거 법령 인용과 범위 기준 명시가 더 안전하다. [교차확인] 연번 1(군산청 인터뷰)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="409" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.3.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>군산지방해양수산청 해양수산환경과 7급 주무관 신재민(해양시설 신고·변경신고 접수 및 등록·관리, 담당 1년 6개월)
-면담자: 오세영, 김현빈 / 비대면(ZOOM)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>「해양환경관리법」 제33조제1항·제2항
 법 제38조제3항(오염물질저장시설 신고의 수리 여부 통지, 2023.10.24. 신설 — 비교 조문)
@@ -624,139 +589,53 @@
 「민원 처리에 관한 법률」 제19조·제22조제1항, 같은 법 시행령 제24조·제25조</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 처리기간과 효력 발생 시점이 법령에 없어 국민신문고 처리기한(최초 7일)을 따르고, 해양시설만 별도로 정한 행정규칙도 없다. 신고 서류를 확인하고 현장 실사를 거쳐 신고증(확인서)을 발급하며, 효력은 증명서가 발급되어야 발생한다고 본다. 심사는 형식만 보지만 신고제도여서 실질 문제로 보완·반려할 법적 규정이 없다. 최초신고와 시설 규모·위치 변경은 수리를 요하는 신고로 유지하고 소유자 변경은 자기완결적 신고로 바꿔도 된다고 본다.
-[발언] 신재민: "해양환경관리법에 해양시설만 별도로 정한 행정규칙 같은 것은 없는 것으로 알고 있습니다. 그리고 해양시설 등록 최초 신고는 국민신문고 기준으로 7일로 나와 있습니다." / 신재민: "이거는 등록 제도처럼 요건이 있습니다. 신고인 일치 여부도 확인해야 하고, 시설 소유자 관련 증빙 같은 것도 받고 있습니다." / 신재민: "설치 장소가 신고된 번지에 있는지, 그 정도 규모가 있는지를 확인하고, 서류상 문제가 없으면 바로 신고증(확인서)이 나갑니다." / (면담자 오세영) "그러면 신고가 접수되고 신고 서류가 도달했을 때 효력이 발생하는 것이 아니라, 주무관님과 같은 담당자의 검토가 끝났을 때, 특히 증명서가 발급되어야 그때부터 신고의 효력이 발생한다고 보면 될까요?" / 신재민: "네 맞습니다." / 신재민: "형식만 봅니다." / 신재민: "그런데 신고 제도이다 보니, 실질적인 부분까지 문제 삼아서 보완하거나 반려할 수 있는 법적 규정이 없습니다." / 신재민: "지금 저희가 수리를 요하는 신고 형태로 가고 있는데, 그게 현행 제도입니다." / 신재민: "최초 신고는 수리를 요하는 신고로 유지하고, 시설물의 규모나 위치가 변경되는 경우는 수리를 요하는 신고가 필요하며, 소유자 변경 같은 기타 사항들은 솔직히 다 자기완결적 신고로 바꿔도 된다고 봅니다."</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>〈군산청 인터뷰〉
+[인터뷰 내용] 처리기간과 효력 발생 시점이 법령에 없어 국민신문고 처리기한(최초 7일)을 따르고, 해양시설만 별도로 정한 행정규칙도 없다. 신고 서류를 확인하고 현장 실사를 거쳐 신고증(확인서)을 발급하며, 효력은 증명서가 발급되어야 발생한다고 본다. 심사는 형식만 보지만 신고제도여서 실질 문제로 보완·반려할 법적 규정이 없다. 최초신고와 시설 규모·위치 변경은 수리를 요하는 신고로 유지하고 소유자 변경은 자기완결적 신고로 바꿔도 된다고 본다.
+[발언] 신재민: "해양환경관리법에 해양시설만 별도로 정한 행정규칙 같은 것은 없는 것으로 알고 있습니다. 그리고 해양시설 등록 최초 신고는 국민신문고 기준으로 7일로 나와 있습니다." / 신재민: "이거는 등록 제도처럼 요건이 있습니다. 신고인 일치 여부도 확인해야 하고, 시설 소유자 관련 증빙 같은 것도 받고 있습니다." / 신재민: "설치 장소가 신고된 번지에 있는지, 그 정도 규모가 있는지를 확인하고, 서류상 문제가 없으면 바로 신고증(확인서)이 나갑니다." / (면담자 오세영) "그러면 신고가 접수되고 신고 서류가 도달했을 때 효력이 발생하는 것이 아니라, 주무관님과 같은 담당자의 검토가 끝났을 때, 특히 증명서가 발급되어야 그때부터 신고의 효력이 발생한다고 보면 될까요?" / 신재민: "네 맞습니다." / 신재민: "형식만 봅니다." / 신재민: "그런데 신고 제도이다 보니, 실질적인 부분까지 문제 삼아서 보완하거나 반려할 수 있는 법적 규정이 없습니다." / 신재민: "지금 저희가 수리를 요하는 신고 형태로 가고 있는데, 그게 현행 제도입니다." / 신재민: "최초 신고는 수리를 요하는 신고로 유지하고, 시설물의 규모나 위치가 변경되는 경우는 수리를 요하는 신고가 필요하며, 소유자 변경 같은 기타 사항들은 솔직히 다 자기완결적 신고로 바꿔도 된다고 봅니다."
+〈포항청 인터뷰〉
+[인터뷰 내용] 처리기한은 법·시행규칙 본문이 아니라 별지 서식 위에 최초 7일·변경 5일로 적혀 있고, 법에 효력 발생 규정이 없으면 신고증명서 발급일을 기준으로 수리된 것으로 본다. 수리 후 민원인에게 통지하며, 수리가 안 되는 경우는 민원처리법에 따른 보완·반려이다. 효력 발생 시점이나 신고증명서의 법적 성격을 명시하면 더 명확해질 것이라고 했다. 규정이 없으면 시행규칙을 개정하면 된다고 보았다.
+[발언] 조호영: "별지 서식을 보면, 최초 신고는 7일 안에 처리해야 하고, 변경 신고는 5일 안에 처리해야 한다고 나와 있습니다." / (면담자 오세영) "시행규칙에는 없던데요." / 조호영: "그러니까 별지 서식 위에 적혀 있을 텐데, 별지 서식이 아니라면 시행규칙과 거의 동일하게 취급해야 되는 거죠." / 조호영: "저희가 만약 신고를 받으면 최초 신고는 7일 안에, 변경 신고는 5일 안에 처리해야 하는데, 접수 후 검토를 해서 민원인에게 신고 수리가 됐다고 통지합니다." / 조호영: "그게, 신고증명서라고 하는 게, 신고증명서 발급일을 기준으로 봐야 됩니다." / 조호영: "수리가 안 되는 경우는 보완이라든지 반려인데, 민원처리법에 따라 첨부서류가 미비하다든지 하면 그렇습니다. 보완이 완료되지 않으면 반려할 수도 있고요." / (면담자 오세영) "효력 발생 시점이나 신고증명서의 법적 성격을 법률이나 행정규칙에 규정할 필요가 있는지요? 예를 들어 '확인서를 발급한 때 효력이 발생한다'는 식으로 명시하는 경우도 있거든요." / 조호영: "그렇게 하면 더 명확해질 것 같습니다." / 조호영: "만약 없다고 하면 통상적으로 신고증명서 발급일 기준으로 신고가 수리된 것으로 보는 거니까요. 민원인도 그렇게 생각할 것 같긴 합니다." / 조호영: "중요한 사항은 아니고, 만약 문제가 된다면 시행규칙을 개정해서 그에 따라 하면 되는 것이라고 생각합니다."
+〈부산청 인터뷰〉
+[인터뷰 내용] 최초신고 처리기한 규정이 법·시행규칙에 없고 신고서 양식에 7일·5일로 명시된 것으로 안다. 서류가 미비하면 접수하지 않고 보완되도록 안내하다가 갖춰졌을 때 접수하며, 서류 완료 시점부터 2~3일 내 결재 후 신고증명서를 등기로 보낸다. 효력 발생 시점은 신고증명서 발급 이후로 본다. 불수리 규정 자체가 없어 최초신고 지연으로 처리한다. 효력 발생 시점, 수리·통지 기한, 검토 범위가 법령에 규정되어 있어야 담당자 판단에 따라 처리가 달라지지 않는다고 했다.
+[발언] 윤혜림: "정확하지는 않지만 최초 신고는 7일 이내, 변경 신고는 5일 이내로 되어 있는 것으로 알고 있습니다." / 윤혜림: "아니면 제 생각에는 신고서 양식 자체에 명시되어 있을 것 같습니다." / (면담자 오세영) "서류가 미비할 경우에는 바로 접수하지 않고 서류가 보완되도록 계속 안내하다가, 서류가 갖추어졌을 때 접수를 받아 신고를 처리하신다는 말씀이시죠?" / 윤혜림: "맞습니다." / 윤혜림: "제가 알기로는 불수리에 대한 규정 자체가 없어서, 그냥 최초 신고를 지연한 상황으로 보고 처리합니다." / (면담자 오세영) "신고서가 접수되면 효력이 발생하는 시점은, 신고 증명서가 발급된 이후로 봐야 하는 거죠?" / 윤혜림: "네, 그렇습니다." / 윤혜림: "최초 신고 시 현장을 반드시 가야 한다는 규정은 없고, 최근에는 잘 나가지 않는 편입니다." / 윤혜림: "법령에 규정이 되어 있는 것이 담당자 입장에서는 업무를 하기가 편하고 좋다고 생각합니다. 규정이 없으면 기준이 없다 보니 담당자 판단에 따라 처리가 달라져 애매한 경우가 많은 것 같습니다."</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려.
 [문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
 [논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
-[개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 8~10과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
-[유의] 인터뷰이는 수리형 유지에 찬성하면서 제도 완화에는 신중한 입장("사회재난 같은 것들이 더 중요시되는 상황에서 제도를 갑자기 완화해 버리면 문제가 발생하지 않을까")이므로, 수리 간주는 '수리형 유지 + 기한 명확화'로 설명하는 것이 입법사실과 부합한다. [교차확인] 연번 4(포항청)·연번 5(부산청)와 동일 쟁점. 처리기한을 정할 때 민원처리법 제19조의 계산 방식(5일 이하 시간 단위, 토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다. 국가관리연안항 해양시설은 법 제33조제1항제1호에서 해양수산부장관 관할로 두면서 시행령 제94조제6항제2호가 접수를 시·도지사에게 위임하고 있어 ③ 정비 시 함께 검토한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="409" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.3.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+[개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 4과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
+[유의] 군산청 인터뷰이는 수리형 유지에 찬성하면서 제도 완화에는 신중한 입장("사회재난 같은 것들이 더 중요시되는 상황에서 제도를 갑자기 완화해 버리면 문제가 발생하지 않을까")이므로, 수리 간주는 '수리형 유지 + 기한 명확화'로 설명하는 것이 입법사실과 부합한다. 포항청 인터뷰이는 처음에는 규정 추가가 "굳이 그럴 필요까지는 없을 것 같"다고 했다가 명시하면 더 명확해진다고 답했고, 자기완결형 전환에는 부정적(사전 검토 과정 상실 우려)이므로 수리형 유지를 전제로 한 정비임을 밝혀야 한다. 포항청 인터뷰이가 '민원처리법상 법정 처리기간 7일'이라고 한 부분은 민원처리법이 아니라 별지 제12호서식 기재 기간으로 확인되며, 검토메모에 차이를 기록했다. 부산청의 '서류 완비 전 미접수' 운영은 법령 정비와 별개로 민원처리법 제22조제1항·행정절차법 제40조제3항에 따라 바로잡을 운영 사항이며(검토메모), 본 행은 그 원인이 되는 법적 성격·절차 규정의 공백을 다룬다. 부산청 인터뷰이는 효력에 대해 "신고를 했기 때문에 과태료를 받지 않는다는 정도"라고 하여 수리의 실익이 크지 않다고 보므로, 경미 사항의 수리 불요 전환(연번 4)과 함께 설계해야 한다. 처리기한을 정할 때 민원처리법 제19조의 계산 방식(5일 이하 시간 단위, 토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다. 국가관리연안항 해양시설은 법 제33조제1항제1호에서 해양수산부장관 관할로 두면서 시행령 제94조제6항제2호가 접수를 시·도지사에게 위임하고 있어 ③ 정비 시 함께 검토한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="303" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026.9.3.
+2026.9.8.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>공무원</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>포항지방해양수산청 해양수산환경과 7급 주무관 조호영(해양시설 신고·변경신고, 담당 약 3년, 기술직)
-면담자: 오세영 / 근무지 방문</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>「해양환경관리법」 제33조제1항·제2항
-법 제38조제3항(오염물질저장시설 신고의 수리 여부 통지, 2023.10.24. 신설 — 비교 조문)
-시행령 제94조제4항제2호·제2호의3, 제6항제2호(권한 위임)
-시행규칙 제17조제1항·제2항·제4항·제5항
-시행규칙 별지 제12호서식(처리기간 최초 7일·변경 5일, 처리절차)·별지 제14호서식(신고증명서)
-「행정기본법」 제34조
-「행정절차법」 제40조제2항~제4항
-「민원 처리에 관한 법률」 제19조·제22조제1항, 같은 법 시행령 제24조·제25조</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 처리기한은 법·시행규칙 본문이 아니라 별지 서식 위에 최초 7일·변경 5일로 적혀 있고, 법에 효력 발생 규정이 없으면 신고증명서 발급일을 기준으로 수리된 것으로 본다. 수리 후 민원인에게 통지하며, 수리가 안 되는 경우는 민원처리법에 따른 보완·반려이다. 효력 발생 시점이나 신고증명서의 법적 성격을 명시하면 더 명확해질 것이라고 했다. 규정이 없으면 시행규칙을 개정하면 된다고 보았다.
-[발언] 조호영: "별지 서식을 보면, 최초 신고는 7일 안에 처리해야 하고, 변경 신고는 5일 안에 처리해야 한다고 나와 있습니다." / (면담자 오세영) "시행규칙에는 없던데요." / 조호영: "그러니까 별지 서식 위에 적혀 있을 텐데, 별지 서식이 아니라면 시행규칙과 거의 동일하게 취급해야 되는 거죠." / 조호영: "저희가 만약 신고를 받으면 최초 신고는 7일 안에, 변경 신고는 5일 안에 처리해야 하는데, 접수 후 검토를 해서 민원인에게 신고 수리가 됐다고 통지합니다." / 조호영: "그게, 신고증명서라고 하는 게, 신고증명서 발급일을 기준으로 봐야 됩니다." / 조호영: "수리가 안 되는 경우는 보완이라든지 반려인데, 민원처리법에 따라 첨부서류가 미비하다든지 하면 그렇습니다. 보완이 완료되지 않으면 반려할 수도 있고요." / (면담자 오세영) "효력 발생 시점이나 신고증명서의 법적 성격을 법률이나 행정규칙에 규정할 필요가 있는지요? 예를 들어 '확인서를 발급한 때 효력이 발생한다'는 식으로 명시하는 경우도 있거든요." / 조호영: "그렇게 하면 더 명확해질 것 같습니다." / 조호영: "만약 없다고 하면 통상적으로 신고증명서 발급일 기준으로 신고가 수리된 것으로 보는 거니까요. 민원인도 그렇게 생각할 것 같긴 합니다." / 조호영: "중요한 사항은 아니고, 만약 문제가 된다면 시행규칙을 개정해서 그에 따라 하면 되는 것이라고 생각합니다."</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려.
-[문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
-[논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
-[개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 8~10과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
-[유의] 인터뷰이는 처음에는 규정 추가가 "굳이 그럴 필요까지는 없을 것 같"다고 했다가 명시하면 더 명확해진다고 답했고, 자기완결형 전환에는 부정적(사전 검토 과정 상실 우려)이므로 수리형 유지를 전제로 한 정비임을 밝혀야 한다. 인터뷰이가 '민원처리법상 법정 처리기간 7일'이라고 한 부분은 민원처리법이 아니라 별지 제12호서식 기재 기간으로 확인되며, 검토메모에 차이를 기록했다. [교차확인] 연번 3(군산청)·연번 5(부산청)와 동일 쟁점. 처리기한을 정할 때 민원처리법 제19조의 계산 방식(5일 이하 시간 단위, 토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다. 국가관리연안항 해양시설은 법 제33조제1항제1호에서 해양수산부장관 관할로 두면서 시행령 제94조제6항제2호가 접수를 시·도지사에게 위임하고 있어 ③ 정비 시 함께 검토한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="409" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.8.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>〈군산청〉 군산지방해양수산청 해양수산환경과 7급 주무관 신재민(해양시설 신고·변경신고 접수 및 등록·관리, 담당 1년 6개월)
+면담자: 오세영, 김현빈 / 비대면(ZOOM)
+〈부산청〉 부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
 면담자: 오세영, 김현빈 / 비대면(Webex)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>「해양환경관리법」 제33조제1항·제2항
-법 제38조제3항(오염물질저장시설 신고의 수리 여부 통지, 2023.10.24. 신설 — 비교 조문)
-시행령 제94조제4항제2호·제2호의3, 제6항제2호(권한 위임)
-시행규칙 제17조제1항·제2항·제4항·제5항
-시행규칙 별지 제12호서식(처리기간 최초 7일·변경 5일, 처리절차)·별지 제14호서식(신고증명서)
-「행정기본법」 제34조
-「행정절차법」 제40조제2항~제4항
-「민원 처리에 관한 법률」 제19조·제22조제1항, 같은 법 시행령 제24조·제25조</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 최초신고 처리기한 규정이 법·시행규칙에 없고 신고서 양식에 7일·5일로 명시된 것으로 안다. 서류가 미비하면 접수하지 않고 보완되도록 안내하다가 갖춰졌을 때 접수하며, 서류 완료 시점부터 2~3일 내 결재 후 신고증명서를 등기로 보낸다. 효력 발생 시점은 신고증명서 발급 이후로 본다. 불수리 규정 자체가 없어 최초신고 지연으로 처리한다. 효력 발생 시점, 수리·통지 기한, 검토 범위가 법령에 규정되어 있어야 담당자 판단에 따라 처리가 달라지지 않는다고 했다.
-[발언] 윤혜림: "정확하지는 않지만 최초 신고는 7일 이내, 변경 신고는 5일 이내로 되어 있는 것으로 알고 있습니다." / 윤혜림: "아니면 제 생각에는 신고서 양식 자체에 명시되어 있을 것 같습니다." / (면담자 오세영) "서류가 미비할 경우에는 바로 접수하지 않고 서류가 보완되도록 계속 안내하다가, 서류가 갖추어졌을 때 접수를 받아 신고를 처리하신다는 말씀이시죠?" / 윤혜림: "맞습니다." / 윤혜림: "제가 알기로는 불수리에 대한 규정 자체가 없어서, 그냥 최초 신고를 지연한 상황으로 보고 처리합니다." / (면담자 오세영) "신고서가 접수되면 효력이 발생하는 시점은, 신고 증명서가 발급된 이후로 봐야 하는 거죠?" / 윤혜림: "네, 그렇습니다." / 윤혜림: "최초 신고 시 현장을 반드시 가야 한다는 규정은 없고, 최근에는 잘 나가지 않는 편입니다." / 윤혜림: "법령에 규정이 되어 있는 것이 담당자 입장에서는 업무를 하기가 편하고 좋다고 생각합니다. 규정이 없으면 기준이 없다 보니 담당자 판단에 따라 처리가 달라져 애매한 경우가 많은 것 같습니다."</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려.
-[문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
-[논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
-[개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 8~10과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
-[유의] 부산청의 '서류 완비 전 미접수' 운영은 법령 정비와 별개로 민원처리법 제22조제1항·행정절차법 제40조제3항에 따라 바로잡을 운영 사항이며(검토메모), 본 행은 그 원인이 되는 법적 성격·절차 규정의 공백을 다룬다. 인터뷰이는 효력에 대해 "신고를 했기 때문에 과태료를 받지 않는다는 정도"라고 하여 수리의 실익이 크지 않다고 보므로, 경미 사항의 수리 불요 전환(연번 8)과 함께 설계해야 한다. [교차확인] 연번 3(군산청)·연번 4(포항청)와 동일 쟁점. 처리기한을 정할 때 민원처리법 제19조의 계산 방식(5일 이하 시간 단위, 토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다. 국가관리연안항 해양시설은 법 제33조제1항제1호에서 해양수산부장관 관할로 두면서 시행령 제94조제6항제2호가 접수를 시·도지사에게 위임하고 있어 ③ 정비 시 함께 검토한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="289.5" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.8.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
-면담자: 오세영, 김현빈 / 비대면(Webex)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>「해양환경관리법」 제33조제1항(신고 의무, 기한 문언 없음)·제2항
 법 제132조제2항제2호
@@ -765,88 +644,52 @@
 「질서위반행위규제법」 제6조(질서위반행위 법정주의)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 신고 내용이 불완전해 수리되지 않은 경우 불수리 규정이 없어 최초신고 지연으로 처리하는데, 변경신고는 처리기한이 며칠 이내로 정해져 있는 반면 최초신고는 기한이 없어 과태료 부과가 애매하므로 보완이 필요하다고 했다. 공유수면 점용사용허가를 받고도 해양시설 신고를 해야 하는지 몰라 과태료를 받는 경우가 있다.
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>〈군산청 인터뷰〉
+[인터뷰 내용] 시설을 다 설치한 뒤 신고하도록 안내하지만, 배수관처럼 육지에서 수 킬로미터를 잇는 공사는 어느 단계에서 신고해야 하는지 민원인이 헷갈리고, 준공 전에는 신고에 필요한 서류도 나오지 않는다. 설치가 끝나지 않았는데 신고하러 오는 사람도 많고, 신고 시점이 법에 없다는 이야기를 하지만 인터뷰이는 상식적 사항이라 법에 담을 필요는 없다고 본다.
+[발언] 신재민: "저희는 설치가 다 되고 나서 신고를 하라고 안내하고 있습니다. 해양오염을 일으킬 수 있는 시설물로서 기능을 할 수 있을 정도로 완공이 되어야 한다고 안내하고 있습니다. 그런게 불명확하죠." / 신재민: "그런데 공사를 할 때 어디까지 완성되었을 때를 기준으로 신고 시점을 잡아야 하는지 헷갈려 합니다. 전체 공정이 다 끝났을 때 해양시설 신고를 해야 하는지, 아니면 일부만 사용하고 있을 때 신고해야 하는지 헷갈려 합니다." / 신재민: "그런 신고해야 하는 타이밍이 좀 모호해요." / 신재민: "그런데 간혹 설치가 안 끝났는데 신고하러 오는 분들도 좀 많습니다." / 신재민: "신고 시점이 법에 나와 있지 않다는 이야기를 하시는데, 상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같습니다."
+〈부산청 인터뷰〉
+[인터뷰 내용] 신고 내용이 불완전해 수리되지 않은 경우 불수리 규정이 없어 최초신고 지연으로 처리하는데, 변경신고는 처리기한이 며칠 이내로 정해져 있는 반면 최초신고는 기한이 없어 과태료 부과가 애매하므로 보완이 필요하다고 했다. 공유수면 점용사용허가를 받고도 해양시설 신고를 해야 하는지 몰라 과태료를 받는 경우가 있다.
 [발언] 윤혜림: "다만 변경 신고는 처리 기한이 며칠 이내로 정해져 있는데 최초 신고는 그런 기한이 없다 보니, 과태료를 부과하기에도 다소 애매한 상황입니다. 이 부분도 보완이 되면 좋겠습니다." / 윤혜림: "해양환경관리법상 신고를 하지 않은 상태는 그냥 불법 상태인 것이고, 신고 증명서 자체가 시설 이용의 효력 발생 요건은 아닙니다." / 윤혜림: "공유수면 점용사용허가를 받았음에도 해양시설 신고를 해야 하는지 몰라서 과태료를 받으시는 경우도 있습니다."</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않으며, 제2항은 신고내용·절차를 부령에 위임한다. 시행규칙 제17조제1항은 "법 제33조제1항 전단에 따라 해양시설의 신고를 하려는 경우에는" 최초신고서를 제출하도록 할 뿐 기한을 두지 않고, 제4항은 변경신고에만 '변경사유가 발생한 날부터 30일 이내'를 두며, 제7항의 폐업신고에도 기한이 없다(해양수산부 FAQ와 구 국토해양부 안내의 '최초신고는 사업개시 후 30일 이내', '폐업신고는 폐업일부터 30일 이내'는 현행 조문에 근거가 없다). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 「질서위반행위규제법」 제6조: 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다.
 [문제점] ① 최초신고의 의무 발생 시점(설치 완료, 사용 개시, 공사 중 일부 가동)이 법령에 없어, 담당자가 "완공이 되어야 한다"고 안내하고 민원인은 "신고 시점이 법에 나와 있지 않다"고 이의를 제기한다. 배수관처럼 수 킬로미터 공정 중 일부만 가동되는 시설은 신고 시점을 특정할 수 없다. ② 변경신고에는 30일 기한이 있어, 같은 호의 과태료(별표 19 너목: 신고·변경신고 미이행 동일 250만원)가 변경신고에는 적용 시점이 분명하고 최초신고에는 불분명한 비대칭이 생긴다. ③ 서류 미비로 증명서가 발급되지 않은 경우를 "최초 신고를 지연한 상황"으로 보고 과태료를 검토하는데, 기한이 없으니 지연 여부 자체를 판단할 수 없어 부과가 "애매"해진다. ④ 행정안내(FAQ)가 조문에 없는 30일 기한을 안내하고 있어, 수범자는 안내문을, 담당자는 조문을 기준으로 삼는 불일치가 있다.
 [논거] 과태료의 구성요건인 '신고를 하지 아니한' 상태는 신고 의무의 이행 기한이 있어야 성립 시점이 확정된다. 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 못하며(「질서위반행위규제법」 제6조) 그 요건은 명확해야 하므로, 기한 없는 의무에 제재를 결부한 현행 구조는 명확성 원칙에 비추어 정비 대상이다. 행정안내로 30일을 운용하는 것은 법령 근거 없이 제재 요건을 보충하는 것이어서 해석·지침으로 해결할 수 없다. 인터뷰이(군산)의 '상식 사항' 견해는 민원인이 실제로 다투고 있다는 같은 인터뷰이의 진술과 상충한다.
-[개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항·제7항에 같은 기산점을 반영하고(폐업신고 기한도 함께), 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행·변경신고 미이행·기한 경과 후 신고로 구분한다(연번 8~10과 연계). 최소 정비안은 ②이나, 의무의 내용(기한)이 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
-[유의] 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 7 참조). 인터뷰이가 말한 '변경 신고 처리 기한'은 맥락상 신고인의 변경신고 기한(시행규칙 제17조제4항, 30일)을 가리키는 것으로 보이며, 행정청의 처리기간(서식 5일)과 구분하여 검토메모에 기록했다. [교차확인] 연번 7(군산청 인터뷰)과 동일 쟁점(단, 군산청 인터뷰이는 입법 불요 의견).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="289.5" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.3.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+[개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항·제7항에 같은 기산점을 반영하고(폐업신고 기한도 함께), 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행·변경신고 미이행·기한 경과 후 신고로 구분한다(연번 4과 연계). 최소 정비안은 ②이나, 의무의 내용(기한)이 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
+[유의] 군산청 인터뷰이는 입법 불요 의견이므로 그 발언은 '신고 시점 불명확으로 인한 민원 혼선'의 입법사실로만 사용하고, 개정 필요성의 판단 근거는 부산청 인터뷰이가 제기한 과태료 집행 문제에 둔다. 부산청 인터뷰이가 말한 '변경 신고 처리 기한'은 맥락상 신고인의 변경신고 기한(시행규칙 제17조제4항, 30일)을 가리키는 것으로 보이며, 행정청의 처리기간(서식 5일)과 구분하여 검토메모에 기록했다. 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="370.5" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026.9.3.
+2026.9.8.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>공무원</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>군산지방해양수산청 해양수산환경과 7급 주무관 신재민(해양시설 신고·변경신고 접수 및 등록·관리, 담당 1년 6개월)
-면담자: 오세영, 김현빈 / 비대면(ZOOM)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>「해양환경관리법」 제33조제1항(신고 의무, 기한 문언 없음)·제2항
-법 제132조제2항제2호
-시행령 제98조·별표 19 너목(개정 2026.6.30.)
-시행규칙 제17조제1항(최초신고: 기한 없음)·제4항(변경신고: 30일)·제7항(폐업신고: 기한 없음)
-「질서위반행위규제법」 제6조(질서위반행위 법정주의)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 시설을 다 설치한 뒤 신고하도록 안내하지만, 배수관처럼 육지에서 수 킬로미터를 잇는 공사는 어느 단계에서 신고해야 하는지 민원인이 헷갈리고, 준공 전에는 신고에 필요한 서류도 나오지 않는다. 설치가 끝나지 않았는데 신고하러 오는 사람도 많고, 신고 시점이 법에 없다는 이야기를 하지만 인터뷰이는 상식적 사항이라 법에 담을 필요는 없다고 본다.
-[발언] 신재민: "저희는 설치가 다 되고 나서 신고를 하라고 안내하고 있습니다. 해양오염을 일으킬 수 있는 시설물로서 기능을 할 수 있을 정도로 완공이 되어야 한다고 안내하고 있습니다. 그런게 불명확하죠." / 신재민: "그런데 공사를 할 때 어디까지 완성되었을 때를 기준으로 신고 시점을 잡아야 하는지 헷갈려 합니다. 전체 공정이 다 끝났을 때 해양시설 신고를 해야 하는지, 아니면 일부만 사용하고 있을 때 신고해야 하는지 헷갈려 합니다." / 신재민: "그런 신고해야 하는 타이밍이 좀 모호해요." / 신재민: "그런데 간혹 설치가 안 끝났는데 신고하러 오는 분들도 좀 많습니다." / 신재민: "신고 시점이 법에 나와 있지 않다는 이야기를 하시는데, 상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같습니다."</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않으며, 제2항은 신고내용·절차를 부령에 위임한다. 시행규칙 제17조제1항은 "법 제33조제1항 전단에 따라 해양시설의 신고를 하려는 경우에는" 최초신고서를 제출하도록 할 뿐 기한을 두지 않고, 제4항은 변경신고에만 '변경사유가 발생한 날부터 30일 이내'를 두며, 제7항의 폐업신고에도 기한이 없다(해양수산부 FAQ와 구 국토해양부 안내의 '최초신고는 사업개시 후 30일 이내', '폐업신고는 폐업일부터 30일 이내'는 현행 조문에 근거가 없다). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 「질서위반행위규제법」 제6조: 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다.
-[문제점] ① 최초신고의 의무 발생 시점(설치 완료, 사용 개시, 공사 중 일부 가동)이 법령에 없어, 담당자가 "완공이 되어야 한다"고 안내하고 민원인은 "신고 시점이 법에 나와 있지 않다"고 이의를 제기한다. 배수관처럼 수 킬로미터 공정 중 일부만 가동되는 시설은 신고 시점을 특정할 수 없다. ② 변경신고에는 30일 기한이 있어, 같은 호의 과태료(별표 19 너목: 신고·변경신고 미이행 동일 250만원)가 변경신고에는 적용 시점이 분명하고 최초신고에는 불분명한 비대칭이 생긴다. ③ 서류 미비로 증명서가 발급되지 않은 경우를 "최초 신고를 지연한 상황"으로 보고 과태료를 검토하는데, 기한이 없으니 지연 여부 자체를 판단할 수 없어 부과가 "애매"해진다. ④ 행정안내(FAQ)가 조문에 없는 30일 기한을 안내하고 있어, 수범자는 안내문을, 담당자는 조문을 기준으로 삼는 불일치가 있다.
-[논거] 과태료의 구성요건인 '신고를 하지 아니한' 상태는 신고 의무의 이행 기한이 있어야 성립 시점이 확정된다. 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 못하며(「질서위반행위규제법」 제6조) 그 요건은 명확해야 하므로, 기한 없는 의무에 제재를 결부한 현행 구조는 명확성 원칙에 비추어 정비 대상이다. 행정안내로 30일을 운용하는 것은 법령 근거 없이 제재 요건을 보충하는 것이어서 해석·지침으로 해결할 수 없다. 인터뷰이(군산)의 '상식 사항' 견해는 민원인이 실제로 다투고 있다는 같은 인터뷰이의 진술과 상충한다.
-[개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항·제7항에 같은 기산점을 반영하고(폐업신고 기한도 함께), 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행·변경신고 미이행·기한 경과 후 신고로 구분한다(연번 8~10과 연계). 최소 정비안은 ②이나, 의무의 내용(기한)이 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
-[유의] 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다(연번 7 참조). 본 행의 인터뷰이는 입법 불요 의견이므로 입법사실로는 '시점 불명확으로 인한 민원 혼선'만 사용하고, 개정 필요성의 판단 근거는 연번 6(부산청)의 과태료 집행 문제에 둔다. [교차확인] 연번 6(부산청 인터뷰)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="316.5" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.8.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>〈군산청〉 군산지방해양수산청 해양수산환경과 7급 주무관 신재민(해양시설 신고·변경신고 접수 및 등록·관리, 담당 1년 6개월)
+면담자: 오세영, 김현빈 / 비대면(ZOOM)
+〈포항청〉 포항지방해양수산청 해양수산환경과 7급 주무관 조호영(해양시설 신고·변경신고, 담당 약 3년, 기술직)
+면담자: 오세영 / 근무지 방문
+〈부산청〉 부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
 면담자: 오세영, 김현빈 / 비대면(Webex)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>「해양환경관리법」 제33조제1항 후단('해양수산부령으로 정하는 중요한 내용'의 변경신고)·제2항
 법 제132조제2항제2호(500만원 이하)·제4항제6호의7(관리인 임명 신고 미이행, 100만원 이하 — 비교)
@@ -857,137 +700,53 @@
 「민원 처리에 관한 법률」 제10조제3항제3호</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 변경신고는 주로 대표자 변경이며, 시설 규모 변경이 아닌 명칭·대표자 변경은 절차가 간단해 자기완결형으로 전환해도 된다고 본다. 30일 이내 변경신고 의무를 안내해도 과태료 대상임을 인지하지 못하는 경우가 많고, 대표자 변경이 해양시설 관리에 크게 영향을 주지 않는데도 과태료 250만원은 높게 산정되어 있다고 본다. 과태료 감경은 담당자별로 판단이 달라질 수 있다.
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>〈군산청 인터뷰〉
+[인터뷰 내용] 신고는 연 6건 미만이며 거의 변경신고이다. 시설물 변경은 수리를 요하는 신고가 필요하지만 소유자 변경은 자기완결적 신고로 충분하다고 본다. 다만 제도를 완화하기보다 대상을 재정립해 규제 정도를 바꾸는 것이 바람직하다는 의견이다.
+[발언] 신재민: "저희 같은 경우 해양시설 신고는 1년에 6건도 안 되는 것 같고, 그마저도 신규가 아니라 변경 신고입니다." / 신재민: "그런데 시설물의 변경 같은 것들은 수리를 요하는 신고 정도가 필요할 거라고 생각합니다. 그런데 소유자 변경 같은 것들은 그냥 자기완결적 신고로도 충분할 것 같습니다." / (면담자 오세영) "소유자의 신분이나 자격 요건이 별도로 필요한 게 아니니까 그렇다는 말씀이시군요." / 신재민: "네, 그래서 제도를 완화하기보다는 대상을 다시 정립해서, 규제를 한다면 규제의 정도를 바꾸는 게 더 바람직하다고 생각합니다."
+〈포항청 인터뷰〉
+[인터뷰 내용] 신규 신고는 거의 없고 대부분 대표자 변경 등 변경신고로 연 2~6건이다. 대표자 변경 신고는 책임 소재와 관련되어 다른 법에도 있는 의무라고 보지만, 경미한 변경·소유자 변경·폐업은 간소한 신고 방식이 가능하되 확인할 수 있는 서류는 필요하다고 했다. 변경신고 중 대표자 변경처럼 서류로 확인 가능한 경우 현장 조사를 생략할 수 있다.
+[발언] 조호영: "이게 신규로는 거의 들어오는 게 없고, 대부분 변경(대표자 변경 등)으로, 1년에 한 2건 정도 들어오고, 많이 들어오면 한 6건 정도입니다." / 조호영: "신고 의무자, 즉 소유자나 운영자가 바뀌면 당연히 신고를 해야 한다고 보고 있습니다. 그게 책임 소재와도 관련이 있으니까요." / 조호영: "변경 신고의 경우 대표자 변경처럼 서류로 충분히 확인 가능한 경우에는 현장 조사를 생략할 수도 있습니다." / (면담자 오세영) "그러면 맨 마지막에 있는, 경미한 변경이나 소유자 변경, 폐업 같은 건 간소한 신고 방식으로 가능할 것 같고요." / 조호영: "대신 이것도 충분히 확인할 수 있는 서류는 필요하겠죠."
+〈부산청 인터뷰〉
+[인터뷰 내용] 변경신고는 주로 대표자 변경이며, 시설 규모 변경이 아닌 명칭·대표자 변경은 절차가 간단해 자기완결형으로 전환해도 된다고 본다. 30일 이내 변경신고 의무를 안내해도 과태료 대상임을 인지하지 못하는 경우가 많고, 대표자 변경이 해양시설 관리에 크게 영향을 주지 않는데도 과태료 250만원은 높게 산정되어 있다고 본다. 과태료 감경은 담당자별로 판단이 달라질 수 있다.
 [발언] 윤혜림: "변경 신고의 경우, 시설 규모가 변경된 경우가 아니라면 단순히 해양시설 명칭이나 대표자가 변경된 정도는 절차가 매우 간단하기 때문에, 그 정도는 자기완결형으로 전환해도 될 것 같습니다." / 윤혜림: "사소한 부분을 자기완결형 신고로 전환하는 것은 크게 문제가 되지 않을 것 같습니다." / 윤혜림: "대표자 변경과 관련해서 과태료가 많이 부과되는 경우가 있습니다. 30일 이내에 변경 신고를 해야 한다고 계속 안내드려도 이것이 과태료 대상이라는 것을 잘 인지하지 못하시는 경우가 많고, 대표자 변경이 해양시설 관리에 크게 영향을 주는 사안이 아닌데도 과태료가 250만 원이다 보니 부담을 많이 느끼십니다." / 윤혜림: "규모가 큰 기업의 경우 대표자 변경이 그다지 의미가 없는 경우가 많아 과태료가 다소 높게 산정되어 있는 것은 아닌가 하는 생각이 업무를 하면서 들었습니다." / 윤혜림: "변경 신고를 하지 않았을 때는 250만 원입니다." / 윤혜림: "다만 이 역시 담당자별로 판단이 달라질 수 있어, 업체 입장에서는 의아하게 느낄 수도 있을 것 같습니다."</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다.
 [문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 같은 별표에서 관리인 임명 신고 미이행은 30만원이다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항제3호), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장). ⑤ 300㎘ 이상 저장시설은 대표자 변경 하나에 해양수산부(변경신고)와 해양경찰(변경검인) 두 절차를 각각 30일 내에 밟아야 하는 중복이 있다.
 [논거] 하위법령이 법률의 위임 문언('중요한 내용')을 넘어 형식적 사항까지 수리형 변경신고 대상으로 정한 것은 위임 범위의 문제이고, 경미한 변경에 중대한 변경과 같은 절차·제재를 결부한 것은 비례원칙(필요 최소한의 절차·제재)에 어긋난다. 과태료 금액은 시행령 별표 19가 정하므로 금액 차등은 시행령 개정으로 가능하고, 신고 유형의 구분은 「행정기본법」 제34조에 따라 법률에서 수리 필요 여부를 명시해야 완결된다. 규제를 완화·세분하는 방향이므로 규제 신설이 아니다.
-[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 11·12와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
-[유의] 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준 나목·다목(2026.6.30. 소상공인 감경 신설)에 이미 있어 검토메모로 분리했다. ⑤의 해경 변경검인 중복은 법령 대조 중 발견한 사항으로 인터뷰이가 직접 제기하지 않았으므로 연계 정비로만 제시하며, 해양경찰청과 협의가 필요하다. [교차확인] 연번 9(군산청)·연번 10(포항청)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="316.5" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.3.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 5와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
+[유의] 군산청 인터뷰이는 과태료 금액에 대해서는 언급하지 않았으므로 본 행의 입법사실은 '소유자 변경의 수리 불요 전환'에 한정된다. 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준 나목·다목(2026.6.30. 소상공인 감경 신설)에 이미 있어 검토메모로 분리했다. ⑤의 해경 변경검인 중복은 법령 대조 중 발견한 사항으로 인터뷰이가 직접 제기하지 않았으므로 연계 정비로만 제시하며, 해양경찰청과 협의가 필요하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="303" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026.9.3.
+2026.9.8.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>공무원</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>군산지방해양수산청 해양수산환경과 7급 주무관 신재민(해양시설 신고·변경신고 접수 및 등록·관리, 담당 1년 6개월)
-면담자: 오세영, 김현빈 / 비대면(ZOOM)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>「해양환경관리법」 제33조제1항 후단('해양수산부령으로 정하는 중요한 내용'의 변경신고)·제2항
-법 제132조제2항제2호(500만원 이하)·제4항제6호의7(관리인 임명 신고 미이행, 100만원 이하 — 비교)
-시행령 제98조·별표 19 너목(250만원)·더목(30만원 — 비교), 일반기준 나목·다목
-시행규칙 제17조제3항제1호(소유자 변경에 사업장 명칭·대표자 변경 포함)·제4항(30일)·제5항(변경신고 시 신고증명서 발급)
-시행규칙 제19조제4항제1호·제5항(대표자 변경 시 비상계획서 변경검인 — 비교)
-「행정기본법」 제34조
-「민원 처리에 관한 법률」 제10조제3항제3호</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 신고는 연 6건 미만이며 거의 변경신고이다. 시설물 변경은 수리를 요하는 신고가 필요하지만 소유자 변경은 자기완결적 신고로 충분하다고 본다. 다만 제도를 완화하기보다 대상을 재정립해 규제 정도를 바꾸는 것이 바람직하다는 의견이다.
-[발언] 신재민: "저희 같은 경우 해양시설 신고는 1년에 6건도 안 되는 것 같고, 그마저도 신규가 아니라 변경 신고입니다." / 신재민: "그런데 시설물의 변경 같은 것들은 수리를 요하는 신고 정도가 필요할 거라고 생각합니다. 그런데 소유자 변경 같은 것들은 그냥 자기완결적 신고로도 충분할 것 같습니다." / (면담자 오세영) "소유자의 신분이나 자격 요건이 별도로 필요한 게 아니니까 그렇다는 말씀이시군요." / 신재민: "네, 그래서 제도를 완화하기보다는 대상을 다시 정립해서, 규제를 한다면 규제의 정도를 바꾸는 게 더 바람직하다고 생각합니다."</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다.
-[문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 같은 별표에서 관리인 임명 신고 미이행은 30만원이다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항제3호), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장). ⑤ 300㎘ 이상 저장시설은 대표자 변경 하나에 해양수산부(변경신고)와 해양경찰(변경검인) 두 절차를 각각 30일 내에 밟아야 하는 중복이 있다.
-[논거] 하위법령이 법률의 위임 문언('중요한 내용')을 넘어 형식적 사항까지 수리형 변경신고 대상으로 정한 것은 위임 범위의 문제이고, 경미한 변경에 중대한 변경과 같은 절차·제재를 결부한 것은 비례원칙(필요 최소한의 절차·제재)에 어긋난다. 과태료 금액은 시행령 별표 19가 정하므로 금액 차등은 시행령 개정으로 가능하고, 신고 유형의 구분은 「행정기본법」 제34조에 따라 법률에서 수리 필요 여부를 명시해야 완결된다. 규제를 완화·세분하는 방향이므로 규제 신설이 아니다.
-[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 11·12와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
-[유의] 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준 나목·다목(2026.6.30. 소상공인 감경 신설)에 이미 있어 검토메모로 분리했다. ⑤의 해경 변경검인 중복은 법령 대조 중 발견한 사항으로 인터뷰이가 직접 제기하지 않았으므로 연계 정비로만 제시하며, 해양경찰청과 협의가 필요하다. 군산청 인터뷰이는 과태료 금액에 대해서는 언급하지 않았으므로 본 행의 입법사실은 '소유자 변경의 수리 불요 전환'에 한정된다. [교차확인] 연번 8(부산청)·연번 10(포항청)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="316.5" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.3.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>포항지방해양수산청 해양수산환경과 7급 주무관 조호영(해양시설 신고·변경신고, 담당 약 3년, 기술직)
-면담자: 오세영 / 근무지 방문</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>「해양환경관리법」 제33조제1항 후단('해양수산부령으로 정하는 중요한 내용'의 변경신고)·제2항
-법 제132조제2항제2호(500만원 이하)·제4항제6호의7(관리인 임명 신고 미이행, 100만원 이하 — 비교)
-시행령 제98조·별표 19 너목(250만원)·더목(30만원 — 비교), 일반기준 나목·다목
-시행규칙 제17조제3항제1호(소유자 변경에 사업장 명칭·대표자 변경 포함)·제4항(30일)·제5항(변경신고 시 신고증명서 발급)
-시행규칙 제19조제4항제1호·제5항(대표자 변경 시 비상계획서 변경검인 — 비교)
-「행정기본법」 제34조
-「민원 처리에 관한 법률」 제10조제3항제3호</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 신규 신고는 거의 없고 대부분 대표자 변경 등 변경신고로 연 2~6건이다. 대표자 변경 신고는 책임 소재와 관련되어 다른 법에도 있는 의무라고 보지만, 경미한 변경·소유자 변경·폐업은 간소한 신고 방식이 가능하되 확인할 수 있는 서류는 필요하다고 했다. 변경신고 중 대표자 변경처럼 서류로 확인 가능한 경우 현장 조사를 생략할 수 있다.
-[발언] 조호영: "이게 신규로는 거의 들어오는 게 없고, 대부분 변경(대표자 변경 등)으로, 1년에 한 2건 정도 들어오고, 많이 들어오면 한 6건 정도입니다." / 조호영: "신고 의무자, 즉 소유자나 운영자가 바뀌면 당연히 신고를 해야 한다고 보고 있습니다. 그게 책임 소재와도 관련이 있으니까요." / 조호영: "변경 신고의 경우 대표자 변경처럼 서류로 충분히 확인 가능한 경우에는 현장 조사를 생략할 수도 있습니다." / (면담자 오세영) "그러면 맨 마지막에 있는, 경미한 변경이나 소유자 변경, 폐업 같은 건 간소한 신고 방식으로 가능할 것 같고요." / 조호영: "대신 이것도 충분히 확인할 수 있는 서류는 필요하겠죠."</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 법 제33조제1항 후단은 "해양수산부령으로 정하는 중요한 내용"의 변경에 변경신고 의무를 두고, 시행규칙 제17조제3항은 ① 해양시설의 소유자(사업장의 명칭 및 대표자를 포함한다)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정)를 중요한 내용으로 정한다. 변경신고도 최초신고와 같은 별지 제12호서식으로 30일 이내에 하고(제4항), 행정청은 신고대장·신고증명서 뒤쪽에 변경내용을 적어 신고증명서를 발급한다(제5항). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 한편 기름·유해액체물질 저장시설(합계용량 300㎘ 이상)은 시행규칙 제19조제4항제1호·제5항에 따라 같은 대표자 변경에 대해 해양경찰서장에게 30일 이내 비상계획서 변경검인도 받아야 한다.
-[문제점] ① 법률은 변경신고 대상을 '중요한 내용'으로 한정했는데, 부령은 시설의 오염 위험·규모·위치와 무관한 대표자·사업장 명칭 변경까지 포함하여 위임 취지(중요성)와 문언이 어긋난다. ② 대표자 변경은 현장 확인이 "무의미"하고 서류만 확인하는데도 최초신고와 동일한 수리형 절차(서식·검토·결재·증명서 발급)를 거치고, 미이행 과태료도 최초신고 미이행과 같은 250만원이어서 위반의 경중과 제재가 비례하지 않는다. 같은 별표에서 관리인 임명 신고 미이행은 30만원이다. 대기업은 대표자 변경이 잦아 반복 부과되고, 민원인은 과태료 대상임을 인지하지 못한다. ③ 대표자 변경은 법인등기로 공시되어 행정정보 공동이용으로 확인할 수 있는 사항이어서(민원처리법 제10조제3항제3호), 신고인에게 증명 서류를 받아 수리하는 절차 자체가 과잉이다. ④ 세 인터뷰이 모두 대표자·명칭 변경은 간소한(도달 시 효력) 신고로 충분하다고 보았다(포항은 신고 의무 자체는 책임 소재 확인을 위해 유지해야 한다는 입장). ⑤ 300㎘ 이상 저장시설은 대표자 변경 하나에 해양수산부(변경신고)와 해양경찰(변경검인) 두 절차를 각각 30일 내에 밟아야 하는 중복이 있다.
-[논거] 하위법령이 법률의 위임 문언('중요한 내용')을 넘어 형식적 사항까지 수리형 변경신고 대상으로 정한 것은 위임 범위의 문제이고, 경미한 변경에 중대한 변경과 같은 절차·제재를 결부한 것은 비례원칙(필요 최소한의 절차·제재)에 어긋난다. 과태료 금액은 시행령 별표 19가 정하므로 금액 차등은 시행령 개정으로 가능하고, 신고 유형의 구분은 「행정기본법」 제34조에 따라 법률에서 수리 필요 여부를 명시해야 완결된다. 규제를 완화·세분하는 방향이므로 규제 신설이 아니다.
-[개정 방향] ① (법률) 법 제33조에 "소유자·대표자·명칭 등 해양수산부령으로 정하는 경미한 사항의 변경은 변경신고 대신 ○일 이내에 통보(수리 불요 신고)한다"는 구분을 두고, 설치 장소·규모 변경만 수리형 변경신고로 남긴다. ② (부령) 시행규칙 제17조제3항제1호에서 사업장 명칭·대표자 변경을 '중요한 내용'에서 분리하고, 그 변경은 신고증명서 재발급 없이 신고대장 기재만으로 처리하며, 법인 등기사항은 담당 공무원이 공동이용으로 확인하도록 한다(연번 11·12와 연계). 제19조제4항제1호의 변경검인 대상에서도 대표자 변경을 '관리자 변경'으로 좁히거나 해양수산부 통보로 갈음하는 연계 규정을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행, 시설 변경신고 미이행, 경미 사항 변경 통보 미이행으로 나누어 금액을 차등하고 하향한다. 최소 정비안은 ②·③이나, ①이 없으면 부령상 '통보'의 법률 근거가 약하다.
-[유의] 포항청 조호영은 대표자 변경 신고 의무 유지(책임 소재)를 주장했으므로 '의무 폐지'가 아니라 '수리 불요·제재 완화'로 설계해야 한다. 과태료 감경 사유의 구체화 요청(부산)은 별표 19 일반기준 나목·다목(2026.6.30. 소상공인 감경 신설)에 이미 있어 검토메모로 분리했다. ⑤의 해경 변경검인 중복은 법령 대조 중 발견한 사항으로 인터뷰이가 직접 제기하지 않았으므로 연계 정비로만 제시하며, 해양경찰청과 협의가 필요하다. 포항청 인터뷰이의 '신고 의무 유지' 의견을 반영하여 본 행의 개정 방향은 의무 존치 + 절차 간소화로 한정된다. [교차확인] 연번 8(부산청)·연번 9(군산청)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="289.5" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.8.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>〈포항청〉 포항지방해양수산청 해양수산환경과 7급 주무관 조호영(해양시설 신고·변경신고, 담당 약 3년, 기술직)
+면담자: 오세영 / 근무지 방문
+〈부산청〉 부산지방해양수산청 해양수산환경과 6급 주무관 윤혜림(해양시설 신규·변경·폐업 신고, 2026.3.부터 약 6개월 담당 후 현재 담당 변경)
 면담자: 오세영, 김현빈 / 비대면(Webex)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>시행규칙 제17조제1항(최초신고 첨부서류)·제4항제2호('변경내용을 증명하는 서류')
 시행규칙 별지 제12호서식(개정 2024.6.28.: 신고인란에 상호·대표자·생년월일 기재, 첨부서류란만 있고 담당 공무원 확인사항란·공동이용 동의란 없음, 첨부서류 2번의 근거 조문을 '법 제32조'로 오기)
@@ -996,64 +755,23 @@
 「해양환경관리법」 제33조제1항(신고 주체: 소유자·설치운영자·임차인)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 가장 빈번한 보완 사항은 사업자등록증·법인 등기부등본으로, 서식의 구비서류 목록에 없어 자주 누락되는데 대표자 등을 확인해야 하므로 별도로 요청하고 유선 안내도 한다. 행정정보 공동이용은 제도적으로 마련되어 있지 않고 시스템 기반도 없어 이용한 적이 없다.
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>〈포항청 인터뷰〉
+[인터뷰 내용] 법령·서식에 없는 사진 등을 요구해서는 안 된다고 하면서도, 사업자등록증 같은 서류는 확인 목적으로 실제로 제출받고 있으며, 행정정보 공동이용 확인은 담당자의 전산 활용 능력에 따라 어려워 민원인의 협조를 구하기도 한다. 보완 요청은 거의 증빙자료 미비 때문이다.
+[발언] 조호영: "보완 요청은 거의 증빙자료 미비 때문입니다." / (면담자 오세영) "혹시 법령이나 서식에 명시되어 있지 않은 사진 같은 걸 요청하시는 경우도 있으신가요?" / 조호영: "그러면 안 되죠." / (면담자 오세영) "실제로 어떻게 하시는지요. 실제로는 다 제출받으시는 거네요." / 조호영: "일단 확인 목적으로요." / 조호영: "그런데 저희가 컴퓨터 활용에 대한 지식이 조금 부족한 경우도 있어서, 확인을 잘 못 하는 경우가 있을 수도 있어서 민원인의 협조를 구하기도 합니다."
+〈부산청 인터뷰〉
+[인터뷰 내용] 가장 빈번한 보완 사항은 사업자등록증·법인 등기부등본으로, 서식의 구비서류 목록에 없어 자주 누락되는데 대표자 등을 확인해야 하므로 별도로 요청하고 유선 안내도 한다. 행정정보 공동이용은 제도적으로 마련되어 있지 않고 시스템 기반도 없어 이용한 적이 없다.
 [발언] 윤혜림: "보통 사업자등록증이나 법인 등기부 등본을 받는데, 신고서 서식에는 이 서류들이 명시되어 있지 않아 자주 누락됩니다. 대표자 등을 확인해야 하기 때문에 이 서류들을 자주 요청하는 편이며, 처음 유선 문의가 오셨을 때도 별도로 안내를 드립니다." / 윤혜림: "법령의 별지 서식에 신고서가 있고 그 아래에 구비 서류가 명시되어 있는데, 그 목록에 해당하는 서류를 제출해 달라고 안내드리다 보니, 사업자등록증이나 법인 등기부 등본은 그 목록에 없어 별도로 추가 제출을 요청드리게 됩니다." / 윤혜림: "저희 쪽에서는 제도적으로 마련되어 있지 않고, 제가 다른 업무를 할 때도 사업자등록증 관련해서 행정정보 공동이용 처리 시스템을 이용한 적은 없습니다. 저희 시스템 자체의 기반이 구축되어 있지 않은 것 같습니다."</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서·도면·위치도, (해당 시설에 한해) 법 제36조에 따른 관리인 임명확인서, 법 제35조에 따른 해양시설오염비상계획서이고, 제4항의 변경신고 첨부서류는 신고증명서와 '변경내용을 증명하는 서류'이다. 사업자등록증·법인 등기사항증명서는 어디에도 없고, 제17조에는 행정정보 공동이용으로 확인한다는 조항이 없다. 별지 제12호서식(개정 2024.6.28.)은 신고인란에 상호(사업장 명칭)·성명(대표자)·생년월일을 적게 하면서 첨부서류란만 두고 담당 공무원 확인사항란과 행정정보 공동이용 동의란이 없으며, 첨부서류 2번의 근거 조문을 '「해양환경관리법」 제32조에 따른 해양오염방지관리인'(선박 관리인 조문)으로 적어 제17조제1항제2호(법 제36조)와 어긋난다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항제3호는 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있으면 서류 제출을 요구할 수 없고 담당자가 직접 확인·처리하도록 하며, 제7항은 변경·갱신 신청 시 기제출 서류의 재요구를 금지한다. 「전자정부법」 제36조제1항은 다른 행정기관으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있으면 같은 정보를 따로 수집하지 못하게 한다.
 [문제점] ① 신고 주체(법 제33조제1항: 소유자·설치운영자·임차인)의 동일성과 변경신고 대상인 대표자 변경(시행규칙 제17조제3항제1호)의 확인은 신고 처리에 실제로 필요한 심사 사항인데, 법령이 이를 확인할 서류나 확인 방법을 정하지 않아 부산청은 사업자등록증·법인 등기부등본을 법정 외 서류로 요구하고, 포항청도 "확인 목적"으로 제출받는다. 이는 민원처리법 제10조제1항에 반하는 상태가 법령 공백 때문에 상시화된 것이다. ② 두 서류 모두 행정정보 공동이용으로 확인 가능한 행정기관 발급 정보이므로 제10조제3항제3호에 따라 담당자가 직접 확인해야 하나, 시행규칙과 서식 어디에도 확인 조항·확인란·동의란이 없어 공동이용 절차를 시작할 근거가 없다(부산청은 공동이용 시스템을 이용한 적이 없음). ③ 변경신고의 '변경내용을 증명하는 서류'는 무엇을 내야 하는지 특정되지 않아 가장 빈번한 보완 사유가 된다. ④ 서식의 근거 조문 오기(제32조)는 신고인이 선박 관리인 조문을 찾게 하는 정합성 흠결이다.
 [논거] 신고 주체의 동일성·대표자 확인이라는 실질 확인의 근거는 법률(제33조제1항의 신고 주체 규정)과 부령(제17조제3항제1호)에 있고, 이를 확인할 서류·방법만 하위법령에 빠져 있는 유형이다. 법령에 없는 서류를 요구하는 실무를 법령에 맞추는 방법은 두 가지인데, 서류 요구를 중단하는 것은 확인을 불가능하게 하므로, 실무상 이미 요구되는 확인 사항을 서식의 '담당 공무원 확인사항'으로 옮겨 공동이용으로 대체하는 것이 민원처리법 제10조제3항·전자정부법 제36조제1항의 취지에 맞는 정비이다. 신고인에게 새로운 서류를 추가하는 것이 아니라 기존 요구 서류를 공동이용으로 대체하는 것이므로 규제 신설이 아니다.
 [개정 방향] ① (부령) 시행규칙 제17조에 "지방해양수산청장 또는 시·도지사는 「전자정부법」 제36조제1항에 따른 행정정보의 공동이용을 통하여 신고인의 법인 등기사항증명서(법인인 경우) 또는 사업자등록증명을 확인하여야 하며, 신고인이 확인에 동의하지 아니하는 경우에는 그 서류를 첨부하게 하여야 한다"는 확인 조항을 신설한다. ② (부령) 별지 제12호서식에 '담당 공무원 확인사항'란과 '행정정보 공동이용 동의서'란을 신설하고, 첨부서류 2번의 근거 조문을 '법 제36조'로 바로잡는다. ③ (부령) 제17조제4항제2호의 '변경내용을 증명하는 서류'를 변경 사유별로 예시한다(대표자·명칭 변경: ①의 공동이용 확인으로 갈음, 장소·규모 변경: 변경된 설치명세서·도면). 모두 부령만으로 가능하다.
-[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 한다. 일부 지방해양수산청 안내문에는 '담당 공무원은 전자정부법 제21조제1항에 따른 행정정보 공동이용으로 첨부서류 정보를 확인하여야 한다'는 구 조문이 실려 있으나 현행 제17조에는 그러한 조항이 없다. 법인 등기사항증명서·사업자등록증명이 지방해양수산청의 공동이용 대상 정보인지는 행정안전부(행정정보공동이용센터) 확인이 필요하며, 대상이 아니면 ①은 '신고인이 첨부' 방식으로만 정비한다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. [교차확인] 연번 12(포항청 인터뷰)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="303" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.3.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>포항지방해양수산청 해양수산환경과 7급 주무관 조호영(해양시설 신고·변경신고, 담당 약 3년, 기술직)
-면담자: 오세영 / 근무지 방문</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>시행규칙 제17조제1항(최초신고 첨부서류)·제4항제2호('변경내용을 증명하는 서류')
-시행규칙 별지 제12호서식(개정 2024.6.28.: 신고인란에 상호·대표자·생년월일 기재, 첨부서류란만 있고 담당 공무원 확인사항란·공동이용 동의란 없음, 첨부서류 2번의 근거 조문을 '법 제32조'로 오기)
-「민원 처리에 관한 법률」 제10조제1항·제3항제3호·제7항
-「전자정부법」 제36조제1항
-「해양환경관리법」 제33조제1항(신고 주체: 소유자·설치운영자·임차인)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 법령·서식에 없는 사진 등을 요구해서는 안 된다고 하면서도, 사업자등록증 같은 서류는 확인 목적으로 실제로 제출받고 있으며, 행정정보 공동이용 확인은 담당자의 전산 활용 능력에 따라 어려워 민원인의 협조를 구하기도 한다. 보완 요청은 거의 증빙자료 미비 때문이다.
-[발언] 조호영: "보완 요청은 거의 증빙자료 미비 때문입니다." / (면담자 오세영) "혹시 법령이나 서식에 명시되어 있지 않은 사진 같은 걸 요청하시는 경우도 있으신가요?" / 조호영: "그러면 안 되죠." / (면담자 오세영) "실제로 어떻게 하시는지요. 실제로는 다 제출받으시는 거네요." / 조호영: "일단 확인 목적으로요." / 조호영: "그런데 저희가 컴퓨터 활용에 대한 지식이 조금 부족한 경우도 있어서, 확인을 잘 못 하는 경우가 있을 수도 있어서 민원인의 협조를 구하기도 합니다."</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 시행규칙 제17조제1항의 최초신고 첨부서류는 설치명세서·도면·위치도, (해당 시설에 한해) 법 제36조에 따른 관리인 임명확인서, 법 제35조에 따른 해양시설오염비상계획서이고, 제4항의 변경신고 첨부서류는 신고증명서와 '변경내용을 증명하는 서류'이다. 사업자등록증·법인 등기사항증명서는 어디에도 없고, 제17조에는 행정정보 공동이용으로 확인한다는 조항이 없다. 별지 제12호서식(개정 2024.6.28.)은 신고인란에 상호(사업장 명칭)·성명(대표자)·생년월일을 적게 하면서 첨부서류란만 두고 담당 공무원 확인사항란과 행정정보 공동이용 동의란이 없으며, 첨부서류 2번의 근거 조문을 '「해양환경관리법」 제32조에 따른 해양오염방지관리인'(선박 관리인 조문)으로 적어 제17조제1항제2호(법 제36조)와 어긋난다. 「민원 처리에 관한 법률」 제10조제1항은 관계법령등에서 정한 구비서류 외의 서류 요구를 금지하고, 제3항제3호는 「전자정부법」 제36조제1항의 행정정보 공동이용으로 확인할 수 있으면 서류 제출을 요구할 수 없고 담당자가 직접 확인·처리하도록 하며, 제7항은 변경·갱신 신청 시 기제출 서류의 재요구를 금지한다. 「전자정부법」 제36조제1항은 다른 행정기관으로부터 신뢰할 수 있는 행정정보를 제공받을 수 있으면 같은 정보를 따로 수집하지 못하게 한다.
-[문제점] ① 신고 주체(법 제33조제1항: 소유자·설치운영자·임차인)의 동일성과 변경신고 대상인 대표자 변경(시행규칙 제17조제3항제1호)의 확인은 신고 처리에 실제로 필요한 심사 사항인데, 법령이 이를 확인할 서류나 확인 방법을 정하지 않아 부산청은 사업자등록증·법인 등기부등본을 법정 외 서류로 요구하고, 포항청도 "확인 목적"으로 제출받는다. 이는 민원처리법 제10조제1항에 반하는 상태가 법령 공백 때문에 상시화된 것이다. ② 두 서류 모두 행정정보 공동이용으로 확인 가능한 행정기관 발급 정보이므로 제10조제3항제3호에 따라 담당자가 직접 확인해야 하나, 시행규칙과 서식 어디에도 확인 조항·확인란·동의란이 없어 공동이용 절차를 시작할 근거가 없다(부산청은 공동이용 시스템을 이용한 적이 없음). ③ 변경신고의 '변경내용을 증명하는 서류'는 무엇을 내야 하는지 특정되지 않아 가장 빈번한 보완 사유가 된다. ④ 서식의 근거 조문 오기(제32조)는 신고인이 선박 관리인 조문을 찾게 하는 정합성 흠결이다.
-[논거] 신고 주체의 동일성·대표자 확인이라는 실질 확인의 근거는 법률(제33조제1항의 신고 주체 규정)과 부령(제17조제3항제1호)에 있고, 이를 확인할 서류·방법만 하위법령에 빠져 있는 유형이다. 법령에 없는 서류를 요구하는 실무를 법령에 맞추는 방법은 두 가지인데, 서류 요구를 중단하는 것은 확인을 불가능하게 하므로, 실무상 이미 요구되는 확인 사항을 서식의 '담당 공무원 확인사항'으로 옮겨 공동이용으로 대체하는 것이 민원처리법 제10조제3항·전자정부법 제36조제1항의 취지에 맞는 정비이다. 신고인에게 새로운 서류를 추가하는 것이 아니라 기존 요구 서류를 공동이용으로 대체하는 것이므로 규제 신설이 아니다.
-[개정 방향] ① (부령) 시행규칙 제17조에 "지방해양수산청장 또는 시·도지사는 「전자정부법」 제36조제1항에 따른 행정정보의 공동이용을 통하여 신고인의 법인 등기사항증명서(법인인 경우) 또는 사업자등록증명을 확인하여야 하며, 신고인이 확인에 동의하지 아니하는 경우에는 그 서류를 첨부하게 하여야 한다"는 확인 조항을 신설한다. ② (부령) 별지 제12호서식에 '담당 공무원 확인사항'란과 '행정정보 공동이용 동의서'란을 신설하고, 첨부서류 2번의 근거 조문을 '법 제36조'로 바로잡는다. ③ (부령) 제17조제4항제2호의 '변경내용을 증명하는 서류'를 변경 사유별로 예시한다(대표자·명칭 변경: ①의 공동이용 확인으로 갈음, 장소·규모 변경: 변경된 설치명세서·도면). 모두 부령만으로 가능하다.
-[유의] 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 한다. 일부 지방해양수산청 안내문에는 '담당 공무원은 전자정부법 제21조제1항에 따른 행정정보 공동이용으로 첨부서류 정보를 확인하여야 한다'는 구 조문이 실려 있으나 현행 제17조에는 그러한 조항이 없다. 법인 등기사항증명서·사업자등록증명이 지방해양수산청의 공동이용 대상 정보인지는 행정안전부(행정정보공동이용센터) 확인이 필요하며, 대상이 아니면 ①은 '신고인이 첨부' 방식으로만 정비한다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다. 포항청 인터뷰이의 발언은 면담자의 유도 질문('실제로는 다 제출받으시는 거네요')에 대한 짧은 긍정이므로 입법사실의 강도는 부산청보다 약하다. [교차확인] 연번 11(부산청 인터뷰)과 동일 쟁점.</t>
+[유의] 포항청 인터뷰이의 발언은 면담자의 유도 질문('실제로는 다 제출받으시는 거네요')에 대한 짧은 긍정이므로 입법사실의 강도는 부산청보다 약하다. 경계 사례이다. 요건 추가가 아니라 기존 운용 기준의 명시·대체 서류 허용으로 한정하여야 한다. 일부 지방해양수산청 안내문에는 '담당 공무원은 전자정부법 제21조제1항에 따른 행정정보 공동이용으로 첨부서류 정보를 확인하여야 한다'는 구 조문이 실려 있으나 현행 제17조에는 그러한 조항이 없다. 법인 등기사항증명서·사업자등록증명이 지방해양수산청의 공동이용 대상 정보인지는 행정안전부(행정정보공동이용센터) 확인이 필요하며, 대상이 아니면 ①은 '신고인이 첨부' 방식으로만 정비한다. 부산청의 공동이용 시스템 미이용은 운영 문제로 분리했다.</t>
         </is>
       </c>
     </row>
@@ -1126,7 +844,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>기준 2(일반법으로 해결 가능). 다만 해양환경관리법상 수리 여부가 불명확한 것이 원인이므로 본표 연번 5에서 함께 다룸.</t>
+          <t>기준 2(일반법으로 해결 가능). 다만 해양환경관리법상 수리 여부가 불명확한 것이 원인이므로 본표 연번 2에서 함께 다룸.</t>
         </is>
       </c>
     </row>
@@ -1151,7 +869,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>기준 1(운영 문제). 인터뷰이 간 발언 차이를 기록함. 본표 연번 5 [유의]에 반영.</t>
+          <t>기준 1(운영 문제). 인터뷰이 간 발언 차이를 기록함. 본표 연번 2 [유의]에 반영.</t>
         </is>
       </c>
     </row>
@@ -1176,7 +894,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>본표 연번 3~5의 입법사실(처리기간이 본문이 아닌 서식에만 있음)을 뒷받침함.</t>
+          <t>본표 연번 2의 입법사실(처리기간이 본문이 아닌 서식에만 있음)을 뒷받침함.</t>
         </is>
       </c>
     </row>
@@ -1201,7 +919,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>본표 연번 6에 반영.</t>
+          <t>본표 연번 3에 반영.</t>
         </is>
       </c>
     </row>
@@ -1226,7 +944,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>입법사실 없음. 본표 연번 6·7의 [현행 규정]·[유의]에 반영. 해양수산부에 안내문 수정 필요성을 전달할 사항.</t>
+          <t>입법사실 없음. 본표 연번 3의 [현행 규정]·[유의]에 반영. 해양수산부에 안내문 수정 필요성을 전달할 사항.</t>
         </is>
       </c>
     </row>
@@ -1271,7 +989,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>허가·등록 도입은 규제 신설·강화. 저위험 시설의 접수형 간소화 부분만 본표 연번 8~10(경미 변경의 수리 불요화)에 반영.</t>
+          <t>허가·등록 도입은 규제 신설·강화. 저위험 시설의 접수형 간소화 부분만 본표 연번 4(경미 변경의 수리 불요화)에 반영.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1376,7 +1094,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>입법사실 없음. [부수 정비 검토 가능] 본표 연번 8~10 정비 시 연계(해양경찰청 협의).</t>
+          <t>입법사실 없음. [부수 정비 검토 가능] 본표 연번 4 정비 시 연계(해양경찰청 협의).</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>기준 2(이미 규정, 재량 통일은 지침 사항). 제외. 금액 차등은 본표 연번 8에 반영.</t>
+          <t>기준 2(이미 규정, 재량 통일은 지침 사항). 제외. 금액 차등은 본표 연번 4에 반영.</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1169,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>기준 1·3. 제외. [부수 정비 검토 가능] 법 제33조에 폐업신고 근거와 기한을 두는 정비를 연번 3~7과 함께 검토.</t>
+          <t>기준 1·3. 제외. [부수 정비 검토 가능] 법 제33조에 폐업신고 근거와 기한을 두는 정비를 연번 2·3과 함께 검토.</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1219,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>입법사실 없음. [부수 정비 검토 가능] 본표 연번 11·12의 서식 정비 시 함께 바로잡을 것.</t>
+          <t>입법사실 없음. [부수 정비 검토 가능] 본표 연번 5의 서식 정비 시 함께 바로잡을 것.</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1244,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>입법사실 없음. 본표 연번 3~5 [문제점] ⑥·[개정 방향] ③에 반영.</t>
+          <t>입법사실 없음. 본표 연번 2 [문제점] ⑥·[개정 방향] ③에 반영.</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1269,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>포항청 조호영은 별표 1 대상 판단에 어려움이 없다고 하여("저희는 그런 시설은 거의 없고, 취수·배수시설과 기름 저장탱크 같은 게 많은데, 저장탱크는 보면 바로 알 수 있습니다.") 연번 1·2의 반대 사례로 기록함.</t>
+          <t>포항청 조호영은 별표 1 대상 판단에 어려움이 없다고 하여("저희는 그런 시설은 거의 없고, 취수·배수시설과 기름 저장탱크 같은 게 많은데, 저장탱크는 보면 바로 알 수 있습니다.") 연번 1의 반대 사례로 기록함.</t>
         </is>
       </c>
     </row>

--- a/해양시설신고/output/261012_입법영향분석_해양시설신고_법령개정_필요사항.xlsx
+++ b/해양시설신고/output/261012_입법영향분석_해양시설신고_법령개정_필요사항.xlsx
@@ -607,7 +607,7 @@
           <t>[현행 규정] 「해양환경관리법」 제33조(해양시설의 신고 및 변경신고) 제1항: 해양시설의 소유자(설치·운영자를 포함하며, 임대 시 시설임차인)는 제1호(배타적 경제수역, 국가관리무역항·국가관리연안항의 해양시설)는 해양수산부장관에게, 제2호(그 밖의 해역)는 시·도지사에게 그 시설을 신고하여야 하고, 신고내용 중 해양수산부령으로 정하는 중요한 내용의 변경이 있으면 변경신고를 하여야 함(각 호 구분은 2020.2.18. 개정, 변경신고 후단은 2016.12.27. 개정으로 신설). 제2항: 신고내용, 변경신고 대상인 중요한 내용, 신고·변경신고 절차 등은 해양수산부령으로 정함. 수리, 처리기한, 효력 발생 시점, 신고증명서에 관한 문언은 없음. 같은 법 제38조제3항(2023.10.24. 신설)은 오염물질저장시설 설치·운영 신고·변경신고에 대해 '신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지하여야 한다'고 규정함. 시행규칙 제17조(해양시설의 신고 등) 제1항: 소유자는 별지 제12호서식 최초신고서(전자문서 포함)에 ① 설치명세서와 도면·위치도(2만5천분의 1 지형도) ② 법 제36조에 따른 관리인 임명확인서(별표 1 제1호 시설) ③ 법 제35조에 따른 해양시설오염비상계획서(제19조제1항의 시설, 2024.6.28. 개정)를 첨부하여 지방해양수산청장 또는 시·도지사에게 제출(기한 없음) / 제2항: 신고를 받으면 별지 제13호서식 신고대장에 적고 별지 제14호서식 신고증명서를 발급하여야 함 / 제3항(2017.6.28. 신설): 법 제33조제1항 후단의 '중요한 내용의 변경'은 ① 소유자(사업장의 명칭 및 대표자 포함)의 변경 ② 설치 장소의 변경 ③ 규모의 100분의 50 이상 증가(②③은 별표 1 제1호가목 시설 한정) / 제4항(2017.6.28. 신설): 변경신고는 변경사유 발생일부터 30일 이내, 신고증명서와 변경내용 증명 서류 첨부 / 제5항: 변경신고를 받으면 신고대장·신고증명서 뒤쪽에 변경내용을 적고 신고증명서 발급 / 제6항: 재발급(별지 제15호서식) / 제7항: 폐업 시 별지 제16호서식 폐업신고서에 신고증명서를 첨부해 제출(기한 없음). 행정정보 공동이용 확인 조항은 없음. 별지 제12호서식(개정 2024.6.28.): 상단에 처리기간 '(최초)7일 (변경)5일' 기재, 첨부서류란은 제17조와 동일, 담당 공무원 확인사항란 없음, 뒤쪽 처리절차는 접수(민원실)→검토→결재→신고증명서 발급. 별지 제14호서식 신고증명서(개정 2015.1.8.)는 '해양시설의 (변경)신고하였음을 증명합니다'로 되어 있음. 시행령 제94조(권한의 위임) 제4항제2호: 해양수산부장관은 국가관리무역항·배타적 경제수역 해양시설의 '신고 및 변경신고의 접수'를 지방해양수산청장에게 위임 / 제6항제2호: 국가관리연안항 해양시설의 '신고 및 변경신고의 접수'를 시·도지사에게 위임. 같은 조 제4항제2호의3은 법 제38조제3항의 오염물질저장시설 신고·변경신고에 대해서는 '수리'를 위임하고 있어, 해양시설 신고는 '접수'만, 오염물질저장시설 신고는 '수리'를 위임하는 문언상 구분이 있음. 「행정기본법」 제34조: 법률에 수리가 필요하다고 명시된 신고(내부 업무 처리 절차로서의 수리 제외)는 수리하여야 효력 발생. 「행정절차법」 제40조제2항~제4항: 형식 요건을 갖춘 신고는 도달 시 의무 이행, 미비 시 보완 요구 후 미보완이면 이유를 밝혀 반려. 「민원 처리에 관한 법률」 제19조: 처리기간 5일 이하는 '시간' 단위(1일 8시간), 6일 이상은 '일' 단위, 토요일·공휴일 불산입 / 제22조제1항·시행령 제24조·제25조: 접수 후 보완 요구, 미보완 시 반려.
 [문제점] ① 법 제33조에는 수리에 관한 문언이 없으므로 「행정기본법」 제34조에 따르면 법률상으로는 수리를 요하지 않는 신고이고, 「행정절차법」 제40조제2항에 따라 형식 요건을 갖춘 신고서가 도달한 때 의무가 이행된다. 시행령 제94조가 해양시설 신고에 대해서는 '접수'만 위임하고(제4항제2호·제6항제2호) 오염물질저장시설 신고에 대해서는 '수리'를 위임하는(제4항제2호의3) 점, 별지 제14호서식 신고증명서가 '신고하였음을 증명합니다'라고 되어 있는 점도 접수형 설계를 뒷받침한다. 그러나 세 지방청 모두 서류 검토(군산·포항은 현장 확인 포함)와 내부 결재를 거쳐 신고증명서를 발급한 때 효력이 발생하는 '수리를 요하는 신고'로 운영한다(서식 뒤쪽 처리절차도 접수→검토→결재→발급). 법 문언과 실무상 법적 성격이 다르다. ② 같은 법 제38조제3항은 오염물질저장시설 신고·변경신고에 대해 '받은 날부터 해양수산부령으로 정하는 기간 내에 신고 수리여부를 신고인에게 통지'하도록 하는데, 성격이 유사한 해양시설 신고(제33조)에는 그런 규정이 없어 같은 법 안에서 신고 유형 간 정합성이 없다. ③ 처리기한이 법령 본문이 아니라 별지 서식 상단에만 기재되어 있어 담당자가 "시행규칙에는 없던데요"라는 질문에 서식을 근거로 답해야 하고, 서식의 '5일'은 민원처리법 제19조제1항에 따라 시간 단위(1일 8시간)로 계산되는 등 적용 기준이 불명확하다. ④ 행정청이 어디까지 확인하는지(형식 심사, 현장 확인 여부)가 법령에 없어 지방청별로 현장 확인 원칙(군산·포항)과 생략(부산)으로 갈린다. ⑤ 수리 통지·수리 간주 조항이 없어 증명서 발급이 지연되면 신고인은 의무 이행 여부가 불확실한 상태에 놓이고, 부산청은 서류가 갖춰질 때까지 접수 자체를 하지 않는 방식으로 운영하여 행정절차법 제40조제3항·민원처리법 제22조제1항(접수 후 보완 요구)과 어긋난다. ⑥ 시행령은 지방해양수산청장·시·도지사에게 '접수'만 위임하는데 시행규칙 제17조제2항·제5항은 이들이 신고증명서를 발급하도록 하여, 증명서 발급(실무상 수리) 권한의 소재가 시행령과 시행규칙 사이에서 정합하지 않는다.
 [논거] 「행정기본법」 제34조는 수리가 필요한 신고를 '법률'에 명시하도록 하므로, 부령·서식·실무로 수리형 절차를 운용하는 현재 구조는 법률유보 원칙에 반할 소지가 있다. 반대로 법률 문언대로 수리 불요 신고라면 접수 거부·반려 실무는 「행정절차법」 제40조를 위반한다. 어느 쪽으로 보더라도 법령과 실무의 불일치가 확인되므로 재량·운영 사항이 아니라 법적 성격을 법률에서 확정해야 하는 정비 사항이며, 같은 법 제38조제3항이 2023년에 수리 통지 조항을 둔 이상 제33조만 비워 두는 것은 법 내부의 정합성 문제이다. 면담자와 인터뷰이(포항)의 "시행규칙을 개정하면 된다"는 견해는 위임 조문(법 제33조제2항: 신고내용·절차)으로 검증하면 처리기한·서식·첨부서류에는 타당하나, 수리 여부와 효력 발생 시점은 행정기본법 제34조상 법률 사항이어서 부령만으로는 정비할 수 없다.
-[개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 4과 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
+[개정 방향] ① (법률) 법 제33조에 제38조제3항과 같은 방식으로 "해양수산부장관 또는 시·도지사는 제1항에 따른 신고 또는 변경신고를 받은 날부터 해양수산부령으로 정하는 기간 내에 신고수리 여부를 신고인에게 통지하여야 한다"는 항과, 그 기간(민원처리 관계법령에 따른 연장 기간 포함) 내에 통지하지 아니하면 기간이 끝난 날의 다음 날에 수리한 것으로 보는 수리 간주 항을 신설하여 최초신고와 시설 변경(장소·규모)을 수리를 요하는 신고로 명확히 한다. 대표자·명칭 변경 등 경미한 사항은 수리 불요 신고(도달 시 효력)로 구분한다(연번 4와 연계). ② (부령) 시행규칙 제17조제2항·제5항에 처리기한을 본문으로 옮기고(서식 기재와 일치), 신고 내용의 확인 방법(서류 심사, 필요 시 현장 확인)과 신고증명서의 성격(수리 사실의 증명)을 명시하며, 별지 제14호서식의 문구를 맞춘다. ③ (시행령) 제94조제4항제2호·제6항제2호의 '접수'를 '접수·수리 및 신고증명서 발급'으로 정비하여 시행규칙 제17조제2항·제5항과 맞춘다(제2호의3과 같은 방식). 최소 정비안은 ②·③이나, 법적 성격의 확정은 ①(법률) 없이는 완결되지 않는다.
 [유의] 군산청 인터뷰이는 수리형 유지에 찬성하면서 제도 완화에는 신중한 입장("사회재난 같은 것들이 더 중요시되는 상황에서 제도를 갑자기 완화해 버리면 문제가 발생하지 않을까")이므로, 수리 간주는 '수리형 유지 + 기한 명확화'로 설명하는 것이 입법사실과 부합한다. 포항청 인터뷰이는 처음에는 규정 추가가 "굳이 그럴 필요까지는 없을 것 같"다고 했다가 명시하면 더 명확해진다고 답했고, 자기완결형 전환에는 부정적(사전 검토 과정 상실 우려)이므로 수리형 유지를 전제로 한 정비임을 밝혀야 한다. 포항청 인터뷰이가 '민원처리법상 법정 처리기간 7일'이라고 한 부분은 민원처리법이 아니라 별지 제12호서식 기재 기간으로 확인되며, 검토메모에 차이를 기록했다. 부산청의 '서류 완비 전 미접수' 운영은 법령 정비와 별개로 민원처리법 제22조제1항·행정절차법 제40조제3항에 따라 바로잡을 운영 사항이며(검토메모), 본 행은 그 원인이 되는 법적 성격·절차 규정의 공백을 다룬다. 부산청 인터뷰이는 효력에 대해 "신고를 했기 때문에 과태료를 받지 않는다는 정도"라고 하여 수리의 실익이 크지 않다고 보므로, 경미 사항의 수리 불요 전환(연번 4)과 함께 설계해야 한다. 처리기한을 정할 때 민원처리법 제19조의 계산 방식(5일 이하 시간 단위, 토요일·공휴일 불산입)과 연장 규정을 반영하고, 행정안전부(민원제도)·법제처와 협의가 필요하다. 수리 간주 도입은 규제 완화에 해당하여 규제영향분석 대상이 아니다. 국가관리연안항 해양시설은 법 제33조제1항제1호에서 해양수산부장관 관할로 두면서 시행령 제94조제6항제2호가 접수를 시·도지사에게 위임하고 있어 ③ 정비 시 함께 검토한다.</t>
         </is>
       </c>
@@ -659,7 +659,7 @@
           <t>[현행 규정] 법 제33조제1항은 해양시설 소유자의 신고 의무만 정하고 '언제까지' 신고해야 하는지 정하지 않으며, 제2항은 신고내용·절차를 부령에 위임한다. 시행규칙 제17조제1항은 "법 제33조제1항 전단에 따라 해양시설의 신고를 하려는 경우에는" 최초신고서를 제출하도록 할 뿐 기한을 두지 않고, 제4항은 변경신고에만 '변경사유가 발생한 날부터 30일 이내'를 두며, 제7항의 폐업신고에도 기한이 없다(해양수산부 FAQ와 구 국토해양부 안내의 '최초신고는 사업개시 후 30일 이내', '폐업신고는 폐업일부터 30일 이내'는 현행 조문에 근거가 없다). 법 제132조제2항제2호: '제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 아니한 자'는 500만원 이하의 과태료. 시행령 제98조·별표 19(개정 2026.6.30.) 개별기준 너목: '법 제33조제1항을 위반하여 해양시설의 신고 또는 변경신고를 하지 않은 경우' 250만원(최초신고 미이행과 변경신고 미이행을 구분하지 않음). 같은 별표에서 관리인 임명 신고 미이행(법 제36조제2항)은 30만원, 안전점검 결과 보고 미이행은 500만원. 일반기준 나목: 질서위반행위규제법 시행령 제2조의2제1항 사유, 사소한 부주의·오류, 시정 노력 등에 2분의 1 범위 감경 / 다목(2026.6.30. 신설): 고의·중과실 없는 소상공인은 100분의 70 범위 감경. 과태료 부과·징수 권한은 시행령 제94조제4항제25호(지방해양수산청장)·제6항제4호(시·도지사, 국가관리연안항의 제2호 위반 한정)로 위임. 「질서위반행위규제법」 제6조: 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 아니한다.
 [문제점] ① 최초신고의 의무 발생 시점(설치 완료, 사용 개시, 공사 중 일부 가동)이 법령에 없어, 담당자가 "완공이 되어야 한다"고 안내하고 민원인은 "신고 시점이 법에 나와 있지 않다"고 이의를 제기한다. 배수관처럼 수 킬로미터 공정 중 일부만 가동되는 시설은 신고 시점을 특정할 수 없다. ② 변경신고에는 30일 기한이 있어, 같은 호의 과태료(별표 19 너목: 신고·변경신고 미이행 동일 250만원)가 변경신고에는 적용 시점이 분명하고 최초신고에는 불분명한 비대칭이 생긴다. ③ 서류 미비로 증명서가 발급되지 않은 경우를 "최초 신고를 지연한 상황"으로 보고 과태료를 검토하는데, 기한이 없으니 지연 여부 자체를 판단할 수 없어 부과가 "애매"해진다. ④ 행정안내(FAQ)가 조문에 없는 30일 기한을 안내하고 있어, 수범자는 안내문을, 담당자는 조문을 기준으로 삼는 불일치가 있다.
 [논거] 과태료의 구성요건인 '신고를 하지 아니한' 상태는 신고 의무의 이행 기한이 있어야 성립 시점이 확정된다. 법률에 따르지 아니하고는 어떤 행위도 질서위반행위로 과태료를 부과하지 못하며(「질서위반행위규제법」 제6조) 그 요건은 명확해야 하므로, 기한 없는 의무에 제재를 결부한 현행 구조는 명확성 원칙에 비추어 정비 대상이다. 행정안내로 30일을 운용하는 것은 법령 근거 없이 제재 요건을 보충하는 것이어서 해석·지침으로 해결할 수 없다. 인터뷰이(군산)의 '상식 사항' 견해는 민원인이 실제로 다투고 있다는 같은 인터뷰이의 진술과 상충한다.
-[개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항·제7항에 같은 기산점을 반영하고(폐업신고 기한도 함께), 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행·변경신고 미이행·기한 경과 후 신고로 구분한다(연번 4과 연계). 최소 정비안은 ②이나, 의무의 내용(기한)이 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
+[개정 방향] ① (법률) 법 제33조제1항에 "해양시설을 설치한 날(기존 시설을 승계·임차한 경우에는 승계·임차한 날)부터 ○일 이내에" 또는 "해양시설의 사용을 개시한 날부터 ○일 이내에"처럼 기산점과 기한을 명시한다. 공사 중 일부 가동 시설은 '사용 개시'를 기산점으로 삼으면 해소된다. ② (부령) 시행규칙 제17조제1항·제7항에 같은 기산점을 반영하고(폐업신고 기한도 함께), 준공 서류가 없는 단계의 첨부서류 대체 방법을 둔다. ③ (시행령) 별표 19 너목을 최초신고 미이행·변경신고 미이행·기한 경과 후 신고로 구분한다(연번 4와 연계). 최소 정비안은 ②이나, 의무의 내용(기한)이 법 제33조제2항의 위임('신고 절차')에 포함되는지 다툼이 있으므로 법률에 두는 것이 안전하다.
 [유의] 군산청 인터뷰이는 입법 불요 의견이므로 그 발언은 '신고 시점 불명확으로 인한 민원 혼선'의 입법사실로만 사용하고, 개정 필요성의 판단 근거는 부산청 인터뷰이가 제기한 과태료 집행 문제에 둔다. 부산청 인터뷰이가 말한 '변경 신고 처리 기한'은 맥락상 신고인의 변경신고 기한(시행규칙 제17조제4항, 30일)을 가리키는 것으로 보이며, 행정청의 처리기간(서식 5일)과 구분하여 검토메모에 기록했다. 해양수산부 FAQ·지방청 안내문의 '30일' 문구는 법령 근거 없는 안내이므로 정비 전까지 수정이 필요하다는 점을 해양수산부에 전달할 필요가 있다. 군산청 신재민은 "상식적인 부분이라 이것까지 법에 담을 필요는 없을 것 같"다고 반대했다.</t>
         </is>
       </c>
